--- a/templates/project-template.xlsx
+++ b/templates/project-template.xlsx
@@ -4050,13 +4050,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH20"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -4086,7 +4086,6 @@
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
     <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="11" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4097,107 +4096,102 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>max |residual|</t>
+          <t>max breach</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tolerance</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>status</t>
         </is>
       </c>
+      <c r="D1" s="7" t="n">
+        <v>2027</v>
+      </c>
       <c r="E1" s="7" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="F1" s="7" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G1" s="7" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="H1" s="7" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="I1" s="7" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="J1" s="7" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="K1" s="7" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="L1" s="7" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="M1" s="7" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="N1" s="7" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="O1" s="7" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="P1" s="7" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Q1" s="7" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="R1" s="7" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="S1" s="7" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="T1" s="7" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="U1" s="7" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="V1" s="7" t="n">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="W1" s="7" t="n">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="X1" s="7" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y1" s="7" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Z1" s="7" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AA1" s="7" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AB1" s="7" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AC1" s="7" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AD1" s="7" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AE1" s="7" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AF1" s="7" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AG1" s="7" t="n">
-        <v>2055</v>
-      </c>
-      <c r="AH1" s="7" t="n">
         <v>2056</v>
       </c>
     </row>
@@ -4208,134 +4202,131 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <f>MAX(E2:AH2)</f>
-        <v/>
-      </c>
-      <c r="C2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D2">
-        <f>IF(B2&lt;=C2,"PASS","FAIL")</f>
+        <f>MAX(D2:AG2)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>IF(B2=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D2" s="13">
+        <f>MAX(0,ABS(Statements!C8-(Statements!C6-Statements!C7))-MAX(0.01,0.001*ABS(Statements!C8)))</f>
         <v/>
       </c>
       <c r="E2" s="13">
-        <f>ABS(Statements!C8-(Statements!C6-Statements!C7))</f>
+        <f>MAX(0,ABS(Statements!D8-(Statements!D6-Statements!D7))-MAX(0.01,0.001*ABS(Statements!D8)))</f>
         <v/>
       </c>
       <c r="F2" s="13">
-        <f>ABS(Statements!D8-(Statements!D6-Statements!D7))</f>
+        <f>MAX(0,ABS(Statements!E8-(Statements!E6-Statements!E7))-MAX(0.01,0.001*ABS(Statements!E8)))</f>
         <v/>
       </c>
       <c r="G2" s="13">
-        <f>ABS(Statements!E8-(Statements!E6-Statements!E7))</f>
+        <f>MAX(0,ABS(Statements!F8-(Statements!F6-Statements!F7))-MAX(0.01,0.001*ABS(Statements!F8)))</f>
         <v/>
       </c>
       <c r="H2" s="13">
-        <f>ABS(Statements!F8-(Statements!F6-Statements!F7))</f>
+        <f>MAX(0,ABS(Statements!G8-(Statements!G6-Statements!G7))-MAX(0.01,0.001*ABS(Statements!G8)))</f>
         <v/>
       </c>
       <c r="I2" s="13">
-        <f>ABS(Statements!G8-(Statements!G6-Statements!G7))</f>
+        <f>MAX(0,ABS(Statements!H8-(Statements!H6-Statements!H7))-MAX(0.01,0.001*ABS(Statements!H8)))</f>
         <v/>
       </c>
       <c r="J2" s="13">
-        <f>ABS(Statements!H8-(Statements!H6-Statements!H7))</f>
+        <f>MAX(0,ABS(Statements!I8-(Statements!I6-Statements!I7))-MAX(0.01,0.001*ABS(Statements!I8)))</f>
         <v/>
       </c>
       <c r="K2" s="13">
-        <f>ABS(Statements!I8-(Statements!I6-Statements!I7))</f>
+        <f>MAX(0,ABS(Statements!J8-(Statements!J6-Statements!J7))-MAX(0.01,0.001*ABS(Statements!J8)))</f>
         <v/>
       </c>
       <c r="L2" s="13">
-        <f>ABS(Statements!J8-(Statements!J6-Statements!J7))</f>
+        <f>MAX(0,ABS(Statements!K8-(Statements!K6-Statements!K7))-MAX(0.01,0.001*ABS(Statements!K8)))</f>
         <v/>
       </c>
       <c r="M2" s="13">
-        <f>ABS(Statements!K8-(Statements!K6-Statements!K7))</f>
+        <f>MAX(0,ABS(Statements!L8-(Statements!L6-Statements!L7))-MAX(0.01,0.001*ABS(Statements!L8)))</f>
         <v/>
       </c>
       <c r="N2" s="13">
-        <f>ABS(Statements!L8-(Statements!L6-Statements!L7))</f>
+        <f>MAX(0,ABS(Statements!M8-(Statements!M6-Statements!M7))-MAX(0.01,0.001*ABS(Statements!M8)))</f>
         <v/>
       </c>
       <c r="O2" s="13">
-        <f>ABS(Statements!M8-(Statements!M6-Statements!M7))</f>
+        <f>MAX(0,ABS(Statements!N8-(Statements!N6-Statements!N7))-MAX(0.01,0.001*ABS(Statements!N8)))</f>
         <v/>
       </c>
       <c r="P2" s="13">
-        <f>ABS(Statements!N8-(Statements!N6-Statements!N7))</f>
+        <f>MAX(0,ABS(Statements!O8-(Statements!O6-Statements!O7))-MAX(0.01,0.001*ABS(Statements!O8)))</f>
         <v/>
       </c>
       <c r="Q2" s="13">
-        <f>ABS(Statements!O8-(Statements!O6-Statements!O7))</f>
+        <f>MAX(0,ABS(Statements!P8-(Statements!P6-Statements!P7))-MAX(0.01,0.001*ABS(Statements!P8)))</f>
         <v/>
       </c>
       <c r="R2" s="13">
-        <f>ABS(Statements!P8-(Statements!P6-Statements!P7))</f>
+        <f>MAX(0,ABS(Statements!Q8-(Statements!Q6-Statements!Q7))-MAX(0.01,0.001*ABS(Statements!Q8)))</f>
         <v/>
       </c>
       <c r="S2" s="13">
-        <f>ABS(Statements!Q8-(Statements!Q6-Statements!Q7))</f>
+        <f>MAX(0,ABS(Statements!R8-(Statements!R6-Statements!R7))-MAX(0.01,0.001*ABS(Statements!R8)))</f>
         <v/>
       </c>
       <c r="T2" s="13">
-        <f>ABS(Statements!R8-(Statements!R6-Statements!R7))</f>
+        <f>MAX(0,ABS(Statements!S8-(Statements!S6-Statements!S7))-MAX(0.01,0.001*ABS(Statements!S8)))</f>
         <v/>
       </c>
       <c r="U2" s="13">
-        <f>ABS(Statements!S8-(Statements!S6-Statements!S7))</f>
+        <f>MAX(0,ABS(Statements!T8-(Statements!T6-Statements!T7))-MAX(0.01,0.001*ABS(Statements!T8)))</f>
         <v/>
       </c>
       <c r="V2" s="13">
-        <f>ABS(Statements!T8-(Statements!T6-Statements!T7))</f>
+        <f>MAX(0,ABS(Statements!U8-(Statements!U6-Statements!U7))-MAX(0.01,0.001*ABS(Statements!U8)))</f>
         <v/>
       </c>
       <c r="W2" s="13">
-        <f>ABS(Statements!U8-(Statements!U6-Statements!U7))</f>
+        <f>MAX(0,ABS(Statements!V8-(Statements!V6-Statements!V7))-MAX(0.01,0.001*ABS(Statements!V8)))</f>
         <v/>
       </c>
       <c r="X2" s="13">
-        <f>ABS(Statements!V8-(Statements!V6-Statements!V7))</f>
+        <f>MAX(0,ABS(Statements!W8-(Statements!W6-Statements!W7))-MAX(0.01,0.001*ABS(Statements!W8)))</f>
         <v/>
       </c>
       <c r="Y2" s="13">
-        <f>ABS(Statements!W8-(Statements!W6-Statements!W7))</f>
+        <f>MAX(0,ABS(Statements!X8-(Statements!X6-Statements!X7))-MAX(0.01,0.001*ABS(Statements!X8)))</f>
         <v/>
       </c>
       <c r="Z2" s="13">
-        <f>ABS(Statements!X8-(Statements!X6-Statements!X7))</f>
+        <f>MAX(0,ABS(Statements!Y8-(Statements!Y6-Statements!Y7))-MAX(0.01,0.001*ABS(Statements!Y8)))</f>
         <v/>
       </c>
       <c r="AA2" s="13">
-        <f>ABS(Statements!Y8-(Statements!Y6-Statements!Y7))</f>
+        <f>MAX(0,ABS(Statements!Z8-(Statements!Z6-Statements!Z7))-MAX(0.01,0.001*ABS(Statements!Z8)))</f>
         <v/>
       </c>
       <c r="AB2" s="13">
-        <f>ABS(Statements!Z8-(Statements!Z6-Statements!Z7))</f>
+        <f>MAX(0,ABS(Statements!AA8-(Statements!AA6-Statements!AA7))-MAX(0.01,0.001*ABS(Statements!AA8)))</f>
         <v/>
       </c>
       <c r="AC2" s="13">
-        <f>ABS(Statements!AA8-(Statements!AA6-Statements!AA7))</f>
+        <f>MAX(0,ABS(Statements!AB8-(Statements!AB6-Statements!AB7))-MAX(0.01,0.001*ABS(Statements!AB8)))</f>
         <v/>
       </c>
       <c r="AD2" s="13">
-        <f>ABS(Statements!AB8-(Statements!AB6-Statements!AB7))</f>
+        <f>MAX(0,ABS(Statements!AC8-(Statements!AC6-Statements!AC7))-MAX(0.01,0.001*ABS(Statements!AC8)))</f>
         <v/>
       </c>
       <c r="AE2" s="13">
-        <f>ABS(Statements!AC8-(Statements!AC6-Statements!AC7))</f>
+        <f>MAX(0,ABS(Statements!AD8-(Statements!AD6-Statements!AD7))-MAX(0.01,0.001*ABS(Statements!AD8)))</f>
         <v/>
       </c>
       <c r="AF2" s="13">
-        <f>ABS(Statements!AD8-(Statements!AD6-Statements!AD7))</f>
+        <f>MAX(0,ABS(Statements!AE8-(Statements!AE6-Statements!AE7))-MAX(0.01,0.001*ABS(Statements!AE8)))</f>
         <v/>
       </c>
       <c r="AG2" s="13">
-        <f>ABS(Statements!AE8-(Statements!AE6-Statements!AE7))</f>
-        <v/>
-      </c>
-      <c r="AH2" s="13">
-        <f>ABS(Statements!AF8-(Statements!AF6-Statements!AF7))</f>
+        <f>MAX(0,ABS(Statements!AF8-(Statements!AF6-Statements!AF7))-MAX(0.01,0.001*ABS(Statements!AF8)))</f>
         <v/>
       </c>
     </row>
@@ -4346,134 +4337,131 @@
         </is>
       </c>
       <c r="B3" s="13">
-        <f>MAX(E3:AH3)</f>
-        <v/>
-      </c>
-      <c r="C3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D3">
-        <f>IF(B3&lt;=C3,"PASS","FAIL")</f>
+        <f>MAX(D3:AG3)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>IF(B3=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D3" s="13">
+        <f>MAX(0,ABS(Statements!C10-(Statements!C8-Statements!C9))-MAX(0.01,0.001*ABS(Statements!C10)))</f>
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>ABS(Statements!C10-(Statements!C8-Statements!C9))</f>
+        <f>MAX(0,ABS(Statements!D10-(Statements!D8-Statements!D9))-MAX(0.01,0.001*ABS(Statements!D10)))</f>
         <v/>
       </c>
       <c r="F3" s="13">
-        <f>ABS(Statements!D10-(Statements!D8-Statements!D9))</f>
+        <f>MAX(0,ABS(Statements!E10-(Statements!E8-Statements!E9))-MAX(0.01,0.001*ABS(Statements!E10)))</f>
         <v/>
       </c>
       <c r="G3" s="13">
-        <f>ABS(Statements!E10-(Statements!E8-Statements!E9))</f>
+        <f>MAX(0,ABS(Statements!F10-(Statements!F8-Statements!F9))-MAX(0.01,0.001*ABS(Statements!F10)))</f>
         <v/>
       </c>
       <c r="H3" s="13">
-        <f>ABS(Statements!F10-(Statements!F8-Statements!F9))</f>
+        <f>MAX(0,ABS(Statements!G10-(Statements!G8-Statements!G9))-MAX(0.01,0.001*ABS(Statements!G10)))</f>
         <v/>
       </c>
       <c r="I3" s="13">
-        <f>ABS(Statements!G10-(Statements!G8-Statements!G9))</f>
+        <f>MAX(0,ABS(Statements!H10-(Statements!H8-Statements!H9))-MAX(0.01,0.001*ABS(Statements!H10)))</f>
         <v/>
       </c>
       <c r="J3" s="13">
-        <f>ABS(Statements!H10-(Statements!H8-Statements!H9))</f>
+        <f>MAX(0,ABS(Statements!I10-(Statements!I8-Statements!I9))-MAX(0.01,0.001*ABS(Statements!I10)))</f>
         <v/>
       </c>
       <c r="K3" s="13">
-        <f>ABS(Statements!I10-(Statements!I8-Statements!I9))</f>
+        <f>MAX(0,ABS(Statements!J10-(Statements!J8-Statements!J9))-MAX(0.01,0.001*ABS(Statements!J10)))</f>
         <v/>
       </c>
       <c r="L3" s="13">
-        <f>ABS(Statements!J10-(Statements!J8-Statements!J9))</f>
+        <f>MAX(0,ABS(Statements!K10-(Statements!K8-Statements!K9))-MAX(0.01,0.001*ABS(Statements!K10)))</f>
         <v/>
       </c>
       <c r="M3" s="13">
-        <f>ABS(Statements!K10-(Statements!K8-Statements!K9))</f>
+        <f>MAX(0,ABS(Statements!L10-(Statements!L8-Statements!L9))-MAX(0.01,0.001*ABS(Statements!L10)))</f>
         <v/>
       </c>
       <c r="N3" s="13">
-        <f>ABS(Statements!L10-(Statements!L8-Statements!L9))</f>
+        <f>MAX(0,ABS(Statements!M10-(Statements!M8-Statements!M9))-MAX(0.01,0.001*ABS(Statements!M10)))</f>
         <v/>
       </c>
       <c r="O3" s="13">
-        <f>ABS(Statements!M10-(Statements!M8-Statements!M9))</f>
+        <f>MAX(0,ABS(Statements!N10-(Statements!N8-Statements!N9))-MAX(0.01,0.001*ABS(Statements!N10)))</f>
         <v/>
       </c>
       <c r="P3" s="13">
-        <f>ABS(Statements!N10-(Statements!N8-Statements!N9))</f>
+        <f>MAX(0,ABS(Statements!O10-(Statements!O8-Statements!O9))-MAX(0.01,0.001*ABS(Statements!O10)))</f>
         <v/>
       </c>
       <c r="Q3" s="13">
-        <f>ABS(Statements!O10-(Statements!O8-Statements!O9))</f>
+        <f>MAX(0,ABS(Statements!P10-(Statements!P8-Statements!P9))-MAX(0.01,0.001*ABS(Statements!P10)))</f>
         <v/>
       </c>
       <c r="R3" s="13">
-        <f>ABS(Statements!P10-(Statements!P8-Statements!P9))</f>
+        <f>MAX(0,ABS(Statements!Q10-(Statements!Q8-Statements!Q9))-MAX(0.01,0.001*ABS(Statements!Q10)))</f>
         <v/>
       </c>
       <c r="S3" s="13">
-        <f>ABS(Statements!Q10-(Statements!Q8-Statements!Q9))</f>
+        <f>MAX(0,ABS(Statements!R10-(Statements!R8-Statements!R9))-MAX(0.01,0.001*ABS(Statements!R10)))</f>
         <v/>
       </c>
       <c r="T3" s="13">
-        <f>ABS(Statements!R10-(Statements!R8-Statements!R9))</f>
+        <f>MAX(0,ABS(Statements!S10-(Statements!S8-Statements!S9))-MAX(0.01,0.001*ABS(Statements!S10)))</f>
         <v/>
       </c>
       <c r="U3" s="13">
-        <f>ABS(Statements!S10-(Statements!S8-Statements!S9))</f>
+        <f>MAX(0,ABS(Statements!T10-(Statements!T8-Statements!T9))-MAX(0.01,0.001*ABS(Statements!T10)))</f>
         <v/>
       </c>
       <c r="V3" s="13">
-        <f>ABS(Statements!T10-(Statements!T8-Statements!T9))</f>
+        <f>MAX(0,ABS(Statements!U10-(Statements!U8-Statements!U9))-MAX(0.01,0.001*ABS(Statements!U10)))</f>
         <v/>
       </c>
       <c r="W3" s="13">
-        <f>ABS(Statements!U10-(Statements!U8-Statements!U9))</f>
+        <f>MAX(0,ABS(Statements!V10-(Statements!V8-Statements!V9))-MAX(0.01,0.001*ABS(Statements!V10)))</f>
         <v/>
       </c>
       <c r="X3" s="13">
-        <f>ABS(Statements!V10-(Statements!V8-Statements!V9))</f>
+        <f>MAX(0,ABS(Statements!W10-(Statements!W8-Statements!W9))-MAX(0.01,0.001*ABS(Statements!W10)))</f>
         <v/>
       </c>
       <c r="Y3" s="13">
-        <f>ABS(Statements!W10-(Statements!W8-Statements!W9))</f>
+        <f>MAX(0,ABS(Statements!X10-(Statements!X8-Statements!X9))-MAX(0.01,0.001*ABS(Statements!X10)))</f>
         <v/>
       </c>
       <c r="Z3" s="13">
-        <f>ABS(Statements!X10-(Statements!X8-Statements!X9))</f>
+        <f>MAX(0,ABS(Statements!Y10-(Statements!Y8-Statements!Y9))-MAX(0.01,0.001*ABS(Statements!Y10)))</f>
         <v/>
       </c>
       <c r="AA3" s="13">
-        <f>ABS(Statements!Y10-(Statements!Y8-Statements!Y9))</f>
+        <f>MAX(0,ABS(Statements!Z10-(Statements!Z8-Statements!Z9))-MAX(0.01,0.001*ABS(Statements!Z10)))</f>
         <v/>
       </c>
       <c r="AB3" s="13">
-        <f>ABS(Statements!Z10-(Statements!Z8-Statements!Z9))</f>
+        <f>MAX(0,ABS(Statements!AA10-(Statements!AA8-Statements!AA9))-MAX(0.01,0.001*ABS(Statements!AA10)))</f>
         <v/>
       </c>
       <c r="AC3" s="13">
-        <f>ABS(Statements!AA10-(Statements!AA8-Statements!AA9))</f>
+        <f>MAX(0,ABS(Statements!AB10-(Statements!AB8-Statements!AB9))-MAX(0.01,0.001*ABS(Statements!AB10)))</f>
         <v/>
       </c>
       <c r="AD3" s="13">
-        <f>ABS(Statements!AB10-(Statements!AB8-Statements!AB9))</f>
+        <f>MAX(0,ABS(Statements!AC10-(Statements!AC8-Statements!AC9))-MAX(0.01,0.001*ABS(Statements!AC10)))</f>
         <v/>
       </c>
       <c r="AE3" s="13">
-        <f>ABS(Statements!AC10-(Statements!AC8-Statements!AC9))</f>
+        <f>MAX(0,ABS(Statements!AD10-(Statements!AD8-Statements!AD9))-MAX(0.01,0.001*ABS(Statements!AD10)))</f>
         <v/>
       </c>
       <c r="AF3" s="13">
-        <f>ABS(Statements!AD10-(Statements!AD8-Statements!AD9))</f>
+        <f>MAX(0,ABS(Statements!AE10-(Statements!AE8-Statements!AE9))-MAX(0.01,0.001*ABS(Statements!AE10)))</f>
         <v/>
       </c>
       <c r="AG3" s="13">
-        <f>ABS(Statements!AE10-(Statements!AE8-Statements!AE9))</f>
-        <v/>
-      </c>
-      <c r="AH3" s="13">
-        <f>ABS(Statements!AF10-(Statements!AF8-Statements!AF9))</f>
+        <f>MAX(0,ABS(Statements!AF10-(Statements!AF8-Statements!AF9))-MAX(0.01,0.001*ABS(Statements!AF10)))</f>
         <v/>
       </c>
     </row>
@@ -4484,134 +4472,131 @@
         </is>
       </c>
       <c r="B4" s="13">
-        <f>MAX(E4:AH4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D4">
-        <f>IF(B4&lt;=C4,"PASS","FAIL")</f>
+        <f>MAX(D4:AG4)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>IF(B4=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D4" s="13">
+        <f>MAX(0,ABS(Statements!C12-(Statements!C10-Statements!C11))-MAX(0.01,0.001*ABS(Statements!C12)))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>ABS(Statements!C12-(Statements!C10-Statements!C11))</f>
+        <f>MAX(0,ABS(Statements!D12-(Statements!D10-Statements!D11))-MAX(0.01,0.001*ABS(Statements!D12)))</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>ABS(Statements!D12-(Statements!D10-Statements!D11))</f>
+        <f>MAX(0,ABS(Statements!E12-(Statements!E10-Statements!E11))-MAX(0.01,0.001*ABS(Statements!E12)))</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>ABS(Statements!E12-(Statements!E10-Statements!E11))</f>
+        <f>MAX(0,ABS(Statements!F12-(Statements!F10-Statements!F11))-MAX(0.01,0.001*ABS(Statements!F12)))</f>
         <v/>
       </c>
       <c r="H4" s="13">
-        <f>ABS(Statements!F12-(Statements!F10-Statements!F11))</f>
+        <f>MAX(0,ABS(Statements!G12-(Statements!G10-Statements!G11))-MAX(0.01,0.001*ABS(Statements!G12)))</f>
         <v/>
       </c>
       <c r="I4" s="13">
-        <f>ABS(Statements!G12-(Statements!G10-Statements!G11))</f>
+        <f>MAX(0,ABS(Statements!H12-(Statements!H10-Statements!H11))-MAX(0.01,0.001*ABS(Statements!H12)))</f>
         <v/>
       </c>
       <c r="J4" s="13">
-        <f>ABS(Statements!H12-(Statements!H10-Statements!H11))</f>
+        <f>MAX(0,ABS(Statements!I12-(Statements!I10-Statements!I11))-MAX(0.01,0.001*ABS(Statements!I12)))</f>
         <v/>
       </c>
       <c r="K4" s="13">
-        <f>ABS(Statements!I12-(Statements!I10-Statements!I11))</f>
+        <f>MAX(0,ABS(Statements!J12-(Statements!J10-Statements!J11))-MAX(0.01,0.001*ABS(Statements!J12)))</f>
         <v/>
       </c>
       <c r="L4" s="13">
-        <f>ABS(Statements!J12-(Statements!J10-Statements!J11))</f>
+        <f>MAX(0,ABS(Statements!K12-(Statements!K10-Statements!K11))-MAX(0.01,0.001*ABS(Statements!K12)))</f>
         <v/>
       </c>
       <c r="M4" s="13">
-        <f>ABS(Statements!K12-(Statements!K10-Statements!K11))</f>
+        <f>MAX(0,ABS(Statements!L12-(Statements!L10-Statements!L11))-MAX(0.01,0.001*ABS(Statements!L12)))</f>
         <v/>
       </c>
       <c r="N4" s="13">
-        <f>ABS(Statements!L12-(Statements!L10-Statements!L11))</f>
+        <f>MAX(0,ABS(Statements!M12-(Statements!M10-Statements!M11))-MAX(0.01,0.001*ABS(Statements!M12)))</f>
         <v/>
       </c>
       <c r="O4" s="13">
-        <f>ABS(Statements!M12-(Statements!M10-Statements!M11))</f>
+        <f>MAX(0,ABS(Statements!N12-(Statements!N10-Statements!N11))-MAX(0.01,0.001*ABS(Statements!N12)))</f>
         <v/>
       </c>
       <c r="P4" s="13">
-        <f>ABS(Statements!N12-(Statements!N10-Statements!N11))</f>
+        <f>MAX(0,ABS(Statements!O12-(Statements!O10-Statements!O11))-MAX(0.01,0.001*ABS(Statements!O12)))</f>
         <v/>
       </c>
       <c r="Q4" s="13">
-        <f>ABS(Statements!O12-(Statements!O10-Statements!O11))</f>
+        <f>MAX(0,ABS(Statements!P12-(Statements!P10-Statements!P11))-MAX(0.01,0.001*ABS(Statements!P12)))</f>
         <v/>
       </c>
       <c r="R4" s="13">
-        <f>ABS(Statements!P12-(Statements!P10-Statements!P11))</f>
+        <f>MAX(0,ABS(Statements!Q12-(Statements!Q10-Statements!Q11))-MAX(0.01,0.001*ABS(Statements!Q12)))</f>
         <v/>
       </c>
       <c r="S4" s="13">
-        <f>ABS(Statements!Q12-(Statements!Q10-Statements!Q11))</f>
+        <f>MAX(0,ABS(Statements!R12-(Statements!R10-Statements!R11))-MAX(0.01,0.001*ABS(Statements!R12)))</f>
         <v/>
       </c>
       <c r="T4" s="13">
-        <f>ABS(Statements!R12-(Statements!R10-Statements!R11))</f>
+        <f>MAX(0,ABS(Statements!S12-(Statements!S10-Statements!S11))-MAX(0.01,0.001*ABS(Statements!S12)))</f>
         <v/>
       </c>
       <c r="U4" s="13">
-        <f>ABS(Statements!S12-(Statements!S10-Statements!S11))</f>
+        <f>MAX(0,ABS(Statements!T12-(Statements!T10-Statements!T11))-MAX(0.01,0.001*ABS(Statements!T12)))</f>
         <v/>
       </c>
       <c r="V4" s="13">
-        <f>ABS(Statements!T12-(Statements!T10-Statements!T11))</f>
+        <f>MAX(0,ABS(Statements!U12-(Statements!U10-Statements!U11))-MAX(0.01,0.001*ABS(Statements!U12)))</f>
         <v/>
       </c>
       <c r="W4" s="13">
-        <f>ABS(Statements!U12-(Statements!U10-Statements!U11))</f>
+        <f>MAX(0,ABS(Statements!V12-(Statements!V10-Statements!V11))-MAX(0.01,0.001*ABS(Statements!V12)))</f>
         <v/>
       </c>
       <c r="X4" s="13">
-        <f>ABS(Statements!V12-(Statements!V10-Statements!V11))</f>
+        <f>MAX(0,ABS(Statements!W12-(Statements!W10-Statements!W11))-MAX(0.01,0.001*ABS(Statements!W12)))</f>
         <v/>
       </c>
       <c r="Y4" s="13">
-        <f>ABS(Statements!W12-(Statements!W10-Statements!W11))</f>
+        <f>MAX(0,ABS(Statements!X12-(Statements!X10-Statements!X11))-MAX(0.01,0.001*ABS(Statements!X12)))</f>
         <v/>
       </c>
       <c r="Z4" s="13">
-        <f>ABS(Statements!X12-(Statements!X10-Statements!X11))</f>
+        <f>MAX(0,ABS(Statements!Y12-(Statements!Y10-Statements!Y11))-MAX(0.01,0.001*ABS(Statements!Y12)))</f>
         <v/>
       </c>
       <c r="AA4" s="13">
-        <f>ABS(Statements!Y12-(Statements!Y10-Statements!Y11))</f>
+        <f>MAX(0,ABS(Statements!Z12-(Statements!Z10-Statements!Z11))-MAX(0.01,0.001*ABS(Statements!Z12)))</f>
         <v/>
       </c>
       <c r="AB4" s="13">
-        <f>ABS(Statements!Z12-(Statements!Z10-Statements!Z11))</f>
+        <f>MAX(0,ABS(Statements!AA12-(Statements!AA10-Statements!AA11))-MAX(0.01,0.001*ABS(Statements!AA12)))</f>
         <v/>
       </c>
       <c r="AC4" s="13">
-        <f>ABS(Statements!AA12-(Statements!AA10-Statements!AA11))</f>
+        <f>MAX(0,ABS(Statements!AB12-(Statements!AB10-Statements!AB11))-MAX(0.01,0.001*ABS(Statements!AB12)))</f>
         <v/>
       </c>
       <c r="AD4" s="13">
-        <f>ABS(Statements!AB12-(Statements!AB10-Statements!AB11))</f>
+        <f>MAX(0,ABS(Statements!AC12-(Statements!AC10-Statements!AC11))-MAX(0.01,0.001*ABS(Statements!AC12)))</f>
         <v/>
       </c>
       <c r="AE4" s="13">
-        <f>ABS(Statements!AC12-(Statements!AC10-Statements!AC11))</f>
+        <f>MAX(0,ABS(Statements!AD12-(Statements!AD10-Statements!AD11))-MAX(0.01,0.001*ABS(Statements!AD12)))</f>
         <v/>
       </c>
       <c r="AF4" s="13">
-        <f>ABS(Statements!AD12-(Statements!AD10-Statements!AD11))</f>
+        <f>MAX(0,ABS(Statements!AE12-(Statements!AE10-Statements!AE11))-MAX(0.01,0.001*ABS(Statements!AE12)))</f>
         <v/>
       </c>
       <c r="AG4" s="13">
-        <f>ABS(Statements!AE12-(Statements!AE10-Statements!AE11))</f>
-        <v/>
-      </c>
-      <c r="AH4" s="13">
-        <f>ABS(Statements!AF12-(Statements!AF10-Statements!AF11))</f>
+        <f>MAX(0,ABS(Statements!AF12-(Statements!AF10-Statements!AF11))-MAX(0.01,0.001*ABS(Statements!AF12)))</f>
         <v/>
       </c>
     </row>
@@ -4622,134 +4607,131 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>MAX(E5:AH5)</f>
-        <v/>
-      </c>
-      <c r="C5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D5">
-        <f>IF(B5&lt;=C5,"PASS","FAIL")</f>
+        <f>MAX(D5:AG5)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>IF(B5=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D5" s="13">
+        <f>MAX(0,ABS(Statements!C14-(Statements!C12-Statements!C13))-MAX(0.01,0.001*ABS(Statements!C14)))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>ABS(Statements!C14-(Statements!C12-Statements!C13))</f>
+        <f>MAX(0,ABS(Statements!D14-(Statements!D12-Statements!D13))-MAX(0.01,0.001*ABS(Statements!D14)))</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>ABS(Statements!D14-(Statements!D12-Statements!D13))</f>
+        <f>MAX(0,ABS(Statements!E14-(Statements!E12-Statements!E13))-MAX(0.01,0.001*ABS(Statements!E14)))</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>ABS(Statements!E14-(Statements!E12-Statements!E13))</f>
+        <f>MAX(0,ABS(Statements!F14-(Statements!F12-Statements!F13))-MAX(0.01,0.001*ABS(Statements!F14)))</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>ABS(Statements!F14-(Statements!F12-Statements!F13))</f>
+        <f>MAX(0,ABS(Statements!G14-(Statements!G12-Statements!G13))-MAX(0.01,0.001*ABS(Statements!G14)))</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>ABS(Statements!G14-(Statements!G12-Statements!G13))</f>
+        <f>MAX(0,ABS(Statements!H14-(Statements!H12-Statements!H13))-MAX(0.01,0.001*ABS(Statements!H14)))</f>
         <v/>
       </c>
       <c r="J5" s="13">
-        <f>ABS(Statements!H14-(Statements!H12-Statements!H13))</f>
+        <f>MAX(0,ABS(Statements!I14-(Statements!I12-Statements!I13))-MAX(0.01,0.001*ABS(Statements!I14)))</f>
         <v/>
       </c>
       <c r="K5" s="13">
-        <f>ABS(Statements!I14-(Statements!I12-Statements!I13))</f>
+        <f>MAX(0,ABS(Statements!J14-(Statements!J12-Statements!J13))-MAX(0.01,0.001*ABS(Statements!J14)))</f>
         <v/>
       </c>
       <c r="L5" s="13">
-        <f>ABS(Statements!J14-(Statements!J12-Statements!J13))</f>
+        <f>MAX(0,ABS(Statements!K14-(Statements!K12-Statements!K13))-MAX(0.01,0.001*ABS(Statements!K14)))</f>
         <v/>
       </c>
       <c r="M5" s="13">
-        <f>ABS(Statements!K14-(Statements!K12-Statements!K13))</f>
+        <f>MAX(0,ABS(Statements!L14-(Statements!L12-Statements!L13))-MAX(0.01,0.001*ABS(Statements!L14)))</f>
         <v/>
       </c>
       <c r="N5" s="13">
-        <f>ABS(Statements!L14-(Statements!L12-Statements!L13))</f>
+        <f>MAX(0,ABS(Statements!M14-(Statements!M12-Statements!M13))-MAX(0.01,0.001*ABS(Statements!M14)))</f>
         <v/>
       </c>
       <c r="O5" s="13">
-        <f>ABS(Statements!M14-(Statements!M12-Statements!M13))</f>
+        <f>MAX(0,ABS(Statements!N14-(Statements!N12-Statements!N13))-MAX(0.01,0.001*ABS(Statements!N14)))</f>
         <v/>
       </c>
       <c r="P5" s="13">
-        <f>ABS(Statements!N14-(Statements!N12-Statements!N13))</f>
+        <f>MAX(0,ABS(Statements!O14-(Statements!O12-Statements!O13))-MAX(0.01,0.001*ABS(Statements!O14)))</f>
         <v/>
       </c>
       <c r="Q5" s="13">
-        <f>ABS(Statements!O14-(Statements!O12-Statements!O13))</f>
+        <f>MAX(0,ABS(Statements!P14-(Statements!P12-Statements!P13))-MAX(0.01,0.001*ABS(Statements!P14)))</f>
         <v/>
       </c>
       <c r="R5" s="13">
-        <f>ABS(Statements!P14-(Statements!P12-Statements!P13))</f>
+        <f>MAX(0,ABS(Statements!Q14-(Statements!Q12-Statements!Q13))-MAX(0.01,0.001*ABS(Statements!Q14)))</f>
         <v/>
       </c>
       <c r="S5" s="13">
-        <f>ABS(Statements!Q14-(Statements!Q12-Statements!Q13))</f>
+        <f>MAX(0,ABS(Statements!R14-(Statements!R12-Statements!R13))-MAX(0.01,0.001*ABS(Statements!R14)))</f>
         <v/>
       </c>
       <c r="T5" s="13">
-        <f>ABS(Statements!R14-(Statements!R12-Statements!R13))</f>
+        <f>MAX(0,ABS(Statements!S14-(Statements!S12-Statements!S13))-MAX(0.01,0.001*ABS(Statements!S14)))</f>
         <v/>
       </c>
       <c r="U5" s="13">
-        <f>ABS(Statements!S14-(Statements!S12-Statements!S13))</f>
+        <f>MAX(0,ABS(Statements!T14-(Statements!T12-Statements!T13))-MAX(0.01,0.001*ABS(Statements!T14)))</f>
         <v/>
       </c>
       <c r="V5" s="13">
-        <f>ABS(Statements!T14-(Statements!T12-Statements!T13))</f>
+        <f>MAX(0,ABS(Statements!U14-(Statements!U12-Statements!U13))-MAX(0.01,0.001*ABS(Statements!U14)))</f>
         <v/>
       </c>
       <c r="W5" s="13">
-        <f>ABS(Statements!U14-(Statements!U12-Statements!U13))</f>
+        <f>MAX(0,ABS(Statements!V14-(Statements!V12-Statements!V13))-MAX(0.01,0.001*ABS(Statements!V14)))</f>
         <v/>
       </c>
       <c r="X5" s="13">
-        <f>ABS(Statements!V14-(Statements!V12-Statements!V13))</f>
+        <f>MAX(0,ABS(Statements!W14-(Statements!W12-Statements!W13))-MAX(0.01,0.001*ABS(Statements!W14)))</f>
         <v/>
       </c>
       <c r="Y5" s="13">
-        <f>ABS(Statements!W14-(Statements!W12-Statements!W13))</f>
+        <f>MAX(0,ABS(Statements!X14-(Statements!X12-Statements!X13))-MAX(0.01,0.001*ABS(Statements!X14)))</f>
         <v/>
       </c>
       <c r="Z5" s="13">
-        <f>ABS(Statements!X14-(Statements!X12-Statements!X13))</f>
+        <f>MAX(0,ABS(Statements!Y14-(Statements!Y12-Statements!Y13))-MAX(0.01,0.001*ABS(Statements!Y14)))</f>
         <v/>
       </c>
       <c r="AA5" s="13">
-        <f>ABS(Statements!Y14-(Statements!Y12-Statements!Y13))</f>
+        <f>MAX(0,ABS(Statements!Z14-(Statements!Z12-Statements!Z13))-MAX(0.01,0.001*ABS(Statements!Z14)))</f>
         <v/>
       </c>
       <c r="AB5" s="13">
-        <f>ABS(Statements!Z14-(Statements!Z12-Statements!Z13))</f>
+        <f>MAX(0,ABS(Statements!AA14-(Statements!AA12-Statements!AA13))-MAX(0.01,0.001*ABS(Statements!AA14)))</f>
         <v/>
       </c>
       <c r="AC5" s="13">
-        <f>ABS(Statements!AA14-(Statements!AA12-Statements!AA13))</f>
+        <f>MAX(0,ABS(Statements!AB14-(Statements!AB12-Statements!AB13))-MAX(0.01,0.001*ABS(Statements!AB14)))</f>
         <v/>
       </c>
       <c r="AD5" s="13">
-        <f>ABS(Statements!AB14-(Statements!AB12-Statements!AB13))</f>
+        <f>MAX(0,ABS(Statements!AC14-(Statements!AC12-Statements!AC13))-MAX(0.01,0.001*ABS(Statements!AC14)))</f>
         <v/>
       </c>
       <c r="AE5" s="13">
-        <f>ABS(Statements!AC14-(Statements!AC12-Statements!AC13))</f>
+        <f>MAX(0,ABS(Statements!AD14-(Statements!AD12-Statements!AD13))-MAX(0.01,0.001*ABS(Statements!AD14)))</f>
         <v/>
       </c>
       <c r="AF5" s="13">
-        <f>ABS(Statements!AD14-(Statements!AD12-Statements!AD13))</f>
+        <f>MAX(0,ABS(Statements!AE14-(Statements!AE12-Statements!AE13))-MAX(0.01,0.001*ABS(Statements!AE14)))</f>
         <v/>
       </c>
       <c r="AG5" s="13">
-        <f>ABS(Statements!AE14-(Statements!AE12-Statements!AE13))</f>
-        <v/>
-      </c>
-      <c r="AH5" s="13">
-        <f>ABS(Statements!AF14-(Statements!AF12-Statements!AF13))</f>
+        <f>MAX(0,ABS(Statements!AF14-(Statements!AF12-Statements!AF13))-MAX(0.01,0.001*ABS(Statements!AF14)))</f>
         <v/>
       </c>
     </row>
@@ -4760,134 +4742,131 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>MAX(E6:AH6)</f>
-        <v/>
-      </c>
-      <c r="C6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D6">
-        <f>IF(B6&lt;=C6,"PASS","FAIL")</f>
+        <f>MAX(D6:AG6)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>IF(B6=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D6" s="13">
+        <f>MAX(0,ABS(Statements!C6-Statements!C3*1000*Statements!C4/1000000)-MAX(0.01,0.001*ABS(Statements!C6)))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>ABS(Statements!C6-Statements!C3*1000*Statements!C4/1000000)</f>
+        <f>MAX(0,ABS(Statements!D6-Statements!D3*1000*Statements!D4/1000000)-MAX(0.01,0.001*ABS(Statements!D6)))</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>ABS(Statements!D6-Statements!D3*1000*Statements!D4/1000000)</f>
+        <f>MAX(0,ABS(Statements!E6-Statements!E3*1000*Statements!E4/1000000)-MAX(0.01,0.001*ABS(Statements!E6)))</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>ABS(Statements!E6-Statements!E3*1000*Statements!E4/1000000)</f>
+        <f>MAX(0,ABS(Statements!F6-Statements!F3*1000*Statements!F4/1000000)-MAX(0.01,0.001*ABS(Statements!F6)))</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>ABS(Statements!F6-Statements!F3*1000*Statements!F4/1000000)</f>
+        <f>MAX(0,ABS(Statements!G6-Statements!G3*1000*Statements!G4/1000000)-MAX(0.01,0.001*ABS(Statements!G6)))</f>
         <v/>
       </c>
       <c r="I6" s="13">
-        <f>ABS(Statements!G6-Statements!G3*1000*Statements!G4/1000000)</f>
+        <f>MAX(0,ABS(Statements!H6-Statements!H3*1000*Statements!H4/1000000)-MAX(0.01,0.001*ABS(Statements!H6)))</f>
         <v/>
       </c>
       <c r="J6" s="13">
-        <f>ABS(Statements!H6-Statements!H3*1000*Statements!H4/1000000)</f>
+        <f>MAX(0,ABS(Statements!I6-Statements!I3*1000*Statements!I4/1000000)-MAX(0.01,0.001*ABS(Statements!I6)))</f>
         <v/>
       </c>
       <c r="K6" s="13">
-        <f>ABS(Statements!I6-Statements!I3*1000*Statements!I4/1000000)</f>
+        <f>MAX(0,ABS(Statements!J6-Statements!J3*1000*Statements!J4/1000000)-MAX(0.01,0.001*ABS(Statements!J6)))</f>
         <v/>
       </c>
       <c r="L6" s="13">
-        <f>ABS(Statements!J6-Statements!J3*1000*Statements!J4/1000000)</f>
+        <f>MAX(0,ABS(Statements!K6-Statements!K3*1000*Statements!K4/1000000)-MAX(0.01,0.001*ABS(Statements!K6)))</f>
         <v/>
       </c>
       <c r="M6" s="13">
-        <f>ABS(Statements!K6-Statements!K3*1000*Statements!K4/1000000)</f>
+        <f>MAX(0,ABS(Statements!L6-Statements!L3*1000*Statements!L4/1000000)-MAX(0.01,0.001*ABS(Statements!L6)))</f>
         <v/>
       </c>
       <c r="N6" s="13">
-        <f>ABS(Statements!L6-Statements!L3*1000*Statements!L4/1000000)</f>
+        <f>MAX(0,ABS(Statements!M6-Statements!M3*1000*Statements!M4/1000000)-MAX(0.01,0.001*ABS(Statements!M6)))</f>
         <v/>
       </c>
       <c r="O6" s="13">
-        <f>ABS(Statements!M6-Statements!M3*1000*Statements!M4/1000000)</f>
+        <f>MAX(0,ABS(Statements!N6-Statements!N3*1000*Statements!N4/1000000)-MAX(0.01,0.001*ABS(Statements!N6)))</f>
         <v/>
       </c>
       <c r="P6" s="13">
-        <f>ABS(Statements!N6-Statements!N3*1000*Statements!N4/1000000)</f>
+        <f>MAX(0,ABS(Statements!O6-Statements!O3*1000*Statements!O4/1000000)-MAX(0.01,0.001*ABS(Statements!O6)))</f>
         <v/>
       </c>
       <c r="Q6" s="13">
-        <f>ABS(Statements!O6-Statements!O3*1000*Statements!O4/1000000)</f>
+        <f>MAX(0,ABS(Statements!P6-Statements!P3*1000*Statements!P4/1000000)-MAX(0.01,0.001*ABS(Statements!P6)))</f>
         <v/>
       </c>
       <c r="R6" s="13">
-        <f>ABS(Statements!P6-Statements!P3*1000*Statements!P4/1000000)</f>
+        <f>MAX(0,ABS(Statements!Q6-Statements!Q3*1000*Statements!Q4/1000000)-MAX(0.01,0.001*ABS(Statements!Q6)))</f>
         <v/>
       </c>
       <c r="S6" s="13">
-        <f>ABS(Statements!Q6-Statements!Q3*1000*Statements!Q4/1000000)</f>
+        <f>MAX(0,ABS(Statements!R6-Statements!R3*1000*Statements!R4/1000000)-MAX(0.01,0.001*ABS(Statements!R6)))</f>
         <v/>
       </c>
       <c r="T6" s="13">
-        <f>ABS(Statements!R6-Statements!R3*1000*Statements!R4/1000000)</f>
+        <f>MAX(0,ABS(Statements!S6-Statements!S3*1000*Statements!S4/1000000)-MAX(0.01,0.001*ABS(Statements!S6)))</f>
         <v/>
       </c>
       <c r="U6" s="13">
-        <f>ABS(Statements!S6-Statements!S3*1000*Statements!S4/1000000)</f>
+        <f>MAX(0,ABS(Statements!T6-Statements!T3*1000*Statements!T4/1000000)-MAX(0.01,0.001*ABS(Statements!T6)))</f>
         <v/>
       </c>
       <c r="V6" s="13">
-        <f>ABS(Statements!T6-Statements!T3*1000*Statements!T4/1000000)</f>
+        <f>MAX(0,ABS(Statements!U6-Statements!U3*1000*Statements!U4/1000000)-MAX(0.01,0.001*ABS(Statements!U6)))</f>
         <v/>
       </c>
       <c r="W6" s="13">
-        <f>ABS(Statements!U6-Statements!U3*1000*Statements!U4/1000000)</f>
+        <f>MAX(0,ABS(Statements!V6-Statements!V3*1000*Statements!V4/1000000)-MAX(0.01,0.001*ABS(Statements!V6)))</f>
         <v/>
       </c>
       <c r="X6" s="13">
-        <f>ABS(Statements!V6-Statements!V3*1000*Statements!V4/1000000)</f>
+        <f>MAX(0,ABS(Statements!W6-Statements!W3*1000*Statements!W4/1000000)-MAX(0.01,0.001*ABS(Statements!W6)))</f>
         <v/>
       </c>
       <c r="Y6" s="13">
-        <f>ABS(Statements!W6-Statements!W3*1000*Statements!W4/1000000)</f>
+        <f>MAX(0,ABS(Statements!X6-Statements!X3*1000*Statements!X4/1000000)-MAX(0.01,0.001*ABS(Statements!X6)))</f>
         <v/>
       </c>
       <c r="Z6" s="13">
-        <f>ABS(Statements!X6-Statements!X3*1000*Statements!X4/1000000)</f>
+        <f>MAX(0,ABS(Statements!Y6-Statements!Y3*1000*Statements!Y4/1000000)-MAX(0.01,0.001*ABS(Statements!Y6)))</f>
         <v/>
       </c>
       <c r="AA6" s="13">
-        <f>ABS(Statements!Y6-Statements!Y3*1000*Statements!Y4/1000000)</f>
+        <f>MAX(0,ABS(Statements!Z6-Statements!Z3*1000*Statements!Z4/1000000)-MAX(0.01,0.001*ABS(Statements!Z6)))</f>
         <v/>
       </c>
       <c r="AB6" s="13">
-        <f>ABS(Statements!Z6-Statements!Z3*1000*Statements!Z4/1000000)</f>
+        <f>MAX(0,ABS(Statements!AA6-Statements!AA3*1000*Statements!AA4/1000000)-MAX(0.01,0.001*ABS(Statements!AA6)))</f>
         <v/>
       </c>
       <c r="AC6" s="13">
-        <f>ABS(Statements!AA6-Statements!AA3*1000*Statements!AA4/1000000)</f>
+        <f>MAX(0,ABS(Statements!AB6-Statements!AB3*1000*Statements!AB4/1000000)-MAX(0.01,0.001*ABS(Statements!AB6)))</f>
         <v/>
       </c>
       <c r="AD6" s="13">
-        <f>ABS(Statements!AB6-Statements!AB3*1000*Statements!AB4/1000000)</f>
+        <f>MAX(0,ABS(Statements!AC6-Statements!AC3*1000*Statements!AC4/1000000)-MAX(0.01,0.001*ABS(Statements!AC6)))</f>
         <v/>
       </c>
       <c r="AE6" s="13">
-        <f>ABS(Statements!AC6-Statements!AC3*1000*Statements!AC4/1000000)</f>
+        <f>MAX(0,ABS(Statements!AD6-Statements!AD3*1000*Statements!AD4/1000000)-MAX(0.01,0.001*ABS(Statements!AD6)))</f>
         <v/>
       </c>
       <c r="AF6" s="13">
-        <f>ABS(Statements!AD6-Statements!AD3*1000*Statements!AD4/1000000)</f>
+        <f>MAX(0,ABS(Statements!AE6-Statements!AE3*1000*Statements!AE4/1000000)-MAX(0.01,0.001*ABS(Statements!AE6)))</f>
         <v/>
       </c>
       <c r="AG6" s="13">
-        <f>ABS(Statements!AE6-Statements!AE3*1000*Statements!AE4/1000000)</f>
-        <v/>
-      </c>
-      <c r="AH6" s="13">
-        <f>ABS(Statements!AF6-Statements!AF3*1000*Statements!AF4/1000000)</f>
+        <f>MAX(0,ABS(Statements!AF6-Statements!AF3*1000*Statements!AF4/1000000)-MAX(0.01,0.001*ABS(Statements!AF6)))</f>
         <v/>
       </c>
     </row>
@@ -4898,134 +4877,131 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>MAX(E7:AH7)</f>
-        <v/>
-      </c>
-      <c r="C7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D7">
-        <f>IF(B7&lt;=C7,"PASS","FAIL")</f>
+        <f>MAX(D7:AG7)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>IF(B7=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D7" s="13">
+        <f>MAX(0,ABS(Statements!C22-(Statements!C8-Statements!C16-Statements!C17-Statements!C18-Statements!C19+Statements!C20))-MAX(0.01,0.001*ABS(Statements!C22)))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>ABS(Statements!C22-(Statements!C8-Statements!C16-Statements!C17-Statements!C18-Statements!C19+Statements!C20))</f>
+        <f>MAX(0,ABS(Statements!D22-(Statements!D8-Statements!D16-Statements!D17-Statements!D18-Statements!D19+Statements!D20))-MAX(0.01,0.001*ABS(Statements!D22)))</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>ABS(Statements!D22-(Statements!D8-Statements!D16-Statements!D17-Statements!D18-Statements!D19+Statements!D20))</f>
+        <f>MAX(0,ABS(Statements!E22-(Statements!E8-Statements!E16-Statements!E17-Statements!E18-Statements!E19+Statements!E20))-MAX(0.01,0.001*ABS(Statements!E22)))</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>ABS(Statements!E22-(Statements!E8-Statements!E16-Statements!E17-Statements!E18-Statements!E19+Statements!E20))</f>
+        <f>MAX(0,ABS(Statements!F22-(Statements!F8-Statements!F16-Statements!F17-Statements!F18-Statements!F19+Statements!F20))-MAX(0.01,0.001*ABS(Statements!F22)))</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>ABS(Statements!F22-(Statements!F8-Statements!F16-Statements!F17-Statements!F18-Statements!F19+Statements!F20))</f>
+        <f>MAX(0,ABS(Statements!G22-(Statements!G8-Statements!G16-Statements!G17-Statements!G18-Statements!G19+Statements!G20))-MAX(0.01,0.001*ABS(Statements!G22)))</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>ABS(Statements!G22-(Statements!G8-Statements!G16-Statements!G17-Statements!G18-Statements!G19+Statements!G20))</f>
+        <f>MAX(0,ABS(Statements!H22-(Statements!H8-Statements!H16-Statements!H17-Statements!H18-Statements!H19+Statements!H20))-MAX(0.01,0.001*ABS(Statements!H22)))</f>
         <v/>
       </c>
       <c r="J7" s="13">
-        <f>ABS(Statements!H22-(Statements!H8-Statements!H16-Statements!H17-Statements!H18-Statements!H19+Statements!H20))</f>
+        <f>MAX(0,ABS(Statements!I22-(Statements!I8-Statements!I16-Statements!I17-Statements!I18-Statements!I19+Statements!I20))-MAX(0.01,0.001*ABS(Statements!I22)))</f>
         <v/>
       </c>
       <c r="K7" s="13">
-        <f>ABS(Statements!I22-(Statements!I8-Statements!I16-Statements!I17-Statements!I18-Statements!I19+Statements!I20))</f>
+        <f>MAX(0,ABS(Statements!J22-(Statements!J8-Statements!J16-Statements!J17-Statements!J18-Statements!J19+Statements!J20))-MAX(0.01,0.001*ABS(Statements!J22)))</f>
         <v/>
       </c>
       <c r="L7" s="13">
-        <f>ABS(Statements!J22-(Statements!J8-Statements!J16-Statements!J17-Statements!J18-Statements!J19+Statements!J20))</f>
+        <f>MAX(0,ABS(Statements!K22-(Statements!K8-Statements!K16-Statements!K17-Statements!K18-Statements!K19+Statements!K20))-MAX(0.01,0.001*ABS(Statements!K22)))</f>
         <v/>
       </c>
       <c r="M7" s="13">
-        <f>ABS(Statements!K22-(Statements!K8-Statements!K16-Statements!K17-Statements!K18-Statements!K19+Statements!K20))</f>
+        <f>MAX(0,ABS(Statements!L22-(Statements!L8-Statements!L16-Statements!L17-Statements!L18-Statements!L19+Statements!L20))-MAX(0.01,0.001*ABS(Statements!L22)))</f>
         <v/>
       </c>
       <c r="N7" s="13">
-        <f>ABS(Statements!L22-(Statements!L8-Statements!L16-Statements!L17-Statements!L18-Statements!L19+Statements!L20))</f>
+        <f>MAX(0,ABS(Statements!M22-(Statements!M8-Statements!M16-Statements!M17-Statements!M18-Statements!M19+Statements!M20))-MAX(0.01,0.001*ABS(Statements!M22)))</f>
         <v/>
       </c>
       <c r="O7" s="13">
-        <f>ABS(Statements!M22-(Statements!M8-Statements!M16-Statements!M17-Statements!M18-Statements!M19+Statements!M20))</f>
+        <f>MAX(0,ABS(Statements!N22-(Statements!N8-Statements!N16-Statements!N17-Statements!N18-Statements!N19+Statements!N20))-MAX(0.01,0.001*ABS(Statements!N22)))</f>
         <v/>
       </c>
       <c r="P7" s="13">
-        <f>ABS(Statements!N22-(Statements!N8-Statements!N16-Statements!N17-Statements!N18-Statements!N19+Statements!N20))</f>
+        <f>MAX(0,ABS(Statements!O22-(Statements!O8-Statements!O16-Statements!O17-Statements!O18-Statements!O19+Statements!O20))-MAX(0.01,0.001*ABS(Statements!O22)))</f>
         <v/>
       </c>
       <c r="Q7" s="13">
-        <f>ABS(Statements!O22-(Statements!O8-Statements!O16-Statements!O17-Statements!O18-Statements!O19+Statements!O20))</f>
+        <f>MAX(0,ABS(Statements!P22-(Statements!P8-Statements!P16-Statements!P17-Statements!P18-Statements!P19+Statements!P20))-MAX(0.01,0.001*ABS(Statements!P22)))</f>
         <v/>
       </c>
       <c r="R7" s="13">
-        <f>ABS(Statements!P22-(Statements!P8-Statements!P16-Statements!P17-Statements!P18-Statements!P19+Statements!P20))</f>
+        <f>MAX(0,ABS(Statements!Q22-(Statements!Q8-Statements!Q16-Statements!Q17-Statements!Q18-Statements!Q19+Statements!Q20))-MAX(0.01,0.001*ABS(Statements!Q22)))</f>
         <v/>
       </c>
       <c r="S7" s="13">
-        <f>ABS(Statements!Q22-(Statements!Q8-Statements!Q16-Statements!Q17-Statements!Q18-Statements!Q19+Statements!Q20))</f>
+        <f>MAX(0,ABS(Statements!R22-(Statements!R8-Statements!R16-Statements!R17-Statements!R18-Statements!R19+Statements!R20))-MAX(0.01,0.001*ABS(Statements!R22)))</f>
         <v/>
       </c>
       <c r="T7" s="13">
-        <f>ABS(Statements!R22-(Statements!R8-Statements!R16-Statements!R17-Statements!R18-Statements!R19+Statements!R20))</f>
+        <f>MAX(0,ABS(Statements!S22-(Statements!S8-Statements!S16-Statements!S17-Statements!S18-Statements!S19+Statements!S20))-MAX(0.01,0.001*ABS(Statements!S22)))</f>
         <v/>
       </c>
       <c r="U7" s="13">
-        <f>ABS(Statements!S22-(Statements!S8-Statements!S16-Statements!S17-Statements!S18-Statements!S19+Statements!S20))</f>
+        <f>MAX(0,ABS(Statements!T22-(Statements!T8-Statements!T16-Statements!T17-Statements!T18-Statements!T19+Statements!T20))-MAX(0.01,0.001*ABS(Statements!T22)))</f>
         <v/>
       </c>
       <c r="V7" s="13">
-        <f>ABS(Statements!T22-(Statements!T8-Statements!T16-Statements!T17-Statements!T18-Statements!T19+Statements!T20))</f>
+        <f>MAX(0,ABS(Statements!U22-(Statements!U8-Statements!U16-Statements!U17-Statements!U18-Statements!U19+Statements!U20))-MAX(0.01,0.001*ABS(Statements!U22)))</f>
         <v/>
       </c>
       <c r="W7" s="13">
-        <f>ABS(Statements!U22-(Statements!U8-Statements!U16-Statements!U17-Statements!U18-Statements!U19+Statements!U20))</f>
+        <f>MAX(0,ABS(Statements!V22-(Statements!V8-Statements!V16-Statements!V17-Statements!V18-Statements!V19+Statements!V20))-MAX(0.01,0.001*ABS(Statements!V22)))</f>
         <v/>
       </c>
       <c r="X7" s="13">
-        <f>ABS(Statements!V22-(Statements!V8-Statements!V16-Statements!V17-Statements!V18-Statements!V19+Statements!V20))</f>
+        <f>MAX(0,ABS(Statements!W22-(Statements!W8-Statements!W16-Statements!W17-Statements!W18-Statements!W19+Statements!W20))-MAX(0.01,0.001*ABS(Statements!W22)))</f>
         <v/>
       </c>
       <c r="Y7" s="13">
-        <f>ABS(Statements!W22-(Statements!W8-Statements!W16-Statements!W17-Statements!W18-Statements!W19+Statements!W20))</f>
+        <f>MAX(0,ABS(Statements!X22-(Statements!X8-Statements!X16-Statements!X17-Statements!X18-Statements!X19+Statements!X20))-MAX(0.01,0.001*ABS(Statements!X22)))</f>
         <v/>
       </c>
       <c r="Z7" s="13">
-        <f>ABS(Statements!X22-(Statements!X8-Statements!X16-Statements!X17-Statements!X18-Statements!X19+Statements!X20))</f>
+        <f>MAX(0,ABS(Statements!Y22-(Statements!Y8-Statements!Y16-Statements!Y17-Statements!Y18-Statements!Y19+Statements!Y20))-MAX(0.01,0.001*ABS(Statements!Y22)))</f>
         <v/>
       </c>
       <c r="AA7" s="13">
-        <f>ABS(Statements!Y22-(Statements!Y8-Statements!Y16-Statements!Y17-Statements!Y18-Statements!Y19+Statements!Y20))</f>
+        <f>MAX(0,ABS(Statements!Z22-(Statements!Z8-Statements!Z16-Statements!Z17-Statements!Z18-Statements!Z19+Statements!Z20))-MAX(0.01,0.001*ABS(Statements!Z22)))</f>
         <v/>
       </c>
       <c r="AB7" s="13">
-        <f>ABS(Statements!Z22-(Statements!Z8-Statements!Z16-Statements!Z17-Statements!Z18-Statements!Z19+Statements!Z20))</f>
+        <f>MAX(0,ABS(Statements!AA22-(Statements!AA8-Statements!AA16-Statements!AA17-Statements!AA18-Statements!AA19+Statements!AA20))-MAX(0.01,0.001*ABS(Statements!AA22)))</f>
         <v/>
       </c>
       <c r="AC7" s="13">
-        <f>ABS(Statements!AA22-(Statements!AA8-Statements!AA16-Statements!AA17-Statements!AA18-Statements!AA19+Statements!AA20))</f>
+        <f>MAX(0,ABS(Statements!AB22-(Statements!AB8-Statements!AB16-Statements!AB17-Statements!AB18-Statements!AB19+Statements!AB20))-MAX(0.01,0.001*ABS(Statements!AB22)))</f>
         <v/>
       </c>
       <c r="AD7" s="13">
-        <f>ABS(Statements!AB22-(Statements!AB8-Statements!AB16-Statements!AB17-Statements!AB18-Statements!AB19+Statements!AB20))</f>
+        <f>MAX(0,ABS(Statements!AC22-(Statements!AC8-Statements!AC16-Statements!AC17-Statements!AC18-Statements!AC19+Statements!AC20))-MAX(0.01,0.001*ABS(Statements!AC22)))</f>
         <v/>
       </c>
       <c r="AE7" s="13">
-        <f>ABS(Statements!AC22-(Statements!AC8-Statements!AC16-Statements!AC17-Statements!AC18-Statements!AC19+Statements!AC20))</f>
+        <f>MAX(0,ABS(Statements!AD22-(Statements!AD8-Statements!AD16-Statements!AD17-Statements!AD18-Statements!AD19+Statements!AD20))-MAX(0.01,0.001*ABS(Statements!AD22)))</f>
         <v/>
       </c>
       <c r="AF7" s="13">
-        <f>ABS(Statements!AD22-(Statements!AD8-Statements!AD16-Statements!AD17-Statements!AD18-Statements!AD19+Statements!AD20))</f>
+        <f>MAX(0,ABS(Statements!AE22-(Statements!AE8-Statements!AE16-Statements!AE17-Statements!AE18-Statements!AE19+Statements!AE20))-MAX(0.01,0.001*ABS(Statements!AE22)))</f>
         <v/>
       </c>
       <c r="AG7" s="13">
-        <f>ABS(Statements!AE22-(Statements!AE8-Statements!AE16-Statements!AE17-Statements!AE18-Statements!AE19+Statements!AE20))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="13">
-        <f>ABS(Statements!AF22-(Statements!AF8-Statements!AF16-Statements!AF17-Statements!AF18-Statements!AF19+Statements!AF20))</f>
+        <f>MAX(0,ABS(Statements!AF22-(Statements!AF8-Statements!AF16-Statements!AF17-Statements!AF18-Statements!AF19+Statements!AF20))-MAX(0.01,0.001*ABS(Statements!AF22)))</f>
         <v/>
       </c>
     </row>
@@ -5036,272 +5012,266 @@
         </is>
       </c>
       <c r="B8" s="13">
-        <f>MAX(E8:AH8)</f>
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D8">
-        <f>IF(B8&lt;=C8,"PASS","FAIL")</f>
+        <f>MAX(D8:AG8)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IF(B8=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
+        <f>MAX(0,ABS(Statements!C27-(Statements!C24-Statements!C26+Statements!C25))-MAX(0.01,0.001*ABS(Statements!C27)))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>ABS(Statements!C27-(Statements!C24-Statements!C26+Statements!C25))</f>
+        <f>MAX(0,ABS(Statements!D27-(Statements!D24-Statements!D26+Statements!D25))-MAX(0.01,0.001*ABS(Statements!D27)))</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>ABS(Statements!D27-(Statements!D24-Statements!D26+Statements!D25))</f>
+        <f>MAX(0,ABS(Statements!E27-(Statements!E24-Statements!E26+Statements!E25))-MAX(0.01,0.001*ABS(Statements!E27)))</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>ABS(Statements!E27-(Statements!E24-Statements!E26+Statements!E25))</f>
+        <f>MAX(0,ABS(Statements!F27-(Statements!F24-Statements!F26+Statements!F25))-MAX(0.01,0.001*ABS(Statements!F27)))</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>ABS(Statements!F27-(Statements!F24-Statements!F26+Statements!F25))</f>
+        <f>MAX(0,ABS(Statements!G27-(Statements!G24-Statements!G26+Statements!G25))-MAX(0.01,0.001*ABS(Statements!G27)))</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>ABS(Statements!G27-(Statements!G24-Statements!G26+Statements!G25))</f>
+        <f>MAX(0,ABS(Statements!H27-(Statements!H24-Statements!H26+Statements!H25))-MAX(0.01,0.001*ABS(Statements!H27)))</f>
         <v/>
       </c>
       <c r="J8" s="13">
-        <f>ABS(Statements!H27-(Statements!H24-Statements!H26+Statements!H25))</f>
+        <f>MAX(0,ABS(Statements!I27-(Statements!I24-Statements!I26+Statements!I25))-MAX(0.01,0.001*ABS(Statements!I27)))</f>
         <v/>
       </c>
       <c r="K8" s="13">
-        <f>ABS(Statements!I27-(Statements!I24-Statements!I26+Statements!I25))</f>
+        <f>MAX(0,ABS(Statements!J27-(Statements!J24-Statements!J26+Statements!J25))-MAX(0.01,0.001*ABS(Statements!J27)))</f>
         <v/>
       </c>
       <c r="L8" s="13">
-        <f>ABS(Statements!J27-(Statements!J24-Statements!J26+Statements!J25))</f>
+        <f>MAX(0,ABS(Statements!K27-(Statements!K24-Statements!K26+Statements!K25))-MAX(0.01,0.001*ABS(Statements!K27)))</f>
         <v/>
       </c>
       <c r="M8" s="13">
-        <f>ABS(Statements!K27-(Statements!K24-Statements!K26+Statements!K25))</f>
+        <f>MAX(0,ABS(Statements!L27-(Statements!L24-Statements!L26+Statements!L25))-MAX(0.01,0.001*ABS(Statements!L27)))</f>
         <v/>
       </c>
       <c r="N8" s="13">
-        <f>ABS(Statements!L27-(Statements!L24-Statements!L26+Statements!L25))</f>
+        <f>MAX(0,ABS(Statements!M27-(Statements!M24-Statements!M26+Statements!M25))-MAX(0.01,0.001*ABS(Statements!M27)))</f>
         <v/>
       </c>
       <c r="O8" s="13">
-        <f>ABS(Statements!M27-(Statements!M24-Statements!M26+Statements!M25))</f>
+        <f>MAX(0,ABS(Statements!N27-(Statements!N24-Statements!N26+Statements!N25))-MAX(0.01,0.001*ABS(Statements!N27)))</f>
         <v/>
       </c>
       <c r="P8" s="13">
-        <f>ABS(Statements!N27-(Statements!N24-Statements!N26+Statements!N25))</f>
+        <f>MAX(0,ABS(Statements!O27-(Statements!O24-Statements!O26+Statements!O25))-MAX(0.01,0.001*ABS(Statements!O27)))</f>
         <v/>
       </c>
       <c r="Q8" s="13">
-        <f>ABS(Statements!O27-(Statements!O24-Statements!O26+Statements!O25))</f>
+        <f>MAX(0,ABS(Statements!P27-(Statements!P24-Statements!P26+Statements!P25))-MAX(0.01,0.001*ABS(Statements!P27)))</f>
         <v/>
       </c>
       <c r="R8" s="13">
-        <f>ABS(Statements!P27-(Statements!P24-Statements!P26+Statements!P25))</f>
+        <f>MAX(0,ABS(Statements!Q27-(Statements!Q24-Statements!Q26+Statements!Q25))-MAX(0.01,0.001*ABS(Statements!Q27)))</f>
         <v/>
       </c>
       <c r="S8" s="13">
-        <f>ABS(Statements!Q27-(Statements!Q24-Statements!Q26+Statements!Q25))</f>
+        <f>MAX(0,ABS(Statements!R27-(Statements!R24-Statements!R26+Statements!R25))-MAX(0.01,0.001*ABS(Statements!R27)))</f>
         <v/>
       </c>
       <c r="T8" s="13">
-        <f>ABS(Statements!R27-(Statements!R24-Statements!R26+Statements!R25))</f>
+        <f>MAX(0,ABS(Statements!S27-(Statements!S24-Statements!S26+Statements!S25))-MAX(0.01,0.001*ABS(Statements!S27)))</f>
         <v/>
       </c>
       <c r="U8" s="13">
-        <f>ABS(Statements!S27-(Statements!S24-Statements!S26+Statements!S25))</f>
+        <f>MAX(0,ABS(Statements!T27-(Statements!T24-Statements!T26+Statements!T25))-MAX(0.01,0.001*ABS(Statements!T27)))</f>
         <v/>
       </c>
       <c r="V8" s="13">
-        <f>ABS(Statements!T27-(Statements!T24-Statements!T26+Statements!T25))</f>
+        <f>MAX(0,ABS(Statements!U27-(Statements!U24-Statements!U26+Statements!U25))-MAX(0.01,0.001*ABS(Statements!U27)))</f>
         <v/>
       </c>
       <c r="W8" s="13">
-        <f>ABS(Statements!U27-(Statements!U24-Statements!U26+Statements!U25))</f>
+        <f>MAX(0,ABS(Statements!V27-(Statements!V24-Statements!V26+Statements!V25))-MAX(0.01,0.001*ABS(Statements!V27)))</f>
         <v/>
       </c>
       <c r="X8" s="13">
-        <f>ABS(Statements!V27-(Statements!V24-Statements!V26+Statements!V25))</f>
+        <f>MAX(0,ABS(Statements!W27-(Statements!W24-Statements!W26+Statements!W25))-MAX(0.01,0.001*ABS(Statements!W27)))</f>
         <v/>
       </c>
       <c r="Y8" s="13">
-        <f>ABS(Statements!W27-(Statements!W24-Statements!W26+Statements!W25))</f>
+        <f>MAX(0,ABS(Statements!X27-(Statements!X24-Statements!X26+Statements!X25))-MAX(0.01,0.001*ABS(Statements!X27)))</f>
         <v/>
       </c>
       <c r="Z8" s="13">
-        <f>ABS(Statements!X27-(Statements!X24-Statements!X26+Statements!X25))</f>
+        <f>MAX(0,ABS(Statements!Y27-(Statements!Y24-Statements!Y26+Statements!Y25))-MAX(0.01,0.001*ABS(Statements!Y27)))</f>
         <v/>
       </c>
       <c r="AA8" s="13">
-        <f>ABS(Statements!Y27-(Statements!Y24-Statements!Y26+Statements!Y25))</f>
+        <f>MAX(0,ABS(Statements!Z27-(Statements!Z24-Statements!Z26+Statements!Z25))-MAX(0.01,0.001*ABS(Statements!Z27)))</f>
         <v/>
       </c>
       <c r="AB8" s="13">
-        <f>ABS(Statements!Z27-(Statements!Z24-Statements!Z26+Statements!Z25))</f>
+        <f>MAX(0,ABS(Statements!AA27-(Statements!AA24-Statements!AA26+Statements!AA25))-MAX(0.01,0.001*ABS(Statements!AA27)))</f>
         <v/>
       </c>
       <c r="AC8" s="13">
-        <f>ABS(Statements!AA27-(Statements!AA24-Statements!AA26+Statements!AA25))</f>
+        <f>MAX(0,ABS(Statements!AB27-(Statements!AB24-Statements!AB26+Statements!AB25))-MAX(0.01,0.001*ABS(Statements!AB27)))</f>
         <v/>
       </c>
       <c r="AD8" s="13">
-        <f>ABS(Statements!AB27-(Statements!AB24-Statements!AB26+Statements!AB25))</f>
+        <f>MAX(0,ABS(Statements!AC27-(Statements!AC24-Statements!AC26+Statements!AC25))-MAX(0.01,0.001*ABS(Statements!AC27)))</f>
         <v/>
       </c>
       <c r="AE8" s="13">
-        <f>ABS(Statements!AC27-(Statements!AC24-Statements!AC26+Statements!AC25))</f>
+        <f>MAX(0,ABS(Statements!AD27-(Statements!AD24-Statements!AD26+Statements!AD25))-MAX(0.01,0.001*ABS(Statements!AD27)))</f>
         <v/>
       </c>
       <c r="AF8" s="13">
-        <f>ABS(Statements!AD27-(Statements!AD24-Statements!AD26+Statements!AD25))</f>
+        <f>MAX(0,ABS(Statements!AE27-(Statements!AE24-Statements!AE26+Statements!AE25))-MAX(0.01,0.001*ABS(Statements!AE27)))</f>
         <v/>
       </c>
       <c r="AG8" s="13">
-        <f>ABS(Statements!AE27-(Statements!AE24-Statements!AE26+Statements!AE25))</f>
-        <v/>
-      </c>
-      <c r="AH8" s="13">
-        <f>ABS(Statements!AF27-(Statements!AF24-Statements!AF26+Statements!AF25))</f>
+        <f>MAX(0,ABS(Statements!AF27-(Statements!AF24-Statements!AF26+Statements!AF25))-MAX(0.01,0.001*ABS(Statements!AF27)))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>opening[t] = closing[t-1]</t>
+          <t>opening[t] = closing[t-1], and opening[0] = 0</t>
         </is>
       </c>
       <c r="B9" s="13">
-        <f>MAX(E9:AH9)</f>
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D9">
-        <f>IF(B9&lt;=C9,"PASS","FAIL")</f>
+        <f>MAX(D9:AG9)</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>IF(B9=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>MAX(0,ABS(Statements!C24)-MAX(0.01,0.001*ABS(0)))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>0</f>
+        <f>MAX(0,ABS(Statements!D24-Statements!C27)-MAX(0.01,0.001*ABS(Statements!D24)))</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>ABS(Statements!D24-Statements!C27)</f>
+        <f>MAX(0,ABS(Statements!E24-Statements!D27)-MAX(0.01,0.001*ABS(Statements!E24)))</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>ABS(Statements!E24-Statements!D27)</f>
+        <f>MAX(0,ABS(Statements!F24-Statements!E27)-MAX(0.01,0.001*ABS(Statements!F24)))</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>ABS(Statements!F24-Statements!E27)</f>
+        <f>MAX(0,ABS(Statements!G24-Statements!F27)-MAX(0.01,0.001*ABS(Statements!G24)))</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>ABS(Statements!G24-Statements!F27)</f>
+        <f>MAX(0,ABS(Statements!H24-Statements!G27)-MAX(0.01,0.001*ABS(Statements!H24)))</f>
         <v/>
       </c>
       <c r="J9" s="13">
-        <f>ABS(Statements!H24-Statements!G27)</f>
+        <f>MAX(0,ABS(Statements!I24-Statements!H27)-MAX(0.01,0.001*ABS(Statements!I24)))</f>
         <v/>
       </c>
       <c r="K9" s="13">
-        <f>ABS(Statements!I24-Statements!H27)</f>
+        <f>MAX(0,ABS(Statements!J24-Statements!I27)-MAX(0.01,0.001*ABS(Statements!J24)))</f>
         <v/>
       </c>
       <c r="L9" s="13">
-        <f>ABS(Statements!J24-Statements!I27)</f>
+        <f>MAX(0,ABS(Statements!K24-Statements!J27)-MAX(0.01,0.001*ABS(Statements!K24)))</f>
         <v/>
       </c>
       <c r="M9" s="13">
-        <f>ABS(Statements!K24-Statements!J27)</f>
+        <f>MAX(0,ABS(Statements!L24-Statements!K27)-MAX(0.01,0.001*ABS(Statements!L24)))</f>
         <v/>
       </c>
       <c r="N9" s="13">
-        <f>ABS(Statements!L24-Statements!K27)</f>
+        <f>MAX(0,ABS(Statements!M24-Statements!L27)-MAX(0.01,0.001*ABS(Statements!M24)))</f>
         <v/>
       </c>
       <c r="O9" s="13">
-        <f>ABS(Statements!M24-Statements!L27)</f>
+        <f>MAX(0,ABS(Statements!N24-Statements!M27)-MAX(0.01,0.001*ABS(Statements!N24)))</f>
         <v/>
       </c>
       <c r="P9" s="13">
-        <f>ABS(Statements!N24-Statements!M27)</f>
+        <f>MAX(0,ABS(Statements!O24-Statements!N27)-MAX(0.01,0.001*ABS(Statements!O24)))</f>
         <v/>
       </c>
       <c r="Q9" s="13">
-        <f>ABS(Statements!O24-Statements!N27)</f>
+        <f>MAX(0,ABS(Statements!P24-Statements!O27)-MAX(0.01,0.001*ABS(Statements!P24)))</f>
         <v/>
       </c>
       <c r="R9" s="13">
-        <f>ABS(Statements!P24-Statements!O27)</f>
+        <f>MAX(0,ABS(Statements!Q24-Statements!P27)-MAX(0.01,0.001*ABS(Statements!Q24)))</f>
         <v/>
       </c>
       <c r="S9" s="13">
-        <f>ABS(Statements!Q24-Statements!P27)</f>
+        <f>MAX(0,ABS(Statements!R24-Statements!Q27)-MAX(0.01,0.001*ABS(Statements!R24)))</f>
         <v/>
       </c>
       <c r="T9" s="13">
-        <f>ABS(Statements!R24-Statements!Q27)</f>
+        <f>MAX(0,ABS(Statements!S24-Statements!R27)-MAX(0.01,0.001*ABS(Statements!S24)))</f>
         <v/>
       </c>
       <c r="U9" s="13">
-        <f>ABS(Statements!S24-Statements!R27)</f>
+        <f>MAX(0,ABS(Statements!T24-Statements!S27)-MAX(0.01,0.001*ABS(Statements!T24)))</f>
         <v/>
       </c>
       <c r="V9" s="13">
-        <f>ABS(Statements!T24-Statements!S27)</f>
+        <f>MAX(0,ABS(Statements!U24-Statements!T27)-MAX(0.01,0.001*ABS(Statements!U24)))</f>
         <v/>
       </c>
       <c r="W9" s="13">
-        <f>ABS(Statements!U24-Statements!T27)</f>
+        <f>MAX(0,ABS(Statements!V24-Statements!U27)-MAX(0.01,0.001*ABS(Statements!V24)))</f>
         <v/>
       </c>
       <c r="X9" s="13">
-        <f>ABS(Statements!V24-Statements!U27)</f>
+        <f>MAX(0,ABS(Statements!W24-Statements!V27)-MAX(0.01,0.001*ABS(Statements!W24)))</f>
         <v/>
       </c>
       <c r="Y9" s="13">
-        <f>ABS(Statements!W24-Statements!V27)</f>
+        <f>MAX(0,ABS(Statements!X24-Statements!W27)-MAX(0.01,0.001*ABS(Statements!X24)))</f>
         <v/>
       </c>
       <c r="Z9" s="13">
-        <f>ABS(Statements!X24-Statements!W27)</f>
+        <f>MAX(0,ABS(Statements!Y24-Statements!X27)-MAX(0.01,0.001*ABS(Statements!Y24)))</f>
         <v/>
       </c>
       <c r="AA9" s="13">
-        <f>ABS(Statements!Y24-Statements!X27)</f>
+        <f>MAX(0,ABS(Statements!Z24-Statements!Y27)-MAX(0.01,0.001*ABS(Statements!Z24)))</f>
         <v/>
       </c>
       <c r="AB9" s="13">
-        <f>ABS(Statements!Z24-Statements!Y27)</f>
+        <f>MAX(0,ABS(Statements!AA24-Statements!Z27)-MAX(0.01,0.001*ABS(Statements!AA24)))</f>
         <v/>
       </c>
       <c r="AC9" s="13">
-        <f>ABS(Statements!AA24-Statements!Z27)</f>
+        <f>MAX(0,ABS(Statements!AB24-Statements!AA27)-MAX(0.01,0.001*ABS(Statements!AB24)))</f>
         <v/>
       </c>
       <c r="AD9" s="13">
-        <f>ABS(Statements!AB24-Statements!AA27)</f>
+        <f>MAX(0,ABS(Statements!AC24-Statements!AB27)-MAX(0.01,0.001*ABS(Statements!AC24)))</f>
         <v/>
       </c>
       <c r="AE9" s="13">
-        <f>ABS(Statements!AC24-Statements!AB27)</f>
+        <f>MAX(0,ABS(Statements!AD24-Statements!AC27)-MAX(0.01,0.001*ABS(Statements!AD24)))</f>
         <v/>
       </c>
       <c r="AF9" s="13">
-        <f>ABS(Statements!AD24-Statements!AC27)</f>
+        <f>MAX(0,ABS(Statements!AE24-Statements!AD27)-MAX(0.01,0.001*ABS(Statements!AE24)))</f>
         <v/>
       </c>
       <c r="AG9" s="13">
-        <f>ABS(Statements!AE24-Statements!AD27)</f>
-        <v/>
-      </c>
-      <c r="AH9" s="13">
-        <f>ABS(Statements!AF24-Statements!AE27)</f>
+        <f>MAX(0,ABS(Statements!AF24-Statements!AE27)-MAX(0.01,0.001*ABS(Statements!AF24)))</f>
         <v/>
       </c>
     </row>
@@ -5312,134 +5282,131 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>MAX(E10:AH10)</f>
-        <v/>
-      </c>
-      <c r="C10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D10">
-        <f>IF(B10&lt;=C10,"PASS","FAIL")</f>
+        <f>MAX(D10:AG10)</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>IF(B10=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>MAX(0,ABS(Statements!C29-(0-Statements!C9+Statements!C19))-MAX(0.01,0.001*ABS(Statements!C29)))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>ABS(Statements!C29-(0-Statements!C9+Statements!C19))</f>
+        <f>MAX(0,ABS(Statements!D29-(Statements!C29-Statements!D9+Statements!D19))-MAX(0.01,0.001*ABS(Statements!D29)))</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>ABS(Statements!D29-(Statements!C29-Statements!D9+Statements!D19))</f>
+        <f>MAX(0,ABS(Statements!E29-(Statements!D29-Statements!E9+Statements!E19))-MAX(0.01,0.001*ABS(Statements!E29)))</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>ABS(Statements!E29-(Statements!D29-Statements!E9+Statements!E19))</f>
+        <f>MAX(0,ABS(Statements!F29-(Statements!E29-Statements!F9+Statements!F19))-MAX(0.01,0.001*ABS(Statements!F29)))</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>ABS(Statements!F29-(Statements!E29-Statements!F9+Statements!F19))</f>
+        <f>MAX(0,ABS(Statements!G29-(Statements!F29-Statements!G9+Statements!G19))-MAX(0.01,0.001*ABS(Statements!G29)))</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>ABS(Statements!G29-(Statements!F29-Statements!G9+Statements!G19))</f>
+        <f>MAX(0,ABS(Statements!H29-(Statements!G29-Statements!H9+Statements!H19))-MAX(0.01,0.001*ABS(Statements!H29)))</f>
         <v/>
       </c>
       <c r="J10" s="13">
-        <f>ABS(Statements!H29-(Statements!G29-Statements!H9+Statements!H19))</f>
+        <f>MAX(0,ABS(Statements!I29-(Statements!H29-Statements!I9+Statements!I19))-MAX(0.01,0.001*ABS(Statements!I29)))</f>
         <v/>
       </c>
       <c r="K10" s="13">
-        <f>ABS(Statements!I29-(Statements!H29-Statements!I9+Statements!I19))</f>
+        <f>MAX(0,ABS(Statements!J29-(Statements!I29-Statements!J9+Statements!J19))-MAX(0.01,0.001*ABS(Statements!J29)))</f>
         <v/>
       </c>
       <c r="L10" s="13">
-        <f>ABS(Statements!J29-(Statements!I29-Statements!J9+Statements!J19))</f>
+        <f>MAX(0,ABS(Statements!K29-(Statements!J29-Statements!K9+Statements!K19))-MAX(0.01,0.001*ABS(Statements!K29)))</f>
         <v/>
       </c>
       <c r="M10" s="13">
-        <f>ABS(Statements!K29-(Statements!J29-Statements!K9+Statements!K19))</f>
+        <f>MAX(0,ABS(Statements!L29-(Statements!K29-Statements!L9+Statements!L19))-MAX(0.01,0.001*ABS(Statements!L29)))</f>
         <v/>
       </c>
       <c r="N10" s="13">
-        <f>ABS(Statements!L29-(Statements!K29-Statements!L9+Statements!L19))</f>
+        <f>MAX(0,ABS(Statements!M29-(Statements!L29-Statements!M9+Statements!M19))-MAX(0.01,0.001*ABS(Statements!M29)))</f>
         <v/>
       </c>
       <c r="O10" s="13">
-        <f>ABS(Statements!M29-(Statements!L29-Statements!M9+Statements!M19))</f>
+        <f>MAX(0,ABS(Statements!N29-(Statements!M29-Statements!N9+Statements!N19))-MAX(0.01,0.001*ABS(Statements!N29)))</f>
         <v/>
       </c>
       <c r="P10" s="13">
-        <f>ABS(Statements!N29-(Statements!M29-Statements!N9+Statements!N19))</f>
+        <f>MAX(0,ABS(Statements!O29-(Statements!N29-Statements!O9+Statements!O19))-MAX(0.01,0.001*ABS(Statements!O29)))</f>
         <v/>
       </c>
       <c r="Q10" s="13">
-        <f>ABS(Statements!O29-(Statements!N29-Statements!O9+Statements!O19))</f>
+        <f>MAX(0,ABS(Statements!P29-(Statements!O29-Statements!P9+Statements!P19))-MAX(0.01,0.001*ABS(Statements!P29)))</f>
         <v/>
       </c>
       <c r="R10" s="13">
-        <f>ABS(Statements!P29-(Statements!O29-Statements!P9+Statements!P19))</f>
+        <f>MAX(0,ABS(Statements!Q29-(Statements!P29-Statements!Q9+Statements!Q19))-MAX(0.01,0.001*ABS(Statements!Q29)))</f>
         <v/>
       </c>
       <c r="S10" s="13">
-        <f>ABS(Statements!Q29-(Statements!P29-Statements!Q9+Statements!Q19))</f>
+        <f>MAX(0,ABS(Statements!R29-(Statements!Q29-Statements!R9+Statements!R19))-MAX(0.01,0.001*ABS(Statements!R29)))</f>
         <v/>
       </c>
       <c r="T10" s="13">
-        <f>ABS(Statements!R29-(Statements!Q29-Statements!R9+Statements!R19))</f>
+        <f>MAX(0,ABS(Statements!S29-(Statements!R29-Statements!S9+Statements!S19))-MAX(0.01,0.001*ABS(Statements!S29)))</f>
         <v/>
       </c>
       <c r="U10" s="13">
-        <f>ABS(Statements!S29-(Statements!R29-Statements!S9+Statements!S19))</f>
+        <f>MAX(0,ABS(Statements!T29-(Statements!S29-Statements!T9+Statements!T19))-MAX(0.01,0.001*ABS(Statements!T29)))</f>
         <v/>
       </c>
       <c r="V10" s="13">
-        <f>ABS(Statements!T29-(Statements!S29-Statements!T9+Statements!T19))</f>
+        <f>MAX(0,ABS(Statements!U29-(Statements!T29-Statements!U9+Statements!U19))-MAX(0.01,0.001*ABS(Statements!U29)))</f>
         <v/>
       </c>
       <c r="W10" s="13">
-        <f>ABS(Statements!U29-(Statements!T29-Statements!U9+Statements!U19))</f>
+        <f>MAX(0,ABS(Statements!V29-(Statements!U29-Statements!V9+Statements!V19))-MAX(0.01,0.001*ABS(Statements!V29)))</f>
         <v/>
       </c>
       <c r="X10" s="13">
-        <f>ABS(Statements!V29-(Statements!U29-Statements!V9+Statements!V19))</f>
+        <f>MAX(0,ABS(Statements!W29-(Statements!V29-Statements!W9+Statements!W19))-MAX(0.01,0.001*ABS(Statements!W29)))</f>
         <v/>
       </c>
       <c r="Y10" s="13">
-        <f>ABS(Statements!W29-(Statements!V29-Statements!W9+Statements!W19))</f>
+        <f>MAX(0,ABS(Statements!X29-(Statements!W29-Statements!X9+Statements!X19))-MAX(0.01,0.001*ABS(Statements!X29)))</f>
         <v/>
       </c>
       <c r="Z10" s="13">
-        <f>ABS(Statements!X29-(Statements!W29-Statements!X9+Statements!X19))</f>
+        <f>MAX(0,ABS(Statements!Y29-(Statements!X29-Statements!Y9+Statements!Y19))-MAX(0.01,0.001*ABS(Statements!Y29)))</f>
         <v/>
       </c>
       <c r="AA10" s="13">
-        <f>ABS(Statements!Y29-(Statements!X29-Statements!Y9+Statements!Y19))</f>
+        <f>MAX(0,ABS(Statements!Z29-(Statements!Y29-Statements!Z9+Statements!Z19))-MAX(0.01,0.001*ABS(Statements!Z29)))</f>
         <v/>
       </c>
       <c r="AB10" s="13">
-        <f>ABS(Statements!Z29-(Statements!Y29-Statements!Z9+Statements!Z19))</f>
+        <f>MAX(0,ABS(Statements!AA29-(Statements!Z29-Statements!AA9+Statements!AA19))-MAX(0.01,0.001*ABS(Statements!AA29)))</f>
         <v/>
       </c>
       <c r="AC10" s="13">
-        <f>ABS(Statements!AA29-(Statements!Z29-Statements!AA9+Statements!AA19))</f>
+        <f>MAX(0,ABS(Statements!AB29-(Statements!AA29-Statements!AB9+Statements!AB19))-MAX(0.01,0.001*ABS(Statements!AB29)))</f>
         <v/>
       </c>
       <c r="AD10" s="13">
-        <f>ABS(Statements!AB29-(Statements!AA29-Statements!AB9+Statements!AB19))</f>
+        <f>MAX(0,ABS(Statements!AC29-(Statements!AB29-Statements!AC9+Statements!AC19))-MAX(0.01,0.001*ABS(Statements!AC29)))</f>
         <v/>
       </c>
       <c r="AE10" s="13">
-        <f>ABS(Statements!AC29-(Statements!AB29-Statements!AC9+Statements!AC19))</f>
+        <f>MAX(0,ABS(Statements!AD29-(Statements!AC29-Statements!AD9+Statements!AD19))-MAX(0.01,0.001*ABS(Statements!AD29)))</f>
         <v/>
       </c>
       <c r="AF10" s="13">
-        <f>ABS(Statements!AD29-(Statements!AC29-Statements!AD9+Statements!AD19))</f>
+        <f>MAX(0,ABS(Statements!AE29-(Statements!AD29-Statements!AE9+Statements!AE19))-MAX(0.01,0.001*ABS(Statements!AE29)))</f>
         <v/>
       </c>
       <c r="AG10" s="13">
-        <f>ABS(Statements!AE29-(Statements!AD29-Statements!AE9+Statements!AE19))</f>
-        <v/>
-      </c>
-      <c r="AH10" s="13">
-        <f>ABS(Statements!AF29-(Statements!AE29-Statements!AF9+Statements!AF19))</f>
+        <f>MAX(0,ABS(Statements!AF29-(Statements!AE29-Statements!AF9+Statements!AF19))-MAX(0.01,0.001*ABS(Statements!AF29)))</f>
         <v/>
       </c>
     </row>
@@ -5450,387 +5417,498 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <f>MAX(E11:AH11)</f>
-        <v/>
-      </c>
-      <c r="C11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D11">
-        <f>IF(B11&lt;=C11,"PASS","FAIL")</f>
+        <f>MAX(D11:AG11)</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>IF(B11=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
+        <f>MAX(0,ABS(Statements!C19-(Statements!C20+Statements!C21))-MAX(0.01,0.001*ABS(Statements!C19)))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>ABS(Statements!C19-(Statements!C20+Statements!C21))</f>
+        <f>MAX(0,ABS(Statements!D19-(Statements!D20+Statements!D21))-MAX(0.01,0.001*ABS(Statements!D19)))</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>ABS(Statements!D19-(Statements!D20+Statements!D21))</f>
+        <f>MAX(0,ABS(Statements!E19-(Statements!E20+Statements!E21))-MAX(0.01,0.001*ABS(Statements!E19)))</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>ABS(Statements!E19-(Statements!E20+Statements!E21))</f>
+        <f>MAX(0,ABS(Statements!F19-(Statements!F20+Statements!F21))-MAX(0.01,0.001*ABS(Statements!F19)))</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>ABS(Statements!F19-(Statements!F20+Statements!F21))</f>
+        <f>MAX(0,ABS(Statements!G19-(Statements!G20+Statements!G21))-MAX(0.01,0.001*ABS(Statements!G19)))</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>ABS(Statements!G19-(Statements!G20+Statements!G21))</f>
+        <f>MAX(0,ABS(Statements!H19-(Statements!H20+Statements!H21))-MAX(0.01,0.001*ABS(Statements!H19)))</f>
         <v/>
       </c>
       <c r="J11" s="13">
-        <f>ABS(Statements!H19-(Statements!H20+Statements!H21))</f>
+        <f>MAX(0,ABS(Statements!I19-(Statements!I20+Statements!I21))-MAX(0.01,0.001*ABS(Statements!I19)))</f>
         <v/>
       </c>
       <c r="K11" s="13">
-        <f>ABS(Statements!I19-(Statements!I20+Statements!I21))</f>
+        <f>MAX(0,ABS(Statements!J19-(Statements!J20+Statements!J21))-MAX(0.01,0.001*ABS(Statements!J19)))</f>
         <v/>
       </c>
       <c r="L11" s="13">
-        <f>ABS(Statements!J19-(Statements!J20+Statements!J21))</f>
+        <f>MAX(0,ABS(Statements!K19-(Statements!K20+Statements!K21))-MAX(0.01,0.001*ABS(Statements!K19)))</f>
         <v/>
       </c>
       <c r="M11" s="13">
-        <f>ABS(Statements!K19-(Statements!K20+Statements!K21))</f>
+        <f>MAX(0,ABS(Statements!L19-(Statements!L20+Statements!L21))-MAX(0.01,0.001*ABS(Statements!L19)))</f>
         <v/>
       </c>
       <c r="N11" s="13">
-        <f>ABS(Statements!L19-(Statements!L20+Statements!L21))</f>
+        <f>MAX(0,ABS(Statements!M19-(Statements!M20+Statements!M21))-MAX(0.01,0.001*ABS(Statements!M19)))</f>
         <v/>
       </c>
       <c r="O11" s="13">
-        <f>ABS(Statements!M19-(Statements!M20+Statements!M21))</f>
+        <f>MAX(0,ABS(Statements!N19-(Statements!N20+Statements!N21))-MAX(0.01,0.001*ABS(Statements!N19)))</f>
         <v/>
       </c>
       <c r="P11" s="13">
-        <f>ABS(Statements!N19-(Statements!N20+Statements!N21))</f>
+        <f>MAX(0,ABS(Statements!O19-(Statements!O20+Statements!O21))-MAX(0.01,0.001*ABS(Statements!O19)))</f>
         <v/>
       </c>
       <c r="Q11" s="13">
-        <f>ABS(Statements!O19-(Statements!O20+Statements!O21))</f>
+        <f>MAX(0,ABS(Statements!P19-(Statements!P20+Statements!P21))-MAX(0.01,0.001*ABS(Statements!P19)))</f>
         <v/>
       </c>
       <c r="R11" s="13">
-        <f>ABS(Statements!P19-(Statements!P20+Statements!P21))</f>
+        <f>MAX(0,ABS(Statements!Q19-(Statements!Q20+Statements!Q21))-MAX(0.01,0.001*ABS(Statements!Q19)))</f>
         <v/>
       </c>
       <c r="S11" s="13">
-        <f>ABS(Statements!Q19-(Statements!Q20+Statements!Q21))</f>
+        <f>MAX(0,ABS(Statements!R19-(Statements!R20+Statements!R21))-MAX(0.01,0.001*ABS(Statements!R19)))</f>
         <v/>
       </c>
       <c r="T11" s="13">
-        <f>ABS(Statements!R19-(Statements!R20+Statements!R21))</f>
+        <f>MAX(0,ABS(Statements!S19-(Statements!S20+Statements!S21))-MAX(0.01,0.001*ABS(Statements!S19)))</f>
         <v/>
       </c>
       <c r="U11" s="13">
-        <f>ABS(Statements!S19-(Statements!S20+Statements!S21))</f>
+        <f>MAX(0,ABS(Statements!T19-(Statements!T20+Statements!T21))-MAX(0.01,0.001*ABS(Statements!T19)))</f>
         <v/>
       </c>
       <c r="V11" s="13">
-        <f>ABS(Statements!T19-(Statements!T20+Statements!T21))</f>
+        <f>MAX(0,ABS(Statements!U19-(Statements!U20+Statements!U21))-MAX(0.01,0.001*ABS(Statements!U19)))</f>
         <v/>
       </c>
       <c r="W11" s="13">
-        <f>ABS(Statements!U19-(Statements!U20+Statements!U21))</f>
+        <f>MAX(0,ABS(Statements!V19-(Statements!V20+Statements!V21))-MAX(0.01,0.001*ABS(Statements!V19)))</f>
         <v/>
       </c>
       <c r="X11" s="13">
-        <f>ABS(Statements!V19-(Statements!V20+Statements!V21))</f>
+        <f>MAX(0,ABS(Statements!W19-(Statements!W20+Statements!W21))-MAX(0.01,0.001*ABS(Statements!W19)))</f>
         <v/>
       </c>
       <c r="Y11" s="13">
-        <f>ABS(Statements!W19-(Statements!W20+Statements!W21))</f>
+        <f>MAX(0,ABS(Statements!X19-(Statements!X20+Statements!X21))-MAX(0.01,0.001*ABS(Statements!X19)))</f>
         <v/>
       </c>
       <c r="Z11" s="13">
-        <f>ABS(Statements!X19-(Statements!X20+Statements!X21))</f>
+        <f>MAX(0,ABS(Statements!Y19-(Statements!Y20+Statements!Y21))-MAX(0.01,0.001*ABS(Statements!Y19)))</f>
         <v/>
       </c>
       <c r="AA11" s="13">
-        <f>ABS(Statements!Y19-(Statements!Y20+Statements!Y21))</f>
+        <f>MAX(0,ABS(Statements!Z19-(Statements!Z20+Statements!Z21))-MAX(0.01,0.001*ABS(Statements!Z19)))</f>
         <v/>
       </c>
       <c r="AB11" s="13">
-        <f>ABS(Statements!Z19-(Statements!Z20+Statements!Z21))</f>
+        <f>MAX(0,ABS(Statements!AA19-(Statements!AA20+Statements!AA21))-MAX(0.01,0.001*ABS(Statements!AA19)))</f>
         <v/>
       </c>
       <c r="AC11" s="13">
-        <f>ABS(Statements!AA19-(Statements!AA20+Statements!AA21))</f>
+        <f>MAX(0,ABS(Statements!AB19-(Statements!AB20+Statements!AB21))-MAX(0.01,0.001*ABS(Statements!AB19)))</f>
         <v/>
       </c>
       <c r="AD11" s="13">
-        <f>ABS(Statements!AB19-(Statements!AB20+Statements!AB21))</f>
+        <f>MAX(0,ABS(Statements!AC19-(Statements!AC20+Statements!AC21))-MAX(0.01,0.001*ABS(Statements!AC19)))</f>
         <v/>
       </c>
       <c r="AE11" s="13">
-        <f>ABS(Statements!AC19-(Statements!AC20+Statements!AC21))</f>
+        <f>MAX(0,ABS(Statements!AD19-(Statements!AD20+Statements!AD21))-MAX(0.01,0.001*ABS(Statements!AD19)))</f>
         <v/>
       </c>
       <c r="AF11" s="13">
-        <f>ABS(Statements!AD19-(Statements!AD20+Statements!AD21))</f>
+        <f>MAX(0,ABS(Statements!AE19-(Statements!AE20+Statements!AE21))-MAX(0.01,0.001*ABS(Statements!AE19)))</f>
         <v/>
       </c>
       <c r="AG11" s="13">
-        <f>ABS(Statements!AE19-(Statements!AE20+Statements!AE21))</f>
-        <v/>
-      </c>
-      <c r="AH11" s="13">
-        <f>ABS(Statements!AF19-(Statements!AF20+Statements!AF21))</f>
+        <f>MAX(0,ABS(Statements!AF19-(Statements!AF20+Statements!AF21))-MAX(0.01,0.001*ABS(Statements!AF19)))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>dscr = ebitda / (interestPaid + debtRepayment), inside the debt life</t>
+          <t>dscr is present exactly inside the debt life</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <f>MAX(E12:AH12)</f>
-        <v/>
-      </c>
-      <c r="C12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D12">
-        <f>IF(B12&lt;=C12,"PASS","FAIL")</f>
+        <f>MAX(D12:AG12)</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>IF(B12=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
+        <f>IF(AND(Statements!$C$1&gt;=Identity!$B$13,Statements!$C$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!C31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(Statements!C31="",0,ABS(Statements!C31-Statements!C8/(Statements!C16+Statements!C17)))</f>
+        <f>IF(AND(Statements!$D$1&gt;=Identity!$B$13,Statements!$D$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!D31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>IF(Statements!D31="",0,ABS(Statements!D31-Statements!D8/(Statements!D16+Statements!D17)))</f>
+        <f>IF(AND(Statements!$E$1&gt;=Identity!$B$13,Statements!$E$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!E31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="G12" s="13">
-        <f>IF(Statements!E31="",0,ABS(Statements!E31-Statements!E8/(Statements!E16+Statements!E17)))</f>
+        <f>IF(AND(Statements!$F$1&gt;=Identity!$B$13,Statements!$F$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!F31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>IF(Statements!F31="",0,ABS(Statements!F31-Statements!F8/(Statements!F16+Statements!F17)))</f>
+        <f>IF(AND(Statements!$G$1&gt;=Identity!$B$13,Statements!$G$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!G31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="I12" s="13">
-        <f>IF(Statements!G31="",0,ABS(Statements!G31-Statements!G8/(Statements!G16+Statements!G17)))</f>
+        <f>IF(AND(Statements!$H$1&gt;=Identity!$B$13,Statements!$H$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!H31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="J12" s="13">
-        <f>IF(Statements!H31="",0,ABS(Statements!H31-Statements!H8/(Statements!H16+Statements!H17)))</f>
+        <f>IF(AND(Statements!$I$1&gt;=Identity!$B$13,Statements!$I$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!I31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="K12" s="13">
-        <f>IF(Statements!I31="",0,ABS(Statements!I31-Statements!I8/(Statements!I16+Statements!I17)))</f>
+        <f>IF(AND(Statements!$J$1&gt;=Identity!$B$13,Statements!$J$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!J31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="L12" s="13">
-        <f>IF(Statements!J31="",0,ABS(Statements!J31-Statements!J8/(Statements!J16+Statements!J17)))</f>
+        <f>IF(AND(Statements!$K$1&gt;=Identity!$B$13,Statements!$K$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!K31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="M12" s="13">
-        <f>IF(Statements!K31="",0,ABS(Statements!K31-Statements!K8/(Statements!K16+Statements!K17)))</f>
+        <f>IF(AND(Statements!$L$1&gt;=Identity!$B$13,Statements!$L$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!L31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="N12" s="13">
-        <f>IF(Statements!L31="",0,ABS(Statements!L31-Statements!L8/(Statements!L16+Statements!L17)))</f>
+        <f>IF(AND(Statements!$M$1&gt;=Identity!$B$13,Statements!$M$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!M31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="O12" s="13">
-        <f>IF(Statements!M31="",0,ABS(Statements!M31-Statements!M8/(Statements!M16+Statements!M17)))</f>
+        <f>IF(AND(Statements!$N$1&gt;=Identity!$B$13,Statements!$N$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!N31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="P12" s="13">
-        <f>IF(Statements!N31="",0,ABS(Statements!N31-Statements!N8/(Statements!N16+Statements!N17)))</f>
+        <f>IF(AND(Statements!$O$1&gt;=Identity!$B$13,Statements!$O$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!O31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="Q12" s="13">
-        <f>IF(Statements!O31="",0,ABS(Statements!O31-Statements!O8/(Statements!O16+Statements!O17)))</f>
+        <f>IF(AND(Statements!$P$1&gt;=Identity!$B$13,Statements!$P$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!P31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="R12" s="13">
-        <f>IF(Statements!P31="",0,ABS(Statements!P31-Statements!P8/(Statements!P16+Statements!P17)))</f>
+        <f>IF(AND(Statements!$Q$1&gt;=Identity!$B$13,Statements!$Q$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!Q31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="S12" s="13">
-        <f>IF(Statements!Q31="",0,ABS(Statements!Q31-Statements!Q8/(Statements!Q16+Statements!Q17)))</f>
+        <f>IF(AND(Statements!$R$1&gt;=Identity!$B$13,Statements!$R$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!R31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="T12" s="13">
-        <f>IF(Statements!R31="",0,ABS(Statements!R31-Statements!R8/(Statements!R16+Statements!R17)))</f>
+        <f>IF(AND(Statements!$S$1&gt;=Identity!$B$13,Statements!$S$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!S31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="U12" s="13">
-        <f>IF(Statements!S31="",0,ABS(Statements!S31-Statements!S8/(Statements!S16+Statements!S17)))</f>
+        <f>IF(AND(Statements!$T$1&gt;=Identity!$B$13,Statements!$T$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!T31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="V12" s="13">
-        <f>IF(Statements!T31="",0,ABS(Statements!T31-Statements!T8/(Statements!T16+Statements!T17)))</f>
+        <f>IF(AND(Statements!$U$1&gt;=Identity!$B$13,Statements!$U$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!U31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="W12" s="13">
-        <f>IF(Statements!U31="",0,ABS(Statements!U31-Statements!U8/(Statements!U16+Statements!U17)))</f>
+        <f>IF(AND(Statements!$V$1&gt;=Identity!$B$13,Statements!$V$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!V31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="X12" s="13">
-        <f>IF(Statements!V31="",0,ABS(Statements!V31-Statements!V8/(Statements!V16+Statements!V17)))</f>
+        <f>IF(AND(Statements!$W$1&gt;=Identity!$B$13,Statements!$W$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!W31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="Y12" s="13">
-        <f>IF(Statements!W31="",0,ABS(Statements!W31-Statements!W8/(Statements!W16+Statements!W17)))</f>
+        <f>IF(AND(Statements!$X$1&gt;=Identity!$B$13,Statements!$X$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!X31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="Z12" s="13">
-        <f>IF(Statements!X31="",0,ABS(Statements!X31-Statements!X8/(Statements!X16+Statements!X17)))</f>
+        <f>IF(AND(Statements!$Y$1&gt;=Identity!$B$13,Statements!$Y$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!Y31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AA12" s="13">
-        <f>IF(Statements!Y31="",0,ABS(Statements!Y31-Statements!Y8/(Statements!Y16+Statements!Y17)))</f>
+        <f>IF(AND(Statements!$Z$1&gt;=Identity!$B$13,Statements!$Z$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!Z31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AB12" s="13">
-        <f>IF(Statements!Z31="",0,ABS(Statements!Z31-Statements!Z8/(Statements!Z16+Statements!Z17)))</f>
+        <f>IF(AND(Statements!$AA$1&gt;=Identity!$B$13,Statements!$AA$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AA31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AC12" s="13">
-        <f>IF(Statements!AA31="",0,ABS(Statements!AA31-Statements!AA8/(Statements!AA16+Statements!AA17)))</f>
+        <f>IF(AND(Statements!$AB$1&gt;=Identity!$B$13,Statements!$AB$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AB31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AD12" s="13">
-        <f>IF(Statements!AB31="",0,ABS(Statements!AB31-Statements!AB8/(Statements!AB16+Statements!AB17)))</f>
+        <f>IF(AND(Statements!$AC$1&gt;=Identity!$B$13,Statements!$AC$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AC31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AE12" s="13">
-        <f>IF(Statements!AC31="",0,ABS(Statements!AC31-Statements!AC8/(Statements!AC16+Statements!AC17)))</f>
+        <f>IF(AND(Statements!$AD$1&gt;=Identity!$B$13,Statements!$AD$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AD31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AF12" s="13">
-        <f>IF(Statements!AD31="",0,ABS(Statements!AD31-Statements!AD8/(Statements!AD16+Statements!AD17)))</f>
+        <f>IF(AND(Statements!$AE$1&gt;=Identity!$B$13,Statements!$AE$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AE31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
       <c r="AG12" s="13">
-        <f>IF(Statements!AE31="",0,ABS(Statements!AE31-Statements!AE8/(Statements!AE16+Statements!AE17)))</f>
-        <v/>
-      </c>
-      <c r="AH12" s="13">
-        <f>IF(Statements!AF31="",0,ABS(Statements!AF31-Statements!AF8/(Statements!AF16+Statements!AF17)))</f>
+        <f>IF(AND(Statements!$AF$1&gt;=Identity!$B$13,Statements!$AF$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AF31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>closing[last] = 0</t>
+          <t>dscr = ebitda / (interestPaid + debtRepayment)</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <f>ABS(Statements!AF27)</f>
-        <v/>
-      </c>
-      <c r="C13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D13">
-        <f>IF(B13&lt;=C13,"PASS","FAIL")</f>
+        <f>MAX(D13:AG13)</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>IF(B13=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>IF(OR(Statements!C31="",Statements!C16+Statements!C17=0),0,MAX(0,ABS(Statements!C31-Statements!C8/(Statements!C16+Statements!C17))-MAX(0.001,0.001*ABS(Statements!C31))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="13">
+        <f>IF(OR(Statements!D31="",Statements!D16+Statements!D17=0),0,MAX(0,ABS(Statements!D31-Statements!D8/(Statements!D16+Statements!D17))-MAX(0.001,0.001*ABS(Statements!D31))))</f>
+        <v/>
+      </c>
+      <c r="F13" s="13">
+        <f>IF(OR(Statements!E31="",Statements!E16+Statements!E17=0),0,MAX(0,ABS(Statements!E31-Statements!E8/(Statements!E16+Statements!E17))-MAX(0.001,0.001*ABS(Statements!E31))))</f>
+        <v/>
+      </c>
+      <c r="G13" s="13">
+        <f>IF(OR(Statements!F31="",Statements!F16+Statements!F17=0),0,MAX(0,ABS(Statements!F31-Statements!F8/(Statements!F16+Statements!F17))-MAX(0.001,0.001*ABS(Statements!F31))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="13">
+        <f>IF(OR(Statements!G31="",Statements!G16+Statements!G17=0),0,MAX(0,ABS(Statements!G31-Statements!G8/(Statements!G16+Statements!G17))-MAX(0.001,0.001*ABS(Statements!G31))))</f>
+        <v/>
+      </c>
+      <c r="I13" s="13">
+        <f>IF(OR(Statements!H31="",Statements!H16+Statements!H17=0),0,MAX(0,ABS(Statements!H31-Statements!H8/(Statements!H16+Statements!H17))-MAX(0.001,0.001*ABS(Statements!H31))))</f>
+        <v/>
+      </c>
+      <c r="J13" s="13">
+        <f>IF(OR(Statements!I31="",Statements!I16+Statements!I17=0),0,MAX(0,ABS(Statements!I31-Statements!I8/(Statements!I16+Statements!I17))-MAX(0.001,0.001*ABS(Statements!I31))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="13">
+        <f>IF(OR(Statements!J31="",Statements!J16+Statements!J17=0),0,MAX(0,ABS(Statements!J31-Statements!J8/(Statements!J16+Statements!J17))-MAX(0.001,0.001*ABS(Statements!J31))))</f>
+        <v/>
+      </c>
+      <c r="L13" s="13">
+        <f>IF(OR(Statements!K31="",Statements!K16+Statements!K17=0),0,MAX(0,ABS(Statements!K31-Statements!K8/(Statements!K16+Statements!K17))-MAX(0.001,0.001*ABS(Statements!K31))))</f>
+        <v/>
+      </c>
+      <c r="M13" s="13">
+        <f>IF(OR(Statements!L31="",Statements!L16+Statements!L17=0),0,MAX(0,ABS(Statements!L31-Statements!L8/(Statements!L16+Statements!L17))-MAX(0.001,0.001*ABS(Statements!L31))))</f>
+        <v/>
+      </c>
+      <c r="N13" s="13">
+        <f>IF(OR(Statements!M31="",Statements!M16+Statements!M17=0),0,MAX(0,ABS(Statements!M31-Statements!M8/(Statements!M16+Statements!M17))-MAX(0.001,0.001*ABS(Statements!M31))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="13">
+        <f>IF(OR(Statements!N31="",Statements!N16+Statements!N17=0),0,MAX(0,ABS(Statements!N31-Statements!N8/(Statements!N16+Statements!N17))-MAX(0.001,0.001*ABS(Statements!N31))))</f>
+        <v/>
+      </c>
+      <c r="P13" s="13">
+        <f>IF(OR(Statements!O31="",Statements!O16+Statements!O17=0),0,MAX(0,ABS(Statements!O31-Statements!O8/(Statements!O16+Statements!O17))-MAX(0.001,0.001*ABS(Statements!O31))))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="13">
+        <f>IF(OR(Statements!P31="",Statements!P16+Statements!P17=0),0,MAX(0,ABS(Statements!P31-Statements!P8/(Statements!P16+Statements!P17))-MAX(0.001,0.001*ABS(Statements!P31))))</f>
+        <v/>
+      </c>
+      <c r="R13" s="13">
+        <f>IF(OR(Statements!Q31="",Statements!Q16+Statements!Q17=0),0,MAX(0,ABS(Statements!Q31-Statements!Q8/(Statements!Q16+Statements!Q17))-MAX(0.001,0.001*ABS(Statements!Q31))))</f>
+        <v/>
+      </c>
+      <c r="S13" s="13">
+        <f>IF(OR(Statements!R31="",Statements!R16+Statements!R17=0),0,MAX(0,ABS(Statements!R31-Statements!R8/(Statements!R16+Statements!R17))-MAX(0.001,0.001*ABS(Statements!R31))))</f>
+        <v/>
+      </c>
+      <c r="T13" s="13">
+        <f>IF(OR(Statements!S31="",Statements!S16+Statements!S17=0),0,MAX(0,ABS(Statements!S31-Statements!S8/(Statements!S16+Statements!S17))-MAX(0.001,0.001*ABS(Statements!S31))))</f>
+        <v/>
+      </c>
+      <c r="U13" s="13">
+        <f>IF(OR(Statements!T31="",Statements!T16+Statements!T17=0),0,MAX(0,ABS(Statements!T31-Statements!T8/(Statements!T16+Statements!T17))-MAX(0.001,0.001*ABS(Statements!T31))))</f>
+        <v/>
+      </c>
+      <c r="V13" s="13">
+        <f>IF(OR(Statements!U31="",Statements!U16+Statements!U17=0),0,MAX(0,ABS(Statements!U31-Statements!U8/(Statements!U16+Statements!U17))-MAX(0.001,0.001*ABS(Statements!U31))))</f>
+        <v/>
+      </c>
+      <c r="W13" s="13">
+        <f>IF(OR(Statements!V31="",Statements!V16+Statements!V17=0),0,MAX(0,ABS(Statements!V31-Statements!V8/(Statements!V16+Statements!V17))-MAX(0.001,0.001*ABS(Statements!V31))))</f>
+        <v/>
+      </c>
+      <c r="X13" s="13">
+        <f>IF(OR(Statements!W31="",Statements!W16+Statements!W17=0),0,MAX(0,ABS(Statements!W31-Statements!W8/(Statements!W16+Statements!W17))-MAX(0.001,0.001*ABS(Statements!W31))))</f>
+        <v/>
+      </c>
+      <c r="Y13" s="13">
+        <f>IF(OR(Statements!X31="",Statements!X16+Statements!X17=0),0,MAX(0,ABS(Statements!X31-Statements!X8/(Statements!X16+Statements!X17))-MAX(0.001,0.001*ABS(Statements!X31))))</f>
+        <v/>
+      </c>
+      <c r="Z13" s="13">
+        <f>IF(OR(Statements!Y31="",Statements!Y16+Statements!Y17=0),0,MAX(0,ABS(Statements!Y31-Statements!Y8/(Statements!Y16+Statements!Y17))-MAX(0.001,0.001*ABS(Statements!Y31))))</f>
+        <v/>
+      </c>
+      <c r="AA13" s="13">
+        <f>IF(OR(Statements!Z31="",Statements!Z16+Statements!Z17=0),0,MAX(0,ABS(Statements!Z31-Statements!Z8/(Statements!Z16+Statements!Z17))-MAX(0.001,0.001*ABS(Statements!Z31))))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="13">
+        <f>IF(OR(Statements!AA31="",Statements!AA16+Statements!AA17=0),0,MAX(0,ABS(Statements!AA31-Statements!AA8/(Statements!AA16+Statements!AA17))-MAX(0.001,0.001*ABS(Statements!AA31))))</f>
+        <v/>
+      </c>
+      <c r="AC13" s="13">
+        <f>IF(OR(Statements!AB31="",Statements!AB16+Statements!AB17=0),0,MAX(0,ABS(Statements!AB31-Statements!AB8/(Statements!AB16+Statements!AB17))-MAX(0.001,0.001*ABS(Statements!AB31))))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="13">
+        <f>IF(OR(Statements!AC31="",Statements!AC16+Statements!AC17=0),0,MAX(0,ABS(Statements!AC31-Statements!AC8/(Statements!AC16+Statements!AC17))-MAX(0.001,0.001*ABS(Statements!AC31))))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="13">
+        <f>IF(OR(Statements!AD31="",Statements!AD16+Statements!AD17=0),0,MAX(0,ABS(Statements!AD31-Statements!AD8/(Statements!AD16+Statements!AD17))-MAX(0.001,0.001*ABS(Statements!AD31))))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="13">
+        <f>IF(OR(Statements!AE31="",Statements!AE16+Statements!AE17=0),0,MAX(0,ABS(Statements!AE31-Statements!AE8/(Statements!AE16+Statements!AE17))-MAX(0.001,0.001*ABS(Statements!AE31))))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="13">
+        <f>IF(OR(Statements!AF31="",Statements!AF16+Statements!AF17=0),0,MAX(0,ABS(Statements!AF31-Statements!AF8/(Statements!AF16+Statements!AF17))-MAX(0.001,0.001*ABS(Statements!AF31))))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>sum debtDrawdown = seniorDebt</t>
+          <t>closing[last] = 0</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <f>ABS(SUM(Statements!$C$20:$AF$20)-Identity!$B$26)</f>
-        <v/>
-      </c>
-      <c r="C14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D14">
-        <f>IF(B14&lt;=C14,"PASS","FAIL")</f>
+        <f>MAX(0,ABS(Statements!AF27)-MAX(0.01,0.001*ABS(0)))</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>IF(B14=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sum equityDrawdown = totalCapex - seniorDebt</t>
+          <t>sum debtDrawdown = seniorDebt</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <f>ABS(SUM(Statements!$C$21:$AF$21)-(Identity!$B$25-Identity!$B$26))</f>
-        <v/>
-      </c>
-      <c r="C15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D15">
-        <f>IF(B15&lt;=C15,"PASS","FAIL")</f>
+        <f>MAX(0,ABS(SUM(Statements!$C$20:$AF$20)-Identity!$B$26)-MAX(0.01,0.001*ABS(Identity!$B$26)))</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>IF(B15=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>sum capex = totalCapex</t>
+          <t>sum equityDrawdown = totalCapex - seniorDebt</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <f>ABS(SUM(Statements!$C$19:$AF$19)-Identity!$B$25)</f>
-        <v/>
-      </c>
-      <c r="C16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D16">
-        <f>IF(B16&lt;=C16,"PASS","FAIL")</f>
+        <f>MAX(0,ABS(SUM(Statements!$C$21:$AF$21)-(Identity!$B$25-Identity!$B$26))-MAX(0.01,0.001*ABS(Identity!$B$25-Identity!$B$26)))</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>IF(B16=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>sum depreciation = totalCapex - ppe[last]</t>
+          <t>sum capex = totalCapex</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <f>ABS(SUM(Statements!$C$9:$AF$9)-(Identity!$B$25-Statements!AF29))</f>
-        <v/>
-      </c>
-      <c r="C17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D17">
-        <f>IF(B17&lt;=C17,"PASS","FAIL")</f>
+        <f>MAX(0,ABS(SUM(Statements!$C$19:$AF$19)-Identity!$B$25)-MAX(0.01,0.001*ABS(Identity!$B$25)))</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>IF(B17=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>sum depreciation = totalCapex - ppe[last]</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>MAX(0,ABS(SUM(Statements!$C$9:$AF$9)-(Identity!$B$25-Statements!AF29))-MAX(0.01,0.001*ABS(Identity!$B$25)))</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>IF(B18=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>taxExpense = taxRate * max(0, pbt)   [warn]</t>
         </is>
       </c>
-      <c r="B18" s="13">
-        <f>ABS(SUM(Statements!$C$13:$AF$13)-Assumptions!$B$3*SUMPRODUCT((Statements!$C$12:$AF$12&gt;0)*Statements!$C$12:$AF$12))</f>
-        <v/>
-      </c>
-      <c r="C18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D18">
-        <f>IF(B18&lt;=C18,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Live formulas against Statements. Tolerance is EUR 0.01m absolute, the value in the assumption set. Every check must read PASS before the file is loaded; the last one is a plausibility warning, not a blocker.</t>
+      <c r="B19" s="13">
+        <f>MAX(0,ABS(SUM(Statements!$C$13:$AF$13)-Assumptions!$B$3*SUMPRODUCT((Statements!$C$12:$AF$12&gt;0)*Statements!$C$12:$AF$12))-MAX(0.01,0.001*ABS(SUM(Statements!$C$13:$AF$13))))</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF(B19=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Live formulas against Statements, Identity and Assumptions. Each cell holds the BREACH over tolerance -- max(0, |residual| - max(absolute, 0.1% of the line)) -- so zero means the year is inside tolerance and any non-zero cell names the year that is not. The absolute limb is EUR 0.01m for a money line and 0.001 for the DSCR ratio, from the assumption set. Every check must read PASS before the file is loaded; the last one is a plausibility warning, not a blocker.</t>
         </is>
       </c>
     </row>

--- a/templates/project-template.xlsx
+++ b/templates/project-template.xlsx
@@ -20,11 +20,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,45 +29,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="005D5D60"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002C455D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6EBFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -78,40 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00B7B7BA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,388 +419,372 @@
   </sheetPr>
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>schemaVersion</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Almonte Solar</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>location.country</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>location.countryCode</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>location.iso3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ESP</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>location.lat</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>39.25</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>degrees</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>location.lon</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>-6.52</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>degrees</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>asset.technology</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>solar</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>asset.stage</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>ready_to_build</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>asset.capacityMw</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>asset.codYear</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>2028</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>asset.netCapacityFactor</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" t="n">
         <v>0.230324</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>asset.opexPerKwYear</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>12.813182</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>EUR/kW/yr</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>revenue.ppaShare</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" t="n">
         <v>0.55</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>revenue.ppaPrice</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>EUR/MWh</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>revenue.ppaTenorYears</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>revenue.countryBaseloadPrice</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>EUR/MWh</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>revenue.captureFactor</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" t="n">
         <v>0.68</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>execution.developmentRiskScore</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" t="n">
         <v>2.7</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>1.0-5.0</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>execution.gridSecured</t>
         </is>
       </c>
-      <c r="B22" s="3" t="b">
+      <c r="B22" t="b">
         <v>1</v>
       </c>
-      <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>execution.omContracted</t>
         </is>
       </c>
-      <c r="B23" s="3" t="b">
+      <c r="B23" t="b">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>execution.currency</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>capitalStructure.totalCapex</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" t="n">
         <v>103.322563</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>EURm</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>capitalStructure.seniorDebt</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" t="n">
         <v>74.392246</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>EURm</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>capitalStructure.maxGearing</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" t="n">
         <v>0.72</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
@@ -877,108 +801,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>assumptions.baseYear</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>2027</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>assumptions.taxRate</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>0.2</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>assumptions.depreciationYears</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>25</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>assumptions.debtRate</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>0.055</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>assumptions.debtTenorYears</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>assumptions.degradationRate</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fraction/yr</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>assumptions.priceEscalation</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fraction/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>assumptions.merchantEscalation</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fraction/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>assumptions.opexEscalation</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fraction/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>assumptions.targetDscr</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Declared inputs, not configuration. The loader's dispersion report compares these across the pipeline.</t>
         </is>
@@ -997,37 +991,31 @@
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>estimateBasis</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>provenance.preparedBy</t>
         </is>
@@ -1039,7 +1027,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>provenance.preparedOn</t>
         </is>
@@ -1051,7 +1039,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>provenance.modelVersion</t>
         </is>
@@ -1063,168 +1051,168 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>per field group</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>generation</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>engineering_estimate</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>P50 from a third-party yield study, two years of on-site pyranometer data.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>contracted</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>55% under a signed 10-year PPA; merchant tail from the house Iberian curve.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>binding_offer</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>EPC offer valid to 2027-03; BoP and grid works at engineering estimate.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>benchmark</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Iberian utility-scale PV benchmark, adjusted for single-axis tracking.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>debtTerms</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>binding_offer</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Indicative term sheet from two lenders; margin not yet fixed.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>grid</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>contracted</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Firm connection agreement signed 2025-11.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>om</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>contracted</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Ten-year full-scope O&amp;M agreement signed with the EPC contractor.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>estimateBasis: contracted | binding_offer | engineering_estimate | benchmark | internal_model | placeholder.  confidence: high | medium | low.  Reported, never blocking.</t>
         </is>
@@ -1243,183 +1231,118 @@
   </sheetPr>
   <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="7" t="n">
+      <c r="C1" t="n">
         <v>2027</v>
       </c>
-      <c r="D1" s="7" t="n">
+      <c r="D1" t="n">
         <v>2028</v>
       </c>
-      <c r="E1" s="7" t="n">
+      <c r="E1" t="n">
         <v>2029</v>
       </c>
-      <c r="F1" s="7" t="n">
+      <c r="F1" t="n">
         <v>2030</v>
       </c>
-      <c r="G1" s="7" t="n">
+      <c r="G1" t="n">
         <v>2031</v>
       </c>
-      <c r="H1" s="7" t="n">
+      <c r="H1" t="n">
         <v>2032</v>
       </c>
-      <c r="I1" s="7" t="n">
+      <c r="I1" t="n">
         <v>2033</v>
       </c>
-      <c r="J1" s="7" t="n">
+      <c r="J1" t="n">
         <v>2034</v>
       </c>
-      <c r="K1" s="7" t="n">
+      <c r="K1" t="n">
         <v>2035</v>
       </c>
-      <c r="L1" s="7" t="n">
+      <c r="L1" t="n">
         <v>2036</v>
       </c>
-      <c r="M1" s="7" t="n">
+      <c r="M1" t="n">
         <v>2037</v>
       </c>
-      <c r="N1" s="7" t="n">
+      <c r="N1" t="n">
         <v>2038</v>
       </c>
-      <c r="O1" s="7" t="n">
+      <c r="O1" t="n">
         <v>2039</v>
       </c>
-      <c r="P1" s="7" t="n">
+      <c r="P1" t="n">
         <v>2040</v>
       </c>
-      <c r="Q1" s="7" t="n">
+      <c r="Q1" t="n">
         <v>2041</v>
       </c>
-      <c r="R1" s="7" t="n">
+      <c r="R1" t="n">
         <v>2042</v>
       </c>
-      <c r="S1" s="7" t="n">
+      <c r="S1" t="n">
         <v>2043</v>
       </c>
-      <c r="T1" s="7" t="n">
+      <c r="T1" t="n">
         <v>2044</v>
       </c>
-      <c r="U1" s="7" t="n">
+      <c r="U1" t="n">
         <v>2045</v>
       </c>
-      <c r="V1" s="7" t="n">
+      <c r="V1" t="n">
         <v>2046</v>
       </c>
-      <c r="W1" s="7" t="n">
+      <c r="W1" t="n">
         <v>2047</v>
       </c>
-      <c r="X1" s="7" t="n">
+      <c r="X1" t="n">
         <v>2048</v>
       </c>
-      <c r="Y1" s="7" t="n">
+      <c r="Y1" t="n">
         <v>2049</v>
       </c>
-      <c r="Z1" s="7" t="n">
+      <c r="Z1" t="n">
         <v>2050</v>
       </c>
-      <c r="AA1" s="7" t="n">
+      <c r="AA1" t="n">
         <v>2051</v>
       </c>
-      <c r="AB1" s="7" t="n">
+      <c r="AB1" t="n">
         <v>2052</v>
       </c>
-      <c r="AC1" s="7" t="n">
+      <c r="AC1" t="n">
         <v>2053</v>
       </c>
-      <c r="AD1" s="7" t="n">
+      <c r="AD1" t="n">
         <v>2054</v>
       </c>
-      <c r="AE1" s="7" t="n">
+      <c r="AE1" t="n">
         <v>2055</v>
       </c>
-      <c r="AF1" s="7" t="n">
+      <c r="AF1" t="n">
         <v>2056</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>physicals</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="9" t="n"/>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="9" t="n"/>
-      <c r="N2" s="9" t="n"/>
-      <c r="O2" s="9" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="9" t="n"/>
-      <c r="T2" s="9" t="n"/>
-      <c r="U2" s="9" t="n"/>
-      <c r="V2" s="9" t="n"/>
-      <c r="W2" s="9" t="n"/>
-      <c r="X2" s="9" t="n"/>
-      <c r="Y2" s="9" t="n"/>
-      <c r="Z2" s="9" t="n"/>
-      <c r="AA2" s="9" t="n"/>
-      <c r="AB2" s="9" t="n"/>
-      <c r="AC2" s="9" t="n"/>
-      <c r="AD2" s="9" t="n"/>
-      <c r="AE2" s="9" t="n"/>
-      <c r="AF2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>physicals.generationGwh</t>
         </is>
@@ -1429,99 +1352,99 @@
           <t>GWh</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
+      <c r="C3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D3" t="n">
         <v>199.746237</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" t="n">
         <v>361.359102</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" t="n">
         <v>359.552307</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" t="n">
         <v>357.754545</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" t="n">
         <v>355.965772</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" t="n">
         <v>354.185944</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" t="n">
         <v>352.415014</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K3" t="n">
         <v>350.652939</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" t="n">
         <v>348.899674</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="M3" t="n">
         <v>347.155176</v>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="N3" t="n">
         <v>345.4194</v>
       </c>
-      <c r="O3" s="11" t="n">
+      <c r="O3" t="n">
         <v>343.692303</v>
       </c>
-      <c r="P3" s="11" t="n">
+      <c r="P3" t="n">
         <v>341.973841</v>
       </c>
-      <c r="Q3" s="11" t="n">
+      <c r="Q3" t="n">
         <v>340.263972</v>
       </c>
-      <c r="R3" s="11" t="n">
+      <c r="R3" t="n">
         <v>338.562652</v>
       </c>
-      <c r="S3" s="11" t="n">
+      <c r="S3" t="n">
         <v>336.869839</v>
       </c>
-      <c r="T3" s="11" t="n">
+      <c r="T3" t="n">
         <v>335.18549</v>
       </c>
-      <c r="U3" s="11" t="n">
+      <c r="U3" t="n">
         <v>333.509562</v>
       </c>
-      <c r="V3" s="11" t="n">
+      <c r="V3" t="n">
         <v>331.842015</v>
       </c>
-      <c r="W3" s="11" t="n">
+      <c r="W3" t="n">
         <v>330.182804</v>
       </c>
-      <c r="X3" s="11" t="n">
+      <c r="X3" t="n">
         <v>328.53189</v>
       </c>
-      <c r="Y3" s="11" t="n">
+      <c r="Y3" t="n">
         <v>326.889231</v>
       </c>
-      <c r="Z3" s="11" t="n">
+      <c r="Z3" t="n">
         <v>325.254785</v>
       </c>
-      <c r="AA3" s="11" t="n">
+      <c r="AA3" t="n">
         <v>323.628511</v>
       </c>
-      <c r="AB3" s="11" t="n">
+      <c r="AB3" t="n">
         <v>322.010368</v>
       </c>
-      <c r="AC3" s="11" t="n">
+      <c r="AC3" t="n">
         <v>320.400317</v>
       </c>
-      <c r="AD3" s="11" t="n">
+      <c r="AD3" t="n">
         <v>318.798315</v>
       </c>
-      <c r="AE3" s="11" t="n">
+      <c r="AE3" t="n">
         <v>317.204323</v>
       </c>
-      <c r="AF3" s="11" t="n">
+      <c r="AF3" t="n">
         <v>315.618302</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>physicals.achievedPrice</t>
         </is>
@@ -1531,137 +1454,106 @@
           <t>EUR/MWh</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="n">
+      <c r="C4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D4" t="n">
         <v>36.25</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" t="n">
         <v>36.71205</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" t="n">
         <v>37.182307</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" t="n">
         <v>37.660936</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" t="n">
         <v>38.148105</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="I4" t="n">
         <v>38.643986</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J4" t="n">
         <v>39.148755</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" t="n">
         <v>39.66259</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" t="n">
         <v>40.185674</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" t="n">
         <v>40.718193</v>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="N4" t="n">
         <v>48.00893</v>
       </c>
-      <c r="O4" s="11" t="n">
+      <c r="O4" t="n">
         <v>49.017118</v>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="P4" t="n">
         <v>50.046477</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" t="n">
         <v>51.097453</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" t="n">
         <v>52.1705</v>
       </c>
-      <c r="S4" s="11" t="n">
+      <c r="S4" t="n">
         <v>53.26608</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" t="n">
         <v>54.384668</v>
       </c>
-      <c r="U4" s="11" t="n">
+      <c r="U4" t="n">
         <v>55.526746</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" t="n">
         <v>56.692808</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" t="n">
         <v>57.883356</v>
       </c>
-      <c r="X4" s="11" t="n">
+      <c r="X4" t="n">
         <v>59.098907</v>
       </c>
-      <c r="Y4" s="11" t="n">
+      <c r="Y4" t="n">
         <v>60.339984</v>
       </c>
-      <c r="Z4" s="11" t="n">
+      <c r="Z4" t="n">
         <v>61.607124</v>
       </c>
-      <c r="AA4" s="11" t="n">
+      <c r="AA4" t="n">
         <v>62.900873</v>
       </c>
-      <c r="AB4" s="11" t="n">
-        <v>64.22179199999999</v>
-      </c>
-      <c r="AC4" s="11" t="n">
+      <c r="AB4" t="n">
+        <v>64.221792</v>
+      </c>
+      <c r="AC4" t="n">
         <v>65.570449</v>
       </c>
-      <c r="AD4" s="11" t="n">
+      <c r="AD4" t="n">
         <v>66.947429</v>
       </c>
-      <c r="AE4" s="11" t="n">
+      <c r="AE4" t="n">
         <v>68.353325</v>
       </c>
-      <c r="AF4" s="11" t="n">
-        <v>69.78874500000001</v>
+      <c r="AF4" t="n">
+        <v>69.788745</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>incomeStatement</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="9" t="n"/>
-      <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
-      <c r="W5" s="9" t="n"/>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="9" t="n"/>
-      <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="9" t="n"/>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>incomeStatement.revenue</t>
         </is>
@@ -1671,99 +1563,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="n">
+      <c r="C6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D6" t="n">
         <v>7.240801</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" t="n">
         <v>13.266233</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" t="n">
         <v>13.368984</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" t="n">
         <v>13.473371</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" t="n">
         <v>13.57942</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" t="n">
         <v>13.687157</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" t="n">
         <v>13.796609</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" t="n">
         <v>13.907804</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" t="n">
         <v>14.020768</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" t="n">
         <v>14.135532</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" t="n">
         <v>16.583216</v>
       </c>
-      <c r="O6" s="12" t="n">
+      <c r="O6" t="n">
         <v>16.846806</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" t="n">
         <v>17.114586</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" t="n">
         <v>17.386622</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" t="n">
         <v>17.662983</v>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" t="n">
         <v>17.943736</v>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" t="n">
         <v>18.228952</v>
       </c>
-      <c r="U6" s="12" t="n">
+      <c r="U6" t="n">
         <v>18.518701</v>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" t="n">
         <v>18.813055</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" t="n">
         <v>19.112089</v>
       </c>
-      <c r="X6" s="12" t="n">
+      <c r="X6" t="n">
         <v>19.415876</v>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" t="n">
         <v>19.724491</v>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" t="n">
         <v>20.038012</v>
       </c>
-      <c r="AA6" s="12" t="n">
+      <c r="AA6" t="n">
         <v>20.356516</v>
       </c>
-      <c r="AB6" s="12" t="n">
+      <c r="AB6" t="n">
         <v>20.680083</v>
       </c>
-      <c r="AC6" s="12" t="n">
+      <c r="AC6" t="n">
         <v>21.008793</v>
       </c>
-      <c r="AD6" s="12" t="n">
+      <c r="AD6" t="n">
         <v>21.342727</v>
       </c>
-      <c r="AE6" s="12" t="n">
+      <c r="AE6" t="n">
         <v>21.68197</v>
       </c>
-      <c r="AF6" s="12" t="n">
+      <c r="AF6" t="n">
         <v>22.026605</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>incomeStatement.opex</t>
         </is>
@@ -1773,99 +1665,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="n">
+      <c r="C7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D7" t="n">
         <v>2.306373</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" t="n">
         <v>2.354807</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" t="n">
         <v>2.404258</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" t="n">
         <v>2.454747</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" t="n">
         <v>2.506297</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" t="n">
         <v>2.558929</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" t="n">
         <v>2.612666</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" t="n">
         <v>2.667532</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" t="n">
         <v>2.723551</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" t="n">
         <v>2.780745</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" t="n">
         <v>2.839141</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" t="n">
         <v>2.898763</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" t="n">
         <v>2.959637</v>
       </c>
-      <c r="Q7" s="12" t="n">
+      <c r="Q7" t="n">
         <v>3.021789</v>
       </c>
-      <c r="R7" s="12" t="n">
+      <c r="R7" t="n">
         <v>3.085247</v>
       </c>
-      <c r="S7" s="12" t="n">
+      <c r="S7" t="n">
         <v>3.150037</v>
       </c>
-      <c r="T7" s="12" t="n">
+      <c r="T7" t="n">
         <v>3.216188</v>
       </c>
-      <c r="U7" s="12" t="n">
+      <c r="U7" t="n">
         <v>3.283728</v>
       </c>
-      <c r="V7" s="12" t="n">
+      <c r="V7" t="n">
         <v>3.352686</v>
       </c>
-      <c r="W7" s="12" t="n">
+      <c r="W7" t="n">
         <v>3.423092</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" t="n">
         <v>3.494977</v>
       </c>
-      <c r="Y7" s="12" t="n">
+      <c r="Y7" t="n">
         <v>3.568372</v>
       </c>
-      <c r="Z7" s="12" t="n">
+      <c r="Z7" t="n">
         <v>3.643308</v>
       </c>
-      <c r="AA7" s="12" t="n">
+      <c r="AA7" t="n">
         <v>3.719817</v>
       </c>
-      <c r="AB7" s="12" t="n">
+      <c r="AB7" t="n">
         <v>3.797933</v>
       </c>
-      <c r="AC7" s="12" t="n">
+      <c r="AC7" t="n">
         <v>3.87769</v>
       </c>
-      <c r="AD7" s="12" t="n">
+      <c r="AD7" t="n">
         <v>3.959121</v>
       </c>
-      <c r="AE7" s="12" t="n">
+      <c r="AE7" t="n">
         <v>4.042263</v>
       </c>
-      <c r="AF7" s="12" t="n">
+      <c r="AF7" t="n">
         <v>4.12715</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>incomeStatement.ebitda</t>
         </is>
@@ -1875,99 +1767,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="n">
+      <c r="C8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D8" t="n">
         <v>4.934428</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" t="n">
         <v>10.911427</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" t="n">
         <v>10.964727</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" t="n">
         <v>11.018624</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" t="n">
         <v>11.073123</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" t="n">
         <v>11.128228</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" t="n">
         <v>11.183943</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" t="n">
         <v>11.240271</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" t="n">
         <v>11.297218</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" t="n">
         <v>11.354786</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" t="n">
         <v>13.744075</v>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="O8" t="n">
         <v>13.948043</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" t="n">
         <v>14.154949</v>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" t="n">
         <v>14.364833</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" t="n">
         <v>14.577736</v>
       </c>
-      <c r="S8" s="12" t="n">
+      <c r="S8" t="n">
         <v>14.793699</v>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" t="n">
         <v>15.012764</v>
       </c>
-      <c r="U8" s="12" t="n">
+      <c r="U8" t="n">
         <v>15.234973</v>
       </c>
-      <c r="V8" s="12" t="n">
+      <c r="V8" t="n">
         <v>15.46037</v>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" t="n">
         <v>15.688997</v>
       </c>
-      <c r="X8" s="12" t="n">
+      <c r="X8" t="n">
         <v>15.920898</v>
       </c>
-      <c r="Y8" s="12" t="n">
+      <c r="Y8" t="n">
         <v>16.156119</v>
       </c>
-      <c r="Z8" s="12" t="n">
+      <c r="Z8" t="n">
         <v>16.394704</v>
       </c>
-      <c r="AA8" s="12" t="n">
+      <c r="AA8" t="n">
         <v>16.636699</v>
       </c>
-      <c r="AB8" s="12" t="n">
+      <c r="AB8" t="n">
         <v>16.88215</v>
       </c>
-      <c r="AC8" s="12" t="n">
+      <c r="AC8" t="n">
         <v>17.131103</v>
       </c>
-      <c r="AD8" s="12" t="n">
+      <c r="AD8" t="n">
         <v>17.383606</v>
       </c>
-      <c r="AE8" s="12" t="n">
+      <c r="AE8" t="n">
         <v>17.639707</v>
       </c>
-      <c r="AF8" s="12" t="n">
+      <c r="AF8" t="n">
         <v>17.899455</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>incomeStatement.depreciation</t>
         </is>
@@ -1977,99 +1869,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="C9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="O9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="T9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="U9" s="12" t="n">
+      <c r="U9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="V9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="W9" s="12" t="n">
+      <c r="W9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="X9" s="12" t="n">
+      <c r="X9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="Y9" s="12" t="n">
+      <c r="Y9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="Z9" s="12" t="n">
+      <c r="Z9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="AA9" s="12" t="n">
+      <c r="AA9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="AB9" s="12" t="n">
+      <c r="AB9" t="n">
         <v>4.132903</v>
       </c>
-      <c r="AC9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12" t="n">
-        <v>0</v>
+      <c r="AC9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>incomeStatement.ebit</t>
         </is>
@@ -2079,99 +1971,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n">
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.801526</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" t="n">
         <v>6.778524</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" t="n">
         <v>6.831824</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" t="n">
         <v>6.885722</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" t="n">
         <v>6.940221</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" t="n">
         <v>6.995325</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" t="n">
         <v>7.05104</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" t="n">
         <v>7.107369</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" t="n">
         <v>7.164315</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" t="n">
         <v>7.221884</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" t="n">
         <v>9.611172</v>
       </c>
-      <c r="O10" s="12" t="n">
-        <v>9.815141000000001</v>
-      </c>
-      <c r="P10" s="12" t="n">
+      <c r="O10" t="n">
+        <v>9.815141</v>
+      </c>
+      <c r="P10" t="n">
         <v>10.022047</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" t="n">
         <v>10.231931</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" t="n">
         <v>10.444833</v>
       </c>
-      <c r="S10" s="12" t="n">
+      <c r="S10" t="n">
         <v>10.660796</v>
       </c>
-      <c r="T10" s="12" t="n">
+      <c r="T10" t="n">
         <v>10.879861</v>
       </c>
-      <c r="U10" s="12" t="n">
+      <c r="U10" t="n">
         <v>11.102071</v>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" t="n">
         <v>11.327467</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" t="n">
         <v>11.556094</v>
       </c>
-      <c r="X10" s="12" t="n">
+      <c r="X10" t="n">
         <v>11.787996</v>
       </c>
-      <c r="Y10" s="12" t="n">
+      <c r="Y10" t="n">
         <v>12.023217</v>
       </c>
-      <c r="Z10" s="12" t="n">
+      <c r="Z10" t="n">
         <v>12.261802</v>
       </c>
-      <c r="AA10" s="12" t="n">
+      <c r="AA10" t="n">
         <v>12.503796</v>
       </c>
-      <c r="AB10" s="12" t="n">
+      <c r="AB10" t="n">
         <v>12.749247</v>
       </c>
-      <c r="AC10" s="12" t="n">
+      <c r="AC10" t="n">
         <v>17.131103</v>
       </c>
-      <c r="AD10" s="12" t="n">
+      <c r="AD10" t="n">
         <v>17.383606</v>
       </c>
-      <c r="AE10" s="12" t="n">
+      <c r="AE10" t="n">
         <v>17.639707</v>
       </c>
-      <c r="AF10" s="12" t="n">
+      <c r="AF10" t="n">
         <v>17.899455</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>incomeStatement.interestExpense</t>
         </is>
@@ -2181,99 +2073,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="n">
+      <c r="C11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D11" t="n">
         <v>4.091574</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" t="n">
         <v>3.952788</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" t="n">
         <v>3.806369</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" t="n">
         <v>3.651897</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" t="n">
         <v>3.488928</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" t="n">
         <v>3.316997</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" t="n">
         <v>3.13561</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" t="n">
         <v>2.944246</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" t="n">
         <v>2.742357</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" t="n">
         <v>2.529364</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" t="n">
         <v>2.304657</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="O11" t="n">
         <v>2.067591</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" t="n">
         <v>1.817486</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" t="n">
         <v>1.553625</v>
       </c>
-      <c r="R11" s="12" t="n">
+      <c r="R11" t="n">
         <v>1.275252</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" t="n">
         <v>0.981569</v>
       </c>
-      <c r="T11" s="12" t="n">
+      <c r="T11" t="n">
         <v>0.671732</v>
       </c>
-      <c r="U11" s="12" t="n">
+      <c r="U11" t="n">
         <v>0.344855</v>
       </c>
-      <c r="V11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12" t="n">
-        <v>0</v>
+      <c r="V11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>incomeStatement.pbt</t>
         </is>
@@ -2283,99 +2175,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n">
+      <c r="C12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D12" t="n">
         <v>-3.290048</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" t="n">
         <v>2.825737</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" t="n">
         <v>3.025456</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" t="n">
         <v>3.233825</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" t="n">
         <v>3.451292</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" t="n">
         <v>3.678328</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" t="n">
         <v>3.91543</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K12" t="n">
         <v>4.163123</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" t="n">
         <v>4.421958</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" t="n">
         <v>4.69252</v>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="N12" t="n">
         <v>7.306516</v>
       </c>
-      <c r="O12" s="12" t="n">
+      <c r="O12" t="n">
         <v>7.74755</v>
       </c>
-      <c r="P12" s="12" t="n">
+      <c r="P12" t="n">
         <v>8.204561</v>
       </c>
-      <c r="Q12" s="12" t="n">
-        <v>8.678305999999999</v>
-      </c>
-      <c r="R12" s="12" t="n">
-        <v>9.169581000000001</v>
-      </c>
-      <c r="S12" s="12" t="n">
+      <c r="Q12" t="n">
+        <v>8.678306</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9.169581</v>
+      </c>
+      <c r="S12" t="n">
         <v>9.679228</v>
       </c>
-      <c r="T12" s="12" t="n">
+      <c r="T12" t="n">
         <v>10.208129</v>
       </c>
-      <c r="U12" s="12" t="n">
+      <c r="U12" t="n">
         <v>10.757215</v>
       </c>
-      <c r="V12" s="12" t="n">
+      <c r="V12" t="n">
         <v>11.327467</v>
       </c>
-      <c r="W12" s="12" t="n">
+      <c r="W12" t="n">
         <v>11.556094</v>
       </c>
-      <c r="X12" s="12" t="n">
+      <c r="X12" t="n">
         <v>11.787996</v>
       </c>
-      <c r="Y12" s="12" t="n">
+      <c r="Y12" t="n">
         <v>12.023217</v>
       </c>
-      <c r="Z12" s="12" t="n">
+      <c r="Z12" t="n">
         <v>12.261802</v>
       </c>
-      <c r="AA12" s="12" t="n">
+      <c r="AA12" t="n">
         <v>12.503796</v>
       </c>
-      <c r="AB12" s="12" t="n">
+      <c r="AB12" t="n">
         <v>12.749247</v>
       </c>
-      <c r="AC12" s="12" t="n">
+      <c r="AC12" t="n">
         <v>17.131103</v>
       </c>
-      <c r="AD12" s="12" t="n">
+      <c r="AD12" t="n">
         <v>17.383606</v>
       </c>
-      <c r="AE12" s="12" t="n">
+      <c r="AE12" t="n">
         <v>17.639707</v>
       </c>
-      <c r="AF12" s="12" t="n">
+      <c r="AF12" t="n">
         <v>17.899455</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>incomeStatement.taxExpense</t>
         </is>
@@ -2385,99 +2277,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12" t="n">
+      <c r="C13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.565147</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" t="n">
         <v>0.605091</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" t="n">
         <v>0.646765</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" t="n">
         <v>0.690258</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" t="n">
         <v>0.735666</v>
       </c>
-      <c r="J13" s="12" t="n">
-        <v>0.7830859999999999</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>0.8326249999999999</v>
-      </c>
-      <c r="L13" s="12" t="n">
+      <c r="J13" t="n">
+        <v>0.783086</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.832625</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.884392</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" t="n">
         <v>0.938504</v>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" t="n">
         <v>1.461303</v>
       </c>
-      <c r="O13" s="12" t="n">
+      <c r="O13" t="n">
         <v>1.54951</v>
       </c>
-      <c r="P13" s="12" t="n">
+      <c r="P13" t="n">
         <v>1.640912</v>
       </c>
-      <c r="Q13" s="12" t="n">
+      <c r="Q13" t="n">
         <v>1.735661</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" t="n">
         <v>1.833916</v>
       </c>
-      <c r="S13" s="12" t="n">
+      <c r="S13" t="n">
         <v>1.935846</v>
       </c>
-      <c r="T13" s="12" t="n">
+      <c r="T13" t="n">
         <v>2.041626</v>
       </c>
-      <c r="U13" s="12" t="n">
+      <c r="U13" t="n">
         <v>2.151443</v>
       </c>
-      <c r="V13" s="12" t="n">
+      <c r="V13" t="n">
         <v>2.265493</v>
       </c>
-      <c r="W13" s="12" t="n">
+      <c r="W13" t="n">
         <v>2.311219</v>
       </c>
-      <c r="X13" s="12" t="n">
+      <c r="X13" t="n">
         <v>2.357599</v>
       </c>
-      <c r="Y13" s="12" t="n">
+      <c r="Y13" t="n">
         <v>2.404643</v>
       </c>
-      <c r="Z13" s="12" t="n">
+      <c r="Z13" t="n">
         <v>2.45236</v>
       </c>
-      <c r="AA13" s="12" t="n">
+      <c r="AA13" t="n">
         <v>2.500759</v>
       </c>
-      <c r="AB13" s="12" t="n">
+      <c r="AB13" t="n">
         <v>2.549849</v>
       </c>
-      <c r="AC13" s="12" t="n">
+      <c r="AC13" t="n">
         <v>3.426221</v>
       </c>
-      <c r="AD13" s="12" t="n">
+      <c r="AD13" t="n">
         <v>3.476721</v>
       </c>
-      <c r="AE13" s="12" t="n">
+      <c r="AE13" t="n">
         <v>3.527941</v>
       </c>
-      <c r="AF13" s="12" t="n">
+      <c r="AF13" t="n">
         <v>3.579891</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>incomeStatement.netIncome</t>
         </is>
@@ -2487,137 +2379,106 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="n">
+      <c r="C14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D14" t="n">
         <v>-3.290048</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" t="n">
         <v>2.260589</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" t="n">
         <v>2.420364</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" t="n">
         <v>2.58706</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" t="n">
         <v>2.761034</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" t="n">
         <v>2.942663</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" t="n">
         <v>3.132344</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" t="n">
         <v>3.330498</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" t="n">
         <v>3.537567</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" t="n">
         <v>3.754016</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" t="n">
         <v>5.845213</v>
       </c>
-      <c r="O14" s="12" t="n">
+      <c r="O14" t="n">
         <v>6.19804</v>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P14" t="n">
         <v>6.563649</v>
       </c>
-      <c r="Q14" s="12" t="n">
+      <c r="Q14" t="n">
         <v>6.942645</v>
       </c>
-      <c r="R14" s="12" t="n">
+      <c r="R14" t="n">
         <v>7.335665</v>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" t="n">
         <v>7.743382</v>
       </c>
-      <c r="T14" s="12" t="n">
-        <v>8.166503000000001</v>
-      </c>
-      <c r="U14" s="12" t="n">
+      <c r="T14" t="n">
+        <v>8.166503</v>
+      </c>
+      <c r="U14" t="n">
         <v>8.605772</v>
       </c>
-      <c r="V14" s="12" t="n">
-        <v>9.061973999999999</v>
-      </c>
-      <c r="W14" s="12" t="n">
+      <c r="V14" t="n">
+        <v>9.061974</v>
+      </c>
+      <c r="W14" t="n">
         <v>9.244875</v>
       </c>
-      <c r="X14" s="12" t="n">
-        <v>9.430396999999999</v>
-      </c>
-      <c r="Y14" s="12" t="n">
+      <c r="X14" t="n">
+        <v>9.430397</v>
+      </c>
+      <c r="Y14" t="n">
         <v>9.618573</v>
       </c>
-      <c r="Z14" s="12" t="n">
+      <c r="Z14" t="n">
         <v>9.809441</v>
       </c>
-      <c r="AA14" s="12" t="n">
+      <c r="AA14" t="n">
         <v>10.003037</v>
       </c>
-      <c r="AB14" s="12" t="n">
+      <c r="AB14" t="n">
         <v>10.199398</v>
       </c>
-      <c r="AC14" s="12" t="n">
+      <c r="AC14" t="n">
         <v>13.704882</v>
       </c>
-      <c r="AD14" s="12" t="n">
+      <c r="AD14" t="n">
         <v>13.906885</v>
       </c>
-      <c r="AE14" s="12" t="n">
+      <c r="AE14" t="n">
         <v>14.111766</v>
       </c>
-      <c r="AF14" s="12" t="n">
+      <c r="AF14" t="n">
         <v>14.319564</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>cashFlow</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="9" t="n"/>
-      <c r="S15" s="9" t="n"/>
-      <c r="T15" s="9" t="n"/>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="9" t="n"/>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="9" t="n"/>
-      <c r="Z15" s="9" t="n"/>
-      <c r="AA15" s="9" t="n"/>
-      <c r="AB15" s="9" t="n"/>
-      <c r="AC15" s="9" t="n"/>
-      <c r="AD15" s="9" t="n"/>
-      <c r="AE15" s="9" t="n"/>
-      <c r="AF15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>cashFlow.interestPaid</t>
         </is>
@@ -2627,99 +2488,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12" t="n">
+      <c r="C16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="n">
         <v>4.091574</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" t="n">
         <v>3.952788</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" t="n">
         <v>3.806369</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" t="n">
         <v>3.651897</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" t="n">
         <v>3.488928</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" t="n">
         <v>3.316997</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" t="n">
         <v>3.13561</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" t="n">
         <v>2.944246</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" t="n">
         <v>2.742357</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" t="n">
         <v>2.529364</v>
       </c>
-      <c r="N16" s="12" t="n">
+      <c r="N16" t="n">
         <v>2.304657</v>
       </c>
-      <c r="O16" s="12" t="n">
+      <c r="O16" t="n">
         <v>2.067591</v>
       </c>
-      <c r="P16" s="12" t="n">
+      <c r="P16" t="n">
         <v>1.817486</v>
       </c>
-      <c r="Q16" s="12" t="n">
+      <c r="Q16" t="n">
         <v>1.553625</v>
       </c>
-      <c r="R16" s="12" t="n">
+      <c r="R16" t="n">
         <v>1.275252</v>
       </c>
-      <c r="S16" s="12" t="n">
+      <c r="S16" t="n">
         <v>0.981569</v>
       </c>
-      <c r="T16" s="12" t="n">
+      <c r="T16" t="n">
         <v>0.671732</v>
       </c>
-      <c r="U16" s="12" t="n">
+      <c r="U16" t="n">
         <v>0.344855</v>
       </c>
-      <c r="V16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="12" t="n">
-        <v>0</v>
+      <c r="V16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>cashFlow.debtRepayment</t>
         </is>
@@ -2729,99 +2590,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12" t="n">
+      <c r="C17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D17" t="n">
         <v>2.523379</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" t="n">
         <v>2.662165</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" t="n">
         <v>2.808584</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" t="n">
         <v>2.963056</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" t="n">
         <v>3.126024</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" t="n">
         <v>3.297955</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" t="n">
         <v>3.479343</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K17" t="n">
         <v>3.670706</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="L17" t="n">
         <v>3.872595</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" t="n">
         <v>4.085588</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" t="n">
         <v>4.310295</v>
       </c>
-      <c r="O17" s="12" t="n">
+      <c r="O17" t="n">
         <v>4.547362</v>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="P17" t="n">
         <v>4.797467</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="Q17" t="n">
         <v>5.061327</v>
       </c>
-      <c r="R17" s="12" t="n">
+      <c r="R17" t="n">
         <v>5.3397</v>
       </c>
-      <c r="S17" s="12" t="n">
+      <c r="S17" t="n">
         <v>5.633384</v>
       </c>
-      <c r="T17" s="12" t="n">
+      <c r="T17" t="n">
         <v>5.94322</v>
       </c>
-      <c r="U17" s="12" t="n">
+      <c r="U17" t="n">
         <v>6.270097</v>
       </c>
-      <c r="V17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="12" t="n">
-        <v>0</v>
+      <c r="V17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>cashFlow.taxPaid</t>
         </is>
@@ -2831,99 +2692,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12" t="n">
+      <c r="C18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.565147</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" t="n">
         <v>0.605091</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" t="n">
         <v>0.646765</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" t="n">
         <v>0.690258</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" t="n">
         <v>0.735666</v>
       </c>
-      <c r="J18" s="12" t="n">
-        <v>0.7830859999999999</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>0.8326249999999999</v>
-      </c>
-      <c r="L18" s="12" t="n">
+      <c r="J18" t="n">
+        <v>0.783086</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.832625</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.884392</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="M18" t="n">
         <v>0.938504</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" t="n">
         <v>1.461303</v>
       </c>
-      <c r="O18" s="12" t="n">
+      <c r="O18" t="n">
         <v>1.54951</v>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" t="n">
         <v>1.640912</v>
       </c>
-      <c r="Q18" s="12" t="n">
+      <c r="Q18" t="n">
         <v>1.735661</v>
       </c>
-      <c r="R18" s="12" t="n">
+      <c r="R18" t="n">
         <v>1.833916</v>
       </c>
-      <c r="S18" s="12" t="n">
+      <c r="S18" t="n">
         <v>1.935846</v>
       </c>
-      <c r="T18" s="12" t="n">
+      <c r="T18" t="n">
         <v>2.041626</v>
       </c>
-      <c r="U18" s="12" t="n">
+      <c r="U18" t="n">
         <v>2.151443</v>
       </c>
-      <c r="V18" s="12" t="n">
+      <c r="V18" t="n">
         <v>2.265493</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" t="n">
         <v>2.311219</v>
       </c>
-      <c r="X18" s="12" t="n">
+      <c r="X18" t="n">
         <v>2.357599</v>
       </c>
-      <c r="Y18" s="12" t="n">
+      <c r="Y18" t="n">
         <v>2.404643</v>
       </c>
-      <c r="Z18" s="12" t="n">
+      <c r="Z18" t="n">
         <v>2.45236</v>
       </c>
-      <c r="AA18" s="12" t="n">
+      <c r="AA18" t="n">
         <v>2.500759</v>
       </c>
-      <c r="AB18" s="12" t="n">
+      <c r="AB18" t="n">
         <v>2.549849</v>
       </c>
-      <c r="AC18" s="12" t="n">
+      <c r="AC18" t="n">
         <v>3.426221</v>
       </c>
-      <c r="AD18" s="12" t="n">
+      <c r="AD18" t="n">
         <v>3.476721</v>
       </c>
-      <c r="AE18" s="12" t="n">
+      <c r="AE18" t="n">
         <v>3.527941</v>
       </c>
-      <c r="AF18" s="12" t="n">
+      <c r="AF18" t="n">
         <v>3.579891</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>cashFlow.capex</t>
         </is>
@@ -2933,99 +2794,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" t="n">
         <v>28.930318</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" t="n">
         <v>74.392246</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="12" t="n">
-        <v>0</v>
+      <c r="E19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>cashFlow.debtDrawdown</t>
         </is>
@@ -3035,99 +2896,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12" t="n">
+      <c r="C20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D20" t="n">
         <v>74.392246</v>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12" t="n">
-        <v>0</v>
+      <c r="E20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>cashFlow.equityDrawdown</t>
         </is>
@@ -3137,99 +2998,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" t="n">
         <v>28.930318</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12" t="n">
-        <v>0</v>
+      <c r="D21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>cashFlow.fcfe</t>
         </is>
@@ -3239,137 +3100,106 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" t="n">
         <v>-28.930318</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" t="n">
         <v>-1.680524</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" t="n">
         <v>3.731327</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" t="n">
         <v>3.744683</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" t="n">
         <v>3.756907</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" t="n">
         <v>3.767912</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" t="n">
         <v>3.77761</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" t="n">
         <v>3.785904</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="K22" t="n">
         <v>3.792694</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="L22" t="n">
         <v>3.797874</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="M22" t="n">
         <v>3.80133</v>
       </c>
-      <c r="N22" s="12" t="n">
+      <c r="N22" t="n">
         <v>5.66782</v>
       </c>
-      <c r="O22" s="12" t="n">
+      <c r="O22" t="n">
         <v>5.783581</v>
       </c>
-      <c r="P22" s="12" t="n">
+      <c r="P22" t="n">
         <v>5.899085</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" t="n">
         <v>6.01422</v>
       </c>
-      <c r="R22" s="12" t="n">
+      <c r="R22" t="n">
         <v>6.128867</v>
       </c>
-      <c r="S22" s="12" t="n">
+      <c r="S22" t="n">
         <v>6.242901</v>
       </c>
-      <c r="T22" s="12" t="n">
+      <c r="T22" t="n">
         <v>6.356186</v>
       </c>
-      <c r="U22" s="12" t="n">
+      <c r="U22" t="n">
         <v>6.468578</v>
       </c>
-      <c r="V22" s="12" t="n">
+      <c r="V22" t="n">
         <v>13.194876</v>
       </c>
-      <c r="W22" s="12" t="n">
+      <c r="W22" t="n">
         <v>13.377778</v>
       </c>
-      <c r="X22" s="12" t="n">
+      <c r="X22" t="n">
         <v>13.563299</v>
       </c>
-      <c r="Y22" s="12" t="n">
+      <c r="Y22" t="n">
         <v>13.751476</v>
       </c>
-      <c r="Z22" s="12" t="n">
+      <c r="Z22" t="n">
         <v>13.942344</v>
       </c>
-      <c r="AA22" s="12" t="n">
+      <c r="AA22" t="n">
         <v>14.13594</v>
       </c>
-      <c r="AB22" s="12" t="n">
+      <c r="AB22" t="n">
         <v>14.3323</v>
       </c>
-      <c r="AC22" s="12" t="n">
+      <c r="AC22" t="n">
         <v>13.704882</v>
       </c>
-      <c r="AD22" s="12" t="n">
+      <c r="AD22" t="n">
         <v>13.906885</v>
       </c>
-      <c r="AE22" s="12" t="n">
+      <c r="AE22" t="n">
         <v>14.111766</v>
       </c>
-      <c r="AF22" s="12" t="n">
+      <c r="AF22" t="n">
         <v>14.319564</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>debtSchedule</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
-      <c r="O23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="9" t="n"/>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="9" t="n"/>
-      <c r="U23" s="9" t="n"/>
-      <c r="V23" s="9" t="n"/>
-      <c r="W23" s="9" t="n"/>
-      <c r="X23" s="9" t="n"/>
-      <c r="Y23" s="9" t="n"/>
-      <c r="Z23" s="9" t="n"/>
-      <c r="AA23" s="9" t="n"/>
-      <c r="AB23" s="9" t="n"/>
-      <c r="AC23" s="9" t="n"/>
-      <c r="AD23" s="9" t="n"/>
-      <c r="AE23" s="9" t="n"/>
-      <c r="AF23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>debtSchedule.opening</t>
         </is>
@@ -3379,99 +3209,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>71.86886699999999</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>69.20670200000001</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>66.39811899999999</v>
-      </c>
-      <c r="H24" s="12" t="n">
+      <c r="C24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>71.868867</v>
+      </c>
+      <c r="F24" t="n">
+        <v>69.206702</v>
+      </c>
+      <c r="G24" t="n">
+        <v>66.398119</v>
+      </c>
+      <c r="H24" t="n">
         <v>63.435063</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" t="n">
         <v>60.309039</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" t="n">
         <v>57.011084</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="K24" t="n">
         <v>53.531741</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="L24" t="n">
         <v>49.861035</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="M24" t="n">
         <v>45.98844</v>
       </c>
-      <c r="N24" s="12" t="n">
+      <c r="N24" t="n">
         <v>41.902852</v>
       </c>
-      <c r="O24" s="12" t="n">
+      <c r="O24" t="n">
         <v>37.592556</v>
       </c>
-      <c r="P24" s="12" t="n">
+      <c r="P24" t="n">
         <v>33.045194</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" t="n">
         <v>28.247728</v>
       </c>
-      <c r="R24" s="12" t="n">
+      <c r="R24" t="n">
         <v>23.186401</v>
       </c>
-      <c r="S24" s="12" t="n">
+      <c r="S24" t="n">
         <v>17.8467</v>
       </c>
-      <c r="T24" s="12" t="n">
+      <c r="T24" t="n">
         <v>12.213317</v>
       </c>
-      <c r="U24" s="12" t="n">
+      <c r="U24" t="n">
         <v>6.270097</v>
       </c>
-      <c r="V24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="12" t="n">
-        <v>0</v>
+      <c r="V24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>debtSchedule.drawdown</t>
         </is>
@@ -3481,99 +3311,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="12" t="n">
+      <c r="C25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D25" t="n">
         <v>74.392246</v>
       </c>
-      <c r="E25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="12" t="n">
-        <v>0</v>
+      <c r="E25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>debtSchedule.repayment</t>
         </is>
@@ -3583,99 +3413,99 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="12" t="n">
+      <c r="C26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D26" t="n">
         <v>2.523379</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" t="n">
         <v>2.662165</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" t="n">
         <v>2.808584</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" t="n">
         <v>2.963056</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" t="n">
         <v>3.126024</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" t="n">
         <v>3.297955</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" t="n">
         <v>3.479343</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="K26" t="n">
         <v>3.670706</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="L26" t="n">
         <v>3.872595</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="M26" t="n">
         <v>4.085588</v>
       </c>
-      <c r="N26" s="12" t="n">
+      <c r="N26" t="n">
         <v>4.310295</v>
       </c>
-      <c r="O26" s="12" t="n">
+      <c r="O26" t="n">
         <v>4.547362</v>
       </c>
-      <c r="P26" s="12" t="n">
+      <c r="P26" t="n">
         <v>4.797467</v>
       </c>
-      <c r="Q26" s="12" t="n">
+      <c r="Q26" t="n">
         <v>5.061327</v>
       </c>
-      <c r="R26" s="12" t="n">
+      <c r="R26" t="n">
         <v>5.3397</v>
       </c>
-      <c r="S26" s="12" t="n">
+      <c r="S26" t="n">
         <v>5.633384</v>
       </c>
-      <c r="T26" s="12" t="n">
+      <c r="T26" t="n">
         <v>5.94322</v>
       </c>
-      <c r="U26" s="12" t="n">
+      <c r="U26" t="n">
         <v>6.270097</v>
       </c>
-      <c r="V26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="12" t="n">
-        <v>0</v>
+      <c r="V26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>debtSchedule.closing</t>
         </is>
@@ -3685,137 +3515,106 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>71.86886699999999</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>69.20670200000001</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>66.39811899999999</v>
-      </c>
-      <c r="G27" s="12" t="n">
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>71.868867</v>
+      </c>
+      <c r="E27" t="n">
+        <v>69.206702</v>
+      </c>
+      <c r="F27" t="n">
+        <v>66.398119</v>
+      </c>
+      <c r="G27" t="n">
         <v>63.435063</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H27" t="n">
         <v>60.309039</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="I27" t="n">
         <v>57.011084</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="J27" t="n">
         <v>53.531741</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="K27" t="n">
         <v>49.861035</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="L27" t="n">
         <v>45.98844</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="M27" t="n">
         <v>41.902852</v>
       </c>
-      <c r="N27" s="12" t="n">
+      <c r="N27" t="n">
         <v>37.592556</v>
       </c>
-      <c r="O27" s="12" t="n">
+      <c r="O27" t="n">
         <v>33.045194</v>
       </c>
-      <c r="P27" s="12" t="n">
+      <c r="P27" t="n">
         <v>28.247728</v>
       </c>
-      <c r="Q27" s="12" t="n">
+      <c r="Q27" t="n">
         <v>23.186401</v>
       </c>
-      <c r="R27" s="12" t="n">
+      <c r="R27" t="n">
         <v>17.8467</v>
       </c>
-      <c r="S27" s="12" t="n">
+      <c r="S27" t="n">
         <v>12.213317</v>
       </c>
-      <c r="T27" s="12" t="n">
+      <c r="T27" t="n">
         <v>6.270097</v>
       </c>
-      <c r="U27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="12" t="n">
-        <v>0</v>
+      <c r="U27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>balanceSheet</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
-      <c r="O28" s="9" t="n"/>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="9" t="n"/>
-      <c r="S28" s="9" t="n"/>
-      <c r="T28" s="9" t="n"/>
-      <c r="U28" s="9" t="n"/>
-      <c r="V28" s="9" t="n"/>
-      <c r="W28" s="9" t="n"/>
-      <c r="X28" s="9" t="n"/>
-      <c r="Y28" s="9" t="n"/>
-      <c r="Z28" s="9" t="n"/>
-      <c r="AA28" s="9" t="n"/>
-      <c r="AB28" s="9" t="n"/>
-      <c r="AC28" s="9" t="n"/>
-      <c r="AD28" s="9" t="n"/>
-      <c r="AE28" s="9" t="n"/>
-      <c r="AF28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>balanceSheet.ppe</t>
         </is>
@@ -3825,137 +3624,106 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" t="n">
         <v>28.930318</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" t="n">
         <v>99.189661</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" t="n">
         <v>95.056758</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" t="n">
         <v>90.923856</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" t="n">
         <v>86.790953</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="H29" t="n">
         <v>82.658051</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I29" t="n">
         <v>78.525148</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J29" t="n">
         <v>74.392246</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="K29" t="n">
         <v>70.259343</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="L29" t="n">
         <v>66.126441</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M29" t="n">
         <v>61.993538</v>
       </c>
-      <c r="N29" s="12" t="n">
+      <c r="N29" t="n">
         <v>57.860635</v>
       </c>
-      <c r="O29" s="12" t="n">
+      <c r="O29" t="n">
         <v>53.727733</v>
       </c>
-      <c r="P29" s="12" t="n">
+      <c r="P29" t="n">
         <v>49.59483</v>
       </c>
-      <c r="Q29" s="12" t="n">
+      <c r="Q29" t="n">
         <v>45.461928</v>
       </c>
-      <c r="R29" s="12" t="n">
+      <c r="R29" t="n">
         <v>41.329025</v>
       </c>
-      <c r="S29" s="12" t="n">
+      <c r="S29" t="n">
         <v>37.196123</v>
       </c>
-      <c r="T29" s="12" t="n">
+      <c r="T29" t="n">
         <v>33.06322</v>
       </c>
-      <c r="U29" s="12" t="n">
+      <c r="U29" t="n">
         <v>28.930318</v>
       </c>
-      <c r="V29" s="12" t="n">
+      <c r="V29" t="n">
         <v>24.797415</v>
       </c>
-      <c r="W29" s="12" t="n">
+      <c r="W29" t="n">
         <v>20.664513</v>
       </c>
-      <c r="X29" s="12" t="n">
+      <c r="X29" t="n">
         <v>16.53161</v>
       </c>
-      <c r="Y29" s="12" t="n">
+      <c r="Y29" t="n">
         <v>12.398708</v>
       </c>
-      <c r="Z29" s="12" t="n">
+      <c r="Z29" t="n">
         <v>8.265805</v>
       </c>
-      <c r="AA29" s="12" t="n">
+      <c r="AA29" t="n">
         <v>4.132903</v>
       </c>
-      <c r="AB29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="12" t="n">
-        <v>0</v>
+      <c r="AB29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ratios</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="9" t="n"/>
-      <c r="S30" s="9" t="n"/>
-      <c r="T30" s="9" t="n"/>
-      <c r="U30" s="9" t="n"/>
-      <c r="V30" s="9" t="n"/>
-      <c r="W30" s="9" t="n"/>
-      <c r="X30" s="9" t="n"/>
-      <c r="Y30" s="9" t="n"/>
-      <c r="Z30" s="9" t="n"/>
-      <c r="AA30" s="9" t="n"/>
-      <c r="AB30" s="9" t="n"/>
-      <c r="AC30" s="9" t="n"/>
-      <c r="AD30" s="9" t="n"/>
-      <c r="AE30" s="9" t="n"/>
-      <c r="AF30" s="9" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>ratios.dscr</t>
         </is>
@@ -3965,75 +3733,63 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n">
+      <c r="D31" t="n">
         <v>0.745951</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" t="n">
         <v>1.64951</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" t="n">
         <v>1.657567</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" t="n">
         <v>1.665715</v>
       </c>
-      <c r="H31" s="11" t="n">
+      <c r="H31" t="n">
         <v>1.673954</v>
       </c>
-      <c r="I31" s="11" t="n">
+      <c r="I31" t="n">
         <v>1.682284</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J31" t="n">
         <v>1.690706</v>
       </c>
-      <c r="K31" s="11" t="n">
+      <c r="K31" t="n">
         <v>1.699222</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L31" t="n">
         <v>1.707831</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="M31" t="n">
         <v>1.716533</v>
       </c>
-      <c r="N31" s="11" t="n">
+      <c r="N31" t="n">
         <v>2.077729</v>
       </c>
-      <c r="O31" s="11" t="n">
+      <c r="O31" t="n">
         <v>2.108563</v>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" t="n">
         <v>2.139841</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" t="n">
         <v>2.17157</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" t="n">
         <v>2.203755</v>
       </c>
-      <c r="S31" s="11" t="n">
+      <c r="S31" t="n">
         <v>2.236403</v>
       </c>
-      <c r="T31" s="11" t="n">
+      <c r="T31" t="n">
         <v>2.26952</v>
       </c>
-      <c r="U31" s="11" t="n">
+      <c r="U31" t="n">
         <v>2.303112</v>
       </c>
-      <c r="V31" s="11" t="n"/>
-      <c r="W31" s="11" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="11" t="n"/>
-      <c r="Z31" s="11" t="n"/>
-      <c r="AA31" s="11" t="n"/>
-      <c r="AB31" s="11" t="n"/>
-      <c r="AC31" s="11" t="n"/>
-      <c r="AD31" s="11" t="n"/>
-      <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>An empty dscr cell means null: dscr is defined only inside the debt life. Every other cell is a number.</t>
         </is>
@@ -4052,156 +3808,121 @@
   </sheetPr>
   <dimension ref="A1:AG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>max breach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" s="7" t="n">
+      <c r="D1" t="n">
         <v>2027</v>
       </c>
-      <c r="E1" s="7" t="n">
+      <c r="E1" t="n">
         <v>2028</v>
       </c>
-      <c r="F1" s="7" t="n">
+      <c r="F1" t="n">
         <v>2029</v>
       </c>
-      <c r="G1" s="7" t="n">
+      <c r="G1" t="n">
         <v>2030</v>
       </c>
-      <c r="H1" s="7" t="n">
+      <c r="H1" t="n">
         <v>2031</v>
       </c>
-      <c r="I1" s="7" t="n">
+      <c r="I1" t="n">
         <v>2032</v>
       </c>
-      <c r="J1" s="7" t="n">
+      <c r="J1" t="n">
         <v>2033</v>
       </c>
-      <c r="K1" s="7" t="n">
+      <c r="K1" t="n">
         <v>2034</v>
       </c>
-      <c r="L1" s="7" t="n">
+      <c r="L1" t="n">
         <v>2035</v>
       </c>
-      <c r="M1" s="7" t="n">
+      <c r="M1" t="n">
         <v>2036</v>
       </c>
-      <c r="N1" s="7" t="n">
+      <c r="N1" t="n">
         <v>2037</v>
       </c>
-      <c r="O1" s="7" t="n">
+      <c r="O1" t="n">
         <v>2038</v>
       </c>
-      <c r="P1" s="7" t="n">
+      <c r="P1" t="n">
         <v>2039</v>
       </c>
-      <c r="Q1" s="7" t="n">
+      <c r="Q1" t="n">
         <v>2040</v>
       </c>
-      <c r="R1" s="7" t="n">
+      <c r="R1" t="n">
         <v>2041</v>
       </c>
-      <c r="S1" s="7" t="n">
+      <c r="S1" t="n">
         <v>2042</v>
       </c>
-      <c r="T1" s="7" t="n">
+      <c r="T1" t="n">
         <v>2043</v>
       </c>
-      <c r="U1" s="7" t="n">
+      <c r="U1" t="n">
         <v>2044</v>
       </c>
-      <c r="V1" s="7" t="n">
+      <c r="V1" t="n">
         <v>2045</v>
       </c>
-      <c r="W1" s="7" t="n">
+      <c r="W1" t="n">
         <v>2046</v>
       </c>
-      <c r="X1" s="7" t="n">
+      <c r="X1" t="n">
         <v>2047</v>
       </c>
-      <c r="Y1" s="7" t="n">
+      <c r="Y1" t="n">
         <v>2048</v>
       </c>
-      <c r="Z1" s="7" t="n">
+      <c r="Z1" t="n">
         <v>2049</v>
       </c>
-      <c r="AA1" s="7" t="n">
+      <c r="AA1" t="n">
         <v>2050</v>
       </c>
-      <c r="AB1" s="7" t="n">
+      <c r="AB1" t="n">
         <v>2051</v>
       </c>
-      <c r="AC1" s="7" t="n">
+      <c r="AC1" t="n">
         <v>2052</v>
       </c>
-      <c r="AD1" s="7" t="n">
+      <c r="AD1" t="n">
         <v>2053</v>
       </c>
-      <c r="AE1" s="7" t="n">
+      <c r="AE1" t="n">
         <v>2054</v>
       </c>
-      <c r="AF1" s="7" t="n">
+      <c r="AF1" t="n">
         <v>2055</v>
       </c>
-      <c r="AG1" s="7" t="n">
+      <c r="AG1" t="n">
         <v>2056</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ebitda = revenue - opex</t>
         </is>
       </c>
-      <c r="B2" s="13">
+      <c r="B2">
         <f>MAX(D2:AG2)</f>
         <v/>
       </c>
@@ -4209,134 +3930,134 @@
         <f>IF(B2=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D2" s="13">
+      <c r="D2">
         <f>MAX(0,ABS(Statements!C8-(Statements!C6-Statements!C7))-MAX(0.01,0.001*ABS(Statements!C8)))</f>
         <v/>
       </c>
-      <c r="E2" s="13">
+      <c r="E2">
         <f>MAX(0,ABS(Statements!D8-(Statements!D6-Statements!D7))-MAX(0.01,0.001*ABS(Statements!D8)))</f>
         <v/>
       </c>
-      <c r="F2" s="13">
+      <c r="F2">
         <f>MAX(0,ABS(Statements!E8-(Statements!E6-Statements!E7))-MAX(0.01,0.001*ABS(Statements!E8)))</f>
         <v/>
       </c>
-      <c r="G2" s="13">
+      <c r="G2">
         <f>MAX(0,ABS(Statements!F8-(Statements!F6-Statements!F7))-MAX(0.01,0.001*ABS(Statements!F8)))</f>
         <v/>
       </c>
-      <c r="H2" s="13">
+      <c r="H2">
         <f>MAX(0,ABS(Statements!G8-(Statements!G6-Statements!G7))-MAX(0.01,0.001*ABS(Statements!G8)))</f>
         <v/>
       </c>
-      <c r="I2" s="13">
+      <c r="I2">
         <f>MAX(0,ABS(Statements!H8-(Statements!H6-Statements!H7))-MAX(0.01,0.001*ABS(Statements!H8)))</f>
         <v/>
       </c>
-      <c r="J2" s="13">
+      <c r="J2">
         <f>MAX(0,ABS(Statements!I8-(Statements!I6-Statements!I7))-MAX(0.01,0.001*ABS(Statements!I8)))</f>
         <v/>
       </c>
-      <c r="K2" s="13">
+      <c r="K2">
         <f>MAX(0,ABS(Statements!J8-(Statements!J6-Statements!J7))-MAX(0.01,0.001*ABS(Statements!J8)))</f>
         <v/>
       </c>
-      <c r="L2" s="13">
+      <c r="L2">
         <f>MAX(0,ABS(Statements!K8-(Statements!K6-Statements!K7))-MAX(0.01,0.001*ABS(Statements!K8)))</f>
         <v/>
       </c>
-      <c r="M2" s="13">
+      <c r="M2">
         <f>MAX(0,ABS(Statements!L8-(Statements!L6-Statements!L7))-MAX(0.01,0.001*ABS(Statements!L8)))</f>
         <v/>
       </c>
-      <c r="N2" s="13">
+      <c r="N2">
         <f>MAX(0,ABS(Statements!M8-(Statements!M6-Statements!M7))-MAX(0.01,0.001*ABS(Statements!M8)))</f>
         <v/>
       </c>
-      <c r="O2" s="13">
+      <c r="O2">
         <f>MAX(0,ABS(Statements!N8-(Statements!N6-Statements!N7))-MAX(0.01,0.001*ABS(Statements!N8)))</f>
         <v/>
       </c>
-      <c r="P2" s="13">
+      <c r="P2">
         <f>MAX(0,ABS(Statements!O8-(Statements!O6-Statements!O7))-MAX(0.01,0.001*ABS(Statements!O8)))</f>
         <v/>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2">
         <f>MAX(0,ABS(Statements!P8-(Statements!P6-Statements!P7))-MAX(0.01,0.001*ABS(Statements!P8)))</f>
         <v/>
       </c>
-      <c r="R2" s="13">
+      <c r="R2">
         <f>MAX(0,ABS(Statements!Q8-(Statements!Q6-Statements!Q7))-MAX(0.01,0.001*ABS(Statements!Q8)))</f>
         <v/>
       </c>
-      <c r="S2" s="13">
+      <c r="S2">
         <f>MAX(0,ABS(Statements!R8-(Statements!R6-Statements!R7))-MAX(0.01,0.001*ABS(Statements!R8)))</f>
         <v/>
       </c>
-      <c r="T2" s="13">
+      <c r="T2">
         <f>MAX(0,ABS(Statements!S8-(Statements!S6-Statements!S7))-MAX(0.01,0.001*ABS(Statements!S8)))</f>
         <v/>
       </c>
-      <c r="U2" s="13">
+      <c r="U2">
         <f>MAX(0,ABS(Statements!T8-(Statements!T6-Statements!T7))-MAX(0.01,0.001*ABS(Statements!T8)))</f>
         <v/>
       </c>
-      <c r="V2" s="13">
+      <c r="V2">
         <f>MAX(0,ABS(Statements!U8-(Statements!U6-Statements!U7))-MAX(0.01,0.001*ABS(Statements!U8)))</f>
         <v/>
       </c>
-      <c r="W2" s="13">
+      <c r="W2">
         <f>MAX(0,ABS(Statements!V8-(Statements!V6-Statements!V7))-MAX(0.01,0.001*ABS(Statements!V8)))</f>
         <v/>
       </c>
-      <c r="X2" s="13">
+      <c r="X2">
         <f>MAX(0,ABS(Statements!W8-(Statements!W6-Statements!W7))-MAX(0.01,0.001*ABS(Statements!W8)))</f>
         <v/>
       </c>
-      <c r="Y2" s="13">
+      <c r="Y2">
         <f>MAX(0,ABS(Statements!X8-(Statements!X6-Statements!X7))-MAX(0.01,0.001*ABS(Statements!X8)))</f>
         <v/>
       </c>
-      <c r="Z2" s="13">
+      <c r="Z2">
         <f>MAX(0,ABS(Statements!Y8-(Statements!Y6-Statements!Y7))-MAX(0.01,0.001*ABS(Statements!Y8)))</f>
         <v/>
       </c>
-      <c r="AA2" s="13">
+      <c r="AA2">
         <f>MAX(0,ABS(Statements!Z8-(Statements!Z6-Statements!Z7))-MAX(0.01,0.001*ABS(Statements!Z8)))</f>
         <v/>
       </c>
-      <c r="AB2" s="13">
+      <c r="AB2">
         <f>MAX(0,ABS(Statements!AA8-(Statements!AA6-Statements!AA7))-MAX(0.01,0.001*ABS(Statements!AA8)))</f>
         <v/>
       </c>
-      <c r="AC2" s="13">
+      <c r="AC2">
         <f>MAX(0,ABS(Statements!AB8-(Statements!AB6-Statements!AB7))-MAX(0.01,0.001*ABS(Statements!AB8)))</f>
         <v/>
       </c>
-      <c r="AD2" s="13">
+      <c r="AD2">
         <f>MAX(0,ABS(Statements!AC8-(Statements!AC6-Statements!AC7))-MAX(0.01,0.001*ABS(Statements!AC8)))</f>
         <v/>
       </c>
-      <c r="AE2" s="13">
+      <c r="AE2">
         <f>MAX(0,ABS(Statements!AD8-(Statements!AD6-Statements!AD7))-MAX(0.01,0.001*ABS(Statements!AD8)))</f>
         <v/>
       </c>
-      <c r="AF2" s="13">
+      <c r="AF2">
         <f>MAX(0,ABS(Statements!AE8-(Statements!AE6-Statements!AE7))-MAX(0.01,0.001*ABS(Statements!AE8)))</f>
         <v/>
       </c>
-      <c r="AG2" s="13">
+      <c r="AG2">
         <f>MAX(0,ABS(Statements!AF8-(Statements!AF6-Statements!AF7))-MAX(0.01,0.001*ABS(Statements!AF8)))</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ebit = ebitda - depreciation</t>
         </is>
       </c>
-      <c r="B3" s="13">
+      <c r="B3">
         <f>MAX(D3:AG3)</f>
         <v/>
       </c>
@@ -4344,134 +4065,134 @@
         <f>IF(B3=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D3" s="13">
+      <c r="D3">
         <f>MAX(0,ABS(Statements!C10-(Statements!C8-Statements!C9))-MAX(0.01,0.001*ABS(Statements!C10)))</f>
         <v/>
       </c>
-      <c r="E3" s="13">
+      <c r="E3">
         <f>MAX(0,ABS(Statements!D10-(Statements!D8-Statements!D9))-MAX(0.01,0.001*ABS(Statements!D10)))</f>
         <v/>
       </c>
-      <c r="F3" s="13">
+      <c r="F3">
         <f>MAX(0,ABS(Statements!E10-(Statements!E8-Statements!E9))-MAX(0.01,0.001*ABS(Statements!E10)))</f>
         <v/>
       </c>
-      <c r="G3" s="13">
+      <c r="G3">
         <f>MAX(0,ABS(Statements!F10-(Statements!F8-Statements!F9))-MAX(0.01,0.001*ABS(Statements!F10)))</f>
         <v/>
       </c>
-      <c r="H3" s="13">
+      <c r="H3">
         <f>MAX(0,ABS(Statements!G10-(Statements!G8-Statements!G9))-MAX(0.01,0.001*ABS(Statements!G10)))</f>
         <v/>
       </c>
-      <c r="I3" s="13">
+      <c r="I3">
         <f>MAX(0,ABS(Statements!H10-(Statements!H8-Statements!H9))-MAX(0.01,0.001*ABS(Statements!H10)))</f>
         <v/>
       </c>
-      <c r="J3" s="13">
+      <c r="J3">
         <f>MAX(0,ABS(Statements!I10-(Statements!I8-Statements!I9))-MAX(0.01,0.001*ABS(Statements!I10)))</f>
         <v/>
       </c>
-      <c r="K3" s="13">
+      <c r="K3">
         <f>MAX(0,ABS(Statements!J10-(Statements!J8-Statements!J9))-MAX(0.01,0.001*ABS(Statements!J10)))</f>
         <v/>
       </c>
-      <c r="L3" s="13">
+      <c r="L3">
         <f>MAX(0,ABS(Statements!K10-(Statements!K8-Statements!K9))-MAX(0.01,0.001*ABS(Statements!K10)))</f>
         <v/>
       </c>
-      <c r="M3" s="13">
+      <c r="M3">
         <f>MAX(0,ABS(Statements!L10-(Statements!L8-Statements!L9))-MAX(0.01,0.001*ABS(Statements!L10)))</f>
         <v/>
       </c>
-      <c r="N3" s="13">
+      <c r="N3">
         <f>MAX(0,ABS(Statements!M10-(Statements!M8-Statements!M9))-MAX(0.01,0.001*ABS(Statements!M10)))</f>
         <v/>
       </c>
-      <c r="O3" s="13">
+      <c r="O3">
         <f>MAX(0,ABS(Statements!N10-(Statements!N8-Statements!N9))-MAX(0.01,0.001*ABS(Statements!N10)))</f>
         <v/>
       </c>
-      <c r="P3" s="13">
+      <c r="P3">
         <f>MAX(0,ABS(Statements!O10-(Statements!O8-Statements!O9))-MAX(0.01,0.001*ABS(Statements!O10)))</f>
         <v/>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3">
         <f>MAX(0,ABS(Statements!P10-(Statements!P8-Statements!P9))-MAX(0.01,0.001*ABS(Statements!P10)))</f>
         <v/>
       </c>
-      <c r="R3" s="13">
+      <c r="R3">
         <f>MAX(0,ABS(Statements!Q10-(Statements!Q8-Statements!Q9))-MAX(0.01,0.001*ABS(Statements!Q10)))</f>
         <v/>
       </c>
-      <c r="S3" s="13">
+      <c r="S3">
         <f>MAX(0,ABS(Statements!R10-(Statements!R8-Statements!R9))-MAX(0.01,0.001*ABS(Statements!R10)))</f>
         <v/>
       </c>
-      <c r="T3" s="13">
+      <c r="T3">
         <f>MAX(0,ABS(Statements!S10-(Statements!S8-Statements!S9))-MAX(0.01,0.001*ABS(Statements!S10)))</f>
         <v/>
       </c>
-      <c r="U3" s="13">
+      <c r="U3">
         <f>MAX(0,ABS(Statements!T10-(Statements!T8-Statements!T9))-MAX(0.01,0.001*ABS(Statements!T10)))</f>
         <v/>
       </c>
-      <c r="V3" s="13">
+      <c r="V3">
         <f>MAX(0,ABS(Statements!U10-(Statements!U8-Statements!U9))-MAX(0.01,0.001*ABS(Statements!U10)))</f>
         <v/>
       </c>
-      <c r="W3" s="13">
+      <c r="W3">
         <f>MAX(0,ABS(Statements!V10-(Statements!V8-Statements!V9))-MAX(0.01,0.001*ABS(Statements!V10)))</f>
         <v/>
       </c>
-      <c r="X3" s="13">
+      <c r="X3">
         <f>MAX(0,ABS(Statements!W10-(Statements!W8-Statements!W9))-MAX(0.01,0.001*ABS(Statements!W10)))</f>
         <v/>
       </c>
-      <c r="Y3" s="13">
+      <c r="Y3">
         <f>MAX(0,ABS(Statements!X10-(Statements!X8-Statements!X9))-MAX(0.01,0.001*ABS(Statements!X10)))</f>
         <v/>
       </c>
-      <c r="Z3" s="13">
+      <c r="Z3">
         <f>MAX(0,ABS(Statements!Y10-(Statements!Y8-Statements!Y9))-MAX(0.01,0.001*ABS(Statements!Y10)))</f>
         <v/>
       </c>
-      <c r="AA3" s="13">
+      <c r="AA3">
         <f>MAX(0,ABS(Statements!Z10-(Statements!Z8-Statements!Z9))-MAX(0.01,0.001*ABS(Statements!Z10)))</f>
         <v/>
       </c>
-      <c r="AB3" s="13">
+      <c r="AB3">
         <f>MAX(0,ABS(Statements!AA10-(Statements!AA8-Statements!AA9))-MAX(0.01,0.001*ABS(Statements!AA10)))</f>
         <v/>
       </c>
-      <c r="AC3" s="13">
+      <c r="AC3">
         <f>MAX(0,ABS(Statements!AB10-(Statements!AB8-Statements!AB9))-MAX(0.01,0.001*ABS(Statements!AB10)))</f>
         <v/>
       </c>
-      <c r="AD3" s="13">
+      <c r="AD3">
         <f>MAX(0,ABS(Statements!AC10-(Statements!AC8-Statements!AC9))-MAX(0.01,0.001*ABS(Statements!AC10)))</f>
         <v/>
       </c>
-      <c r="AE3" s="13">
+      <c r="AE3">
         <f>MAX(0,ABS(Statements!AD10-(Statements!AD8-Statements!AD9))-MAX(0.01,0.001*ABS(Statements!AD10)))</f>
         <v/>
       </c>
-      <c r="AF3" s="13">
+      <c r="AF3">
         <f>MAX(0,ABS(Statements!AE10-(Statements!AE8-Statements!AE9))-MAX(0.01,0.001*ABS(Statements!AE10)))</f>
         <v/>
       </c>
-      <c r="AG3" s="13">
+      <c r="AG3">
         <f>MAX(0,ABS(Statements!AF10-(Statements!AF8-Statements!AF9))-MAX(0.01,0.001*ABS(Statements!AF10)))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>pbt = ebit - interestExpense</t>
         </is>
       </c>
-      <c r="B4" s="13">
+      <c r="B4">
         <f>MAX(D4:AG4)</f>
         <v/>
       </c>
@@ -4479,134 +4200,134 @@
         <f>IF(B4=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D4" s="13">
+      <c r="D4">
         <f>MAX(0,ABS(Statements!C12-(Statements!C10-Statements!C11))-MAX(0.01,0.001*ABS(Statements!C12)))</f>
         <v/>
       </c>
-      <c r="E4" s="13">
+      <c r="E4">
         <f>MAX(0,ABS(Statements!D12-(Statements!D10-Statements!D11))-MAX(0.01,0.001*ABS(Statements!D12)))</f>
         <v/>
       </c>
-      <c r="F4" s="13">
+      <c r="F4">
         <f>MAX(0,ABS(Statements!E12-(Statements!E10-Statements!E11))-MAX(0.01,0.001*ABS(Statements!E12)))</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4">
         <f>MAX(0,ABS(Statements!F12-(Statements!F10-Statements!F11))-MAX(0.01,0.001*ABS(Statements!F12)))</f>
         <v/>
       </c>
-      <c r="H4" s="13">
+      <c r="H4">
         <f>MAX(0,ABS(Statements!G12-(Statements!G10-Statements!G11))-MAX(0.01,0.001*ABS(Statements!G12)))</f>
         <v/>
       </c>
-      <c r="I4" s="13">
+      <c r="I4">
         <f>MAX(0,ABS(Statements!H12-(Statements!H10-Statements!H11))-MAX(0.01,0.001*ABS(Statements!H12)))</f>
         <v/>
       </c>
-      <c r="J4" s="13">
+      <c r="J4">
         <f>MAX(0,ABS(Statements!I12-(Statements!I10-Statements!I11))-MAX(0.01,0.001*ABS(Statements!I12)))</f>
         <v/>
       </c>
-      <c r="K4" s="13">
+      <c r="K4">
         <f>MAX(0,ABS(Statements!J12-(Statements!J10-Statements!J11))-MAX(0.01,0.001*ABS(Statements!J12)))</f>
         <v/>
       </c>
-      <c r="L4" s="13">
+      <c r="L4">
         <f>MAX(0,ABS(Statements!K12-(Statements!K10-Statements!K11))-MAX(0.01,0.001*ABS(Statements!K12)))</f>
         <v/>
       </c>
-      <c r="M4" s="13">
+      <c r="M4">
         <f>MAX(0,ABS(Statements!L12-(Statements!L10-Statements!L11))-MAX(0.01,0.001*ABS(Statements!L12)))</f>
         <v/>
       </c>
-      <c r="N4" s="13">
+      <c r="N4">
         <f>MAX(0,ABS(Statements!M12-(Statements!M10-Statements!M11))-MAX(0.01,0.001*ABS(Statements!M12)))</f>
         <v/>
       </c>
-      <c r="O4" s="13">
+      <c r="O4">
         <f>MAX(0,ABS(Statements!N12-(Statements!N10-Statements!N11))-MAX(0.01,0.001*ABS(Statements!N12)))</f>
         <v/>
       </c>
-      <c r="P4" s="13">
+      <c r="P4">
         <f>MAX(0,ABS(Statements!O12-(Statements!O10-Statements!O11))-MAX(0.01,0.001*ABS(Statements!O12)))</f>
         <v/>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4">
         <f>MAX(0,ABS(Statements!P12-(Statements!P10-Statements!P11))-MAX(0.01,0.001*ABS(Statements!P12)))</f>
         <v/>
       </c>
-      <c r="R4" s="13">
+      <c r="R4">
         <f>MAX(0,ABS(Statements!Q12-(Statements!Q10-Statements!Q11))-MAX(0.01,0.001*ABS(Statements!Q12)))</f>
         <v/>
       </c>
-      <c r="S4" s="13">
+      <c r="S4">
         <f>MAX(0,ABS(Statements!R12-(Statements!R10-Statements!R11))-MAX(0.01,0.001*ABS(Statements!R12)))</f>
         <v/>
       </c>
-      <c r="T4" s="13">
+      <c r="T4">
         <f>MAX(0,ABS(Statements!S12-(Statements!S10-Statements!S11))-MAX(0.01,0.001*ABS(Statements!S12)))</f>
         <v/>
       </c>
-      <c r="U4" s="13">
+      <c r="U4">
         <f>MAX(0,ABS(Statements!T12-(Statements!T10-Statements!T11))-MAX(0.01,0.001*ABS(Statements!T12)))</f>
         <v/>
       </c>
-      <c r="V4" s="13">
+      <c r="V4">
         <f>MAX(0,ABS(Statements!U12-(Statements!U10-Statements!U11))-MAX(0.01,0.001*ABS(Statements!U12)))</f>
         <v/>
       </c>
-      <c r="W4" s="13">
+      <c r="W4">
         <f>MAX(0,ABS(Statements!V12-(Statements!V10-Statements!V11))-MAX(0.01,0.001*ABS(Statements!V12)))</f>
         <v/>
       </c>
-      <c r="X4" s="13">
+      <c r="X4">
         <f>MAX(0,ABS(Statements!W12-(Statements!W10-Statements!W11))-MAX(0.01,0.001*ABS(Statements!W12)))</f>
         <v/>
       </c>
-      <c r="Y4" s="13">
+      <c r="Y4">
         <f>MAX(0,ABS(Statements!X12-(Statements!X10-Statements!X11))-MAX(0.01,0.001*ABS(Statements!X12)))</f>
         <v/>
       </c>
-      <c r="Z4" s="13">
+      <c r="Z4">
         <f>MAX(0,ABS(Statements!Y12-(Statements!Y10-Statements!Y11))-MAX(0.01,0.001*ABS(Statements!Y12)))</f>
         <v/>
       </c>
-      <c r="AA4" s="13">
+      <c r="AA4">
         <f>MAX(0,ABS(Statements!Z12-(Statements!Z10-Statements!Z11))-MAX(0.01,0.001*ABS(Statements!Z12)))</f>
         <v/>
       </c>
-      <c r="AB4" s="13">
+      <c r="AB4">
         <f>MAX(0,ABS(Statements!AA12-(Statements!AA10-Statements!AA11))-MAX(0.01,0.001*ABS(Statements!AA12)))</f>
         <v/>
       </c>
-      <c r="AC4" s="13">
+      <c r="AC4">
         <f>MAX(0,ABS(Statements!AB12-(Statements!AB10-Statements!AB11))-MAX(0.01,0.001*ABS(Statements!AB12)))</f>
         <v/>
       </c>
-      <c r="AD4" s="13">
+      <c r="AD4">
         <f>MAX(0,ABS(Statements!AC12-(Statements!AC10-Statements!AC11))-MAX(0.01,0.001*ABS(Statements!AC12)))</f>
         <v/>
       </c>
-      <c r="AE4" s="13">
+      <c r="AE4">
         <f>MAX(0,ABS(Statements!AD12-(Statements!AD10-Statements!AD11))-MAX(0.01,0.001*ABS(Statements!AD12)))</f>
         <v/>
       </c>
-      <c r="AF4" s="13">
+      <c r="AF4">
         <f>MAX(0,ABS(Statements!AE12-(Statements!AE10-Statements!AE11))-MAX(0.01,0.001*ABS(Statements!AE12)))</f>
         <v/>
       </c>
-      <c r="AG4" s="13">
+      <c r="AG4">
         <f>MAX(0,ABS(Statements!AF12-(Statements!AF10-Statements!AF11))-MAX(0.01,0.001*ABS(Statements!AF12)))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>netIncome = pbt - taxExpense</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5">
         <f>MAX(D5:AG5)</f>
         <v/>
       </c>
@@ -4614,134 +4335,134 @@
         <f>IF(B5=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D5" s="13">
+      <c r="D5">
         <f>MAX(0,ABS(Statements!C14-(Statements!C12-Statements!C13))-MAX(0.01,0.001*ABS(Statements!C14)))</f>
         <v/>
       </c>
-      <c r="E5" s="13">
+      <c r="E5">
         <f>MAX(0,ABS(Statements!D14-(Statements!D12-Statements!D13))-MAX(0.01,0.001*ABS(Statements!D14)))</f>
         <v/>
       </c>
-      <c r="F5" s="13">
+      <c r="F5">
         <f>MAX(0,ABS(Statements!E14-(Statements!E12-Statements!E13))-MAX(0.01,0.001*ABS(Statements!E14)))</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5">
         <f>MAX(0,ABS(Statements!F14-(Statements!F12-Statements!F13))-MAX(0.01,0.001*ABS(Statements!F14)))</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5">
         <f>MAX(0,ABS(Statements!G14-(Statements!G12-Statements!G13))-MAX(0.01,0.001*ABS(Statements!G14)))</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5">
         <f>MAX(0,ABS(Statements!H14-(Statements!H12-Statements!H13))-MAX(0.01,0.001*ABS(Statements!H14)))</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5">
         <f>MAX(0,ABS(Statements!I14-(Statements!I12-Statements!I13))-MAX(0.01,0.001*ABS(Statements!I14)))</f>
         <v/>
       </c>
-      <c r="K5" s="13">
+      <c r="K5">
         <f>MAX(0,ABS(Statements!J14-(Statements!J12-Statements!J13))-MAX(0.01,0.001*ABS(Statements!J14)))</f>
         <v/>
       </c>
-      <c r="L5" s="13">
+      <c r="L5">
         <f>MAX(0,ABS(Statements!K14-(Statements!K12-Statements!K13))-MAX(0.01,0.001*ABS(Statements!K14)))</f>
         <v/>
       </c>
-      <c r="M5" s="13">
+      <c r="M5">
         <f>MAX(0,ABS(Statements!L14-(Statements!L12-Statements!L13))-MAX(0.01,0.001*ABS(Statements!L14)))</f>
         <v/>
       </c>
-      <c r="N5" s="13">
+      <c r="N5">
         <f>MAX(0,ABS(Statements!M14-(Statements!M12-Statements!M13))-MAX(0.01,0.001*ABS(Statements!M14)))</f>
         <v/>
       </c>
-      <c r="O5" s="13">
+      <c r="O5">
         <f>MAX(0,ABS(Statements!N14-(Statements!N12-Statements!N13))-MAX(0.01,0.001*ABS(Statements!N14)))</f>
         <v/>
       </c>
-      <c r="P5" s="13">
+      <c r="P5">
         <f>MAX(0,ABS(Statements!O14-(Statements!O12-Statements!O13))-MAX(0.01,0.001*ABS(Statements!O14)))</f>
         <v/>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5">
         <f>MAX(0,ABS(Statements!P14-(Statements!P12-Statements!P13))-MAX(0.01,0.001*ABS(Statements!P14)))</f>
         <v/>
       </c>
-      <c r="R5" s="13">
+      <c r="R5">
         <f>MAX(0,ABS(Statements!Q14-(Statements!Q12-Statements!Q13))-MAX(0.01,0.001*ABS(Statements!Q14)))</f>
         <v/>
       </c>
-      <c r="S5" s="13">
+      <c r="S5">
         <f>MAX(0,ABS(Statements!R14-(Statements!R12-Statements!R13))-MAX(0.01,0.001*ABS(Statements!R14)))</f>
         <v/>
       </c>
-      <c r="T5" s="13">
+      <c r="T5">
         <f>MAX(0,ABS(Statements!S14-(Statements!S12-Statements!S13))-MAX(0.01,0.001*ABS(Statements!S14)))</f>
         <v/>
       </c>
-      <c r="U5" s="13">
+      <c r="U5">
         <f>MAX(0,ABS(Statements!T14-(Statements!T12-Statements!T13))-MAX(0.01,0.001*ABS(Statements!T14)))</f>
         <v/>
       </c>
-      <c r="V5" s="13">
+      <c r="V5">
         <f>MAX(0,ABS(Statements!U14-(Statements!U12-Statements!U13))-MAX(0.01,0.001*ABS(Statements!U14)))</f>
         <v/>
       </c>
-      <c r="W5" s="13">
+      <c r="W5">
         <f>MAX(0,ABS(Statements!V14-(Statements!V12-Statements!V13))-MAX(0.01,0.001*ABS(Statements!V14)))</f>
         <v/>
       </c>
-      <c r="X5" s="13">
+      <c r="X5">
         <f>MAX(0,ABS(Statements!W14-(Statements!W12-Statements!W13))-MAX(0.01,0.001*ABS(Statements!W14)))</f>
         <v/>
       </c>
-      <c r="Y5" s="13">
+      <c r="Y5">
         <f>MAX(0,ABS(Statements!X14-(Statements!X12-Statements!X13))-MAX(0.01,0.001*ABS(Statements!X14)))</f>
         <v/>
       </c>
-      <c r="Z5" s="13">
+      <c r="Z5">
         <f>MAX(0,ABS(Statements!Y14-(Statements!Y12-Statements!Y13))-MAX(0.01,0.001*ABS(Statements!Y14)))</f>
         <v/>
       </c>
-      <c r="AA5" s="13">
+      <c r="AA5">
         <f>MAX(0,ABS(Statements!Z14-(Statements!Z12-Statements!Z13))-MAX(0.01,0.001*ABS(Statements!Z14)))</f>
         <v/>
       </c>
-      <c r="AB5" s="13">
+      <c r="AB5">
         <f>MAX(0,ABS(Statements!AA14-(Statements!AA12-Statements!AA13))-MAX(0.01,0.001*ABS(Statements!AA14)))</f>
         <v/>
       </c>
-      <c r="AC5" s="13">
+      <c r="AC5">
         <f>MAX(0,ABS(Statements!AB14-(Statements!AB12-Statements!AB13))-MAX(0.01,0.001*ABS(Statements!AB14)))</f>
         <v/>
       </c>
-      <c r="AD5" s="13">
+      <c r="AD5">
         <f>MAX(0,ABS(Statements!AC14-(Statements!AC12-Statements!AC13))-MAX(0.01,0.001*ABS(Statements!AC14)))</f>
         <v/>
       </c>
-      <c r="AE5" s="13">
+      <c r="AE5">
         <f>MAX(0,ABS(Statements!AD14-(Statements!AD12-Statements!AD13))-MAX(0.01,0.001*ABS(Statements!AD14)))</f>
         <v/>
       </c>
-      <c r="AF5" s="13">
+      <c r="AF5">
         <f>MAX(0,ABS(Statements!AE14-(Statements!AE12-Statements!AE13))-MAX(0.01,0.001*ABS(Statements!AE14)))</f>
         <v/>
       </c>
-      <c r="AG5" s="13">
+      <c r="AG5">
         <f>MAX(0,ABS(Statements!AF14-(Statements!AF12-Statements!AF13))-MAX(0.01,0.001*ABS(Statements!AF14)))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>revenue = generationGwh * 1000 * achievedPrice / 1e6</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6">
         <f>MAX(D6:AG6)</f>
         <v/>
       </c>
@@ -4749,134 +4470,134 @@
         <f>IF(B6=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D6" s="13">
-        <f>MAX(0,ABS(Statements!C6-Statements!C3*1000*Statements!C4/1000000)-MAX(0.01,0.001*ABS(Statements!C6)))</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>MAX(0,ABS(Statements!D6-Statements!D3*1000*Statements!D4/1000000)-MAX(0.01,0.001*ABS(Statements!D6)))</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>MAX(0,ABS(Statements!E6-Statements!E3*1000*Statements!E4/1000000)-MAX(0.01,0.001*ABS(Statements!E6)))</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>MAX(0,ABS(Statements!F6-Statements!F3*1000*Statements!F4/1000000)-MAX(0.01,0.001*ABS(Statements!F6)))</f>
-        <v/>
-      </c>
-      <c r="H6" s="13">
-        <f>MAX(0,ABS(Statements!G6-Statements!G3*1000*Statements!G4/1000000)-MAX(0.01,0.001*ABS(Statements!G6)))</f>
-        <v/>
-      </c>
-      <c r="I6" s="13">
-        <f>MAX(0,ABS(Statements!H6-Statements!H3*1000*Statements!H4/1000000)-MAX(0.01,0.001*ABS(Statements!H6)))</f>
-        <v/>
-      </c>
-      <c r="J6" s="13">
-        <f>MAX(0,ABS(Statements!I6-Statements!I3*1000*Statements!I4/1000000)-MAX(0.01,0.001*ABS(Statements!I6)))</f>
-        <v/>
-      </c>
-      <c r="K6" s="13">
-        <f>MAX(0,ABS(Statements!J6-Statements!J3*1000*Statements!J4/1000000)-MAX(0.01,0.001*ABS(Statements!J6)))</f>
-        <v/>
-      </c>
-      <c r="L6" s="13">
-        <f>MAX(0,ABS(Statements!K6-Statements!K3*1000*Statements!K4/1000000)-MAX(0.01,0.001*ABS(Statements!K6)))</f>
-        <v/>
-      </c>
-      <c r="M6" s="13">
-        <f>MAX(0,ABS(Statements!L6-Statements!L3*1000*Statements!L4/1000000)-MAX(0.01,0.001*ABS(Statements!L6)))</f>
-        <v/>
-      </c>
-      <c r="N6" s="13">
-        <f>MAX(0,ABS(Statements!M6-Statements!M3*1000*Statements!M4/1000000)-MAX(0.01,0.001*ABS(Statements!M6)))</f>
-        <v/>
-      </c>
-      <c r="O6" s="13">
-        <f>MAX(0,ABS(Statements!N6-Statements!N3*1000*Statements!N4/1000000)-MAX(0.01,0.001*ABS(Statements!N6)))</f>
-        <v/>
-      </c>
-      <c r="P6" s="13">
-        <f>MAX(0,ABS(Statements!O6-Statements!O3*1000*Statements!O4/1000000)-MAX(0.01,0.001*ABS(Statements!O6)))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="13">
-        <f>MAX(0,ABS(Statements!P6-Statements!P3*1000*Statements!P4/1000000)-MAX(0.01,0.001*ABS(Statements!P6)))</f>
-        <v/>
-      </c>
-      <c r="R6" s="13">
-        <f>MAX(0,ABS(Statements!Q6-Statements!Q3*1000*Statements!Q4/1000000)-MAX(0.01,0.001*ABS(Statements!Q6)))</f>
-        <v/>
-      </c>
-      <c r="S6" s="13">
-        <f>MAX(0,ABS(Statements!R6-Statements!R3*1000*Statements!R4/1000000)-MAX(0.01,0.001*ABS(Statements!R6)))</f>
-        <v/>
-      </c>
-      <c r="T6" s="13">
-        <f>MAX(0,ABS(Statements!S6-Statements!S3*1000*Statements!S4/1000000)-MAX(0.01,0.001*ABS(Statements!S6)))</f>
-        <v/>
-      </c>
-      <c r="U6" s="13">
-        <f>MAX(0,ABS(Statements!T6-Statements!T3*1000*Statements!T4/1000000)-MAX(0.01,0.001*ABS(Statements!T6)))</f>
-        <v/>
-      </c>
-      <c r="V6" s="13">
-        <f>MAX(0,ABS(Statements!U6-Statements!U3*1000*Statements!U4/1000000)-MAX(0.01,0.001*ABS(Statements!U6)))</f>
-        <v/>
-      </c>
-      <c r="W6" s="13">
-        <f>MAX(0,ABS(Statements!V6-Statements!V3*1000*Statements!V4/1000000)-MAX(0.01,0.001*ABS(Statements!V6)))</f>
-        <v/>
-      </c>
-      <c r="X6" s="13">
-        <f>MAX(0,ABS(Statements!W6-Statements!W3*1000*Statements!W4/1000000)-MAX(0.01,0.001*ABS(Statements!W6)))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="13">
-        <f>MAX(0,ABS(Statements!X6-Statements!X3*1000*Statements!X4/1000000)-MAX(0.01,0.001*ABS(Statements!X6)))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="13">
-        <f>MAX(0,ABS(Statements!Y6-Statements!Y3*1000*Statements!Y4/1000000)-MAX(0.01,0.001*ABS(Statements!Y6)))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="13">
-        <f>MAX(0,ABS(Statements!Z6-Statements!Z3*1000*Statements!Z4/1000000)-MAX(0.01,0.001*ABS(Statements!Z6)))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="13">
-        <f>MAX(0,ABS(Statements!AA6-Statements!AA3*1000*Statements!AA4/1000000)-MAX(0.01,0.001*ABS(Statements!AA6)))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="13">
-        <f>MAX(0,ABS(Statements!AB6-Statements!AB3*1000*Statements!AB4/1000000)-MAX(0.01,0.001*ABS(Statements!AB6)))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="13">
-        <f>MAX(0,ABS(Statements!AC6-Statements!AC3*1000*Statements!AC4/1000000)-MAX(0.01,0.001*ABS(Statements!AC6)))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="13">
-        <f>MAX(0,ABS(Statements!AD6-Statements!AD3*1000*Statements!AD4/1000000)-MAX(0.01,0.001*ABS(Statements!AD6)))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="13">
-        <f>MAX(0,ABS(Statements!AE6-Statements!AE3*1000*Statements!AE4/1000000)-MAX(0.01,0.001*ABS(Statements!AE6)))</f>
-        <v/>
-      </c>
-      <c r="AG6" s="13">
-        <f>MAX(0,ABS(Statements!AF6-Statements!AF3*1000*Statements!AF4/1000000)-MAX(0.01,0.001*ABS(Statements!AF6)))</f>
+      <c r="D6">
+        <f>MAX(0,ABS(Statements!C6-(Statements!C3*1000*Statements!C4/1000000))-MAX(0.01,0.001*ABS(Statements!C6)))</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>MAX(0,ABS(Statements!D6-(Statements!D3*1000*Statements!D4/1000000))-MAX(0.01,0.001*ABS(Statements!D6)))</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>MAX(0,ABS(Statements!E6-(Statements!E3*1000*Statements!E4/1000000))-MAX(0.01,0.001*ABS(Statements!E6)))</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>MAX(0,ABS(Statements!F6-(Statements!F3*1000*Statements!F4/1000000))-MAX(0.01,0.001*ABS(Statements!F6)))</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>MAX(0,ABS(Statements!G6-(Statements!G3*1000*Statements!G4/1000000))-MAX(0.01,0.001*ABS(Statements!G6)))</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>MAX(0,ABS(Statements!H6-(Statements!H3*1000*Statements!H4/1000000))-MAX(0.01,0.001*ABS(Statements!H6)))</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>MAX(0,ABS(Statements!I6-(Statements!I3*1000*Statements!I4/1000000))-MAX(0.01,0.001*ABS(Statements!I6)))</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>MAX(0,ABS(Statements!J6-(Statements!J3*1000*Statements!J4/1000000))-MAX(0.01,0.001*ABS(Statements!J6)))</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>MAX(0,ABS(Statements!K6-(Statements!K3*1000*Statements!K4/1000000))-MAX(0.01,0.001*ABS(Statements!K6)))</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>MAX(0,ABS(Statements!L6-(Statements!L3*1000*Statements!L4/1000000))-MAX(0.01,0.001*ABS(Statements!L6)))</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>MAX(0,ABS(Statements!M6-(Statements!M3*1000*Statements!M4/1000000))-MAX(0.01,0.001*ABS(Statements!M6)))</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>MAX(0,ABS(Statements!N6-(Statements!N3*1000*Statements!N4/1000000))-MAX(0.01,0.001*ABS(Statements!N6)))</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>MAX(0,ABS(Statements!O6-(Statements!O3*1000*Statements!O4/1000000))-MAX(0.01,0.001*ABS(Statements!O6)))</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>MAX(0,ABS(Statements!P6-(Statements!P3*1000*Statements!P4/1000000))-MAX(0.01,0.001*ABS(Statements!P6)))</f>
+        <v/>
+      </c>
+      <c r="R6">
+        <f>MAX(0,ABS(Statements!Q6-(Statements!Q3*1000*Statements!Q4/1000000))-MAX(0.01,0.001*ABS(Statements!Q6)))</f>
+        <v/>
+      </c>
+      <c r="S6">
+        <f>MAX(0,ABS(Statements!R6-(Statements!R3*1000*Statements!R4/1000000))-MAX(0.01,0.001*ABS(Statements!R6)))</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>MAX(0,ABS(Statements!S6-(Statements!S3*1000*Statements!S4/1000000))-MAX(0.01,0.001*ABS(Statements!S6)))</f>
+        <v/>
+      </c>
+      <c r="U6">
+        <f>MAX(0,ABS(Statements!T6-(Statements!T3*1000*Statements!T4/1000000))-MAX(0.01,0.001*ABS(Statements!T6)))</f>
+        <v/>
+      </c>
+      <c r="V6">
+        <f>MAX(0,ABS(Statements!U6-(Statements!U3*1000*Statements!U4/1000000))-MAX(0.01,0.001*ABS(Statements!U6)))</f>
+        <v/>
+      </c>
+      <c r="W6">
+        <f>MAX(0,ABS(Statements!V6-(Statements!V3*1000*Statements!V4/1000000))-MAX(0.01,0.001*ABS(Statements!V6)))</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>MAX(0,ABS(Statements!W6-(Statements!W3*1000*Statements!W4/1000000))-MAX(0.01,0.001*ABS(Statements!W6)))</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>MAX(0,ABS(Statements!X6-(Statements!X3*1000*Statements!X4/1000000))-MAX(0.01,0.001*ABS(Statements!X6)))</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>MAX(0,ABS(Statements!Y6-(Statements!Y3*1000*Statements!Y4/1000000))-MAX(0.01,0.001*ABS(Statements!Y6)))</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>MAX(0,ABS(Statements!Z6-(Statements!Z3*1000*Statements!Z4/1000000))-MAX(0.01,0.001*ABS(Statements!Z6)))</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>MAX(0,ABS(Statements!AA6-(Statements!AA3*1000*Statements!AA4/1000000))-MAX(0.01,0.001*ABS(Statements!AA6)))</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>MAX(0,ABS(Statements!AB6-(Statements!AB3*1000*Statements!AB4/1000000))-MAX(0.01,0.001*ABS(Statements!AB6)))</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>MAX(0,ABS(Statements!AC6-(Statements!AC3*1000*Statements!AC4/1000000))-MAX(0.01,0.001*ABS(Statements!AC6)))</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>MAX(0,ABS(Statements!AD6-(Statements!AD3*1000*Statements!AD4/1000000))-MAX(0.01,0.001*ABS(Statements!AD6)))</f>
+        <v/>
+      </c>
+      <c r="AF6">
+        <f>MAX(0,ABS(Statements!AE6-(Statements!AE3*1000*Statements!AE4/1000000))-MAX(0.01,0.001*ABS(Statements!AE6)))</f>
+        <v/>
+      </c>
+      <c r="AG6">
+        <f>MAX(0,ABS(Statements!AF6-(Statements!AF3*1000*Statements!AF4/1000000))-MAX(0.01,0.001*ABS(Statements!AF6)))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>fcfe = ebitda - interestPaid - debtRepayment - taxPaid - capex + debtDrawdown</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7">
         <f>MAX(D7:AG7)</f>
         <v/>
       </c>
@@ -4884,134 +4605,134 @@
         <f>IF(B7=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D7" s="13">
+      <c r="D7">
         <f>MAX(0,ABS(Statements!C22-(Statements!C8-Statements!C16-Statements!C17-Statements!C18-Statements!C19+Statements!C20))-MAX(0.01,0.001*ABS(Statements!C22)))</f>
         <v/>
       </c>
-      <c r="E7" s="13">
+      <c r="E7">
         <f>MAX(0,ABS(Statements!D22-(Statements!D8-Statements!D16-Statements!D17-Statements!D18-Statements!D19+Statements!D20))-MAX(0.01,0.001*ABS(Statements!D22)))</f>
         <v/>
       </c>
-      <c r="F7" s="13">
+      <c r="F7">
         <f>MAX(0,ABS(Statements!E22-(Statements!E8-Statements!E16-Statements!E17-Statements!E18-Statements!E19+Statements!E20))-MAX(0.01,0.001*ABS(Statements!E22)))</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7">
         <f>MAX(0,ABS(Statements!F22-(Statements!F8-Statements!F16-Statements!F17-Statements!F18-Statements!F19+Statements!F20))-MAX(0.01,0.001*ABS(Statements!F22)))</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7">
         <f>MAX(0,ABS(Statements!G22-(Statements!G8-Statements!G16-Statements!G17-Statements!G18-Statements!G19+Statements!G20))-MAX(0.01,0.001*ABS(Statements!G22)))</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7">
         <f>MAX(0,ABS(Statements!H22-(Statements!H8-Statements!H16-Statements!H17-Statements!H18-Statements!H19+Statements!H20))-MAX(0.01,0.001*ABS(Statements!H22)))</f>
         <v/>
       </c>
-      <c r="J7" s="13">
+      <c r="J7">
         <f>MAX(0,ABS(Statements!I22-(Statements!I8-Statements!I16-Statements!I17-Statements!I18-Statements!I19+Statements!I20))-MAX(0.01,0.001*ABS(Statements!I22)))</f>
         <v/>
       </c>
-      <c r="K7" s="13">
+      <c r="K7">
         <f>MAX(0,ABS(Statements!J22-(Statements!J8-Statements!J16-Statements!J17-Statements!J18-Statements!J19+Statements!J20))-MAX(0.01,0.001*ABS(Statements!J22)))</f>
         <v/>
       </c>
-      <c r="L7" s="13">
+      <c r="L7">
         <f>MAX(0,ABS(Statements!K22-(Statements!K8-Statements!K16-Statements!K17-Statements!K18-Statements!K19+Statements!K20))-MAX(0.01,0.001*ABS(Statements!K22)))</f>
         <v/>
       </c>
-      <c r="M7" s="13">
+      <c r="M7">
         <f>MAX(0,ABS(Statements!L22-(Statements!L8-Statements!L16-Statements!L17-Statements!L18-Statements!L19+Statements!L20))-MAX(0.01,0.001*ABS(Statements!L22)))</f>
         <v/>
       </c>
-      <c r="N7" s="13">
+      <c r="N7">
         <f>MAX(0,ABS(Statements!M22-(Statements!M8-Statements!M16-Statements!M17-Statements!M18-Statements!M19+Statements!M20))-MAX(0.01,0.001*ABS(Statements!M22)))</f>
         <v/>
       </c>
-      <c r="O7" s="13">
+      <c r="O7">
         <f>MAX(0,ABS(Statements!N22-(Statements!N8-Statements!N16-Statements!N17-Statements!N18-Statements!N19+Statements!N20))-MAX(0.01,0.001*ABS(Statements!N22)))</f>
         <v/>
       </c>
-      <c r="P7" s="13">
+      <c r="P7">
         <f>MAX(0,ABS(Statements!O22-(Statements!O8-Statements!O16-Statements!O17-Statements!O18-Statements!O19+Statements!O20))-MAX(0.01,0.001*ABS(Statements!O22)))</f>
         <v/>
       </c>
-      <c r="Q7" s="13">
+      <c r="Q7">
         <f>MAX(0,ABS(Statements!P22-(Statements!P8-Statements!P16-Statements!P17-Statements!P18-Statements!P19+Statements!P20))-MAX(0.01,0.001*ABS(Statements!P22)))</f>
         <v/>
       </c>
-      <c r="R7" s="13">
+      <c r="R7">
         <f>MAX(0,ABS(Statements!Q22-(Statements!Q8-Statements!Q16-Statements!Q17-Statements!Q18-Statements!Q19+Statements!Q20))-MAX(0.01,0.001*ABS(Statements!Q22)))</f>
         <v/>
       </c>
-      <c r="S7" s="13">
+      <c r="S7">
         <f>MAX(0,ABS(Statements!R22-(Statements!R8-Statements!R16-Statements!R17-Statements!R18-Statements!R19+Statements!R20))-MAX(0.01,0.001*ABS(Statements!R22)))</f>
         <v/>
       </c>
-      <c r="T7" s="13">
+      <c r="T7">
         <f>MAX(0,ABS(Statements!S22-(Statements!S8-Statements!S16-Statements!S17-Statements!S18-Statements!S19+Statements!S20))-MAX(0.01,0.001*ABS(Statements!S22)))</f>
         <v/>
       </c>
-      <c r="U7" s="13">
+      <c r="U7">
         <f>MAX(0,ABS(Statements!T22-(Statements!T8-Statements!T16-Statements!T17-Statements!T18-Statements!T19+Statements!T20))-MAX(0.01,0.001*ABS(Statements!T22)))</f>
         <v/>
       </c>
-      <c r="V7" s="13">
+      <c r="V7">
         <f>MAX(0,ABS(Statements!U22-(Statements!U8-Statements!U16-Statements!U17-Statements!U18-Statements!U19+Statements!U20))-MAX(0.01,0.001*ABS(Statements!U22)))</f>
         <v/>
       </c>
-      <c r="W7" s="13">
+      <c r="W7">
         <f>MAX(0,ABS(Statements!V22-(Statements!V8-Statements!V16-Statements!V17-Statements!V18-Statements!V19+Statements!V20))-MAX(0.01,0.001*ABS(Statements!V22)))</f>
         <v/>
       </c>
-      <c r="X7" s="13">
+      <c r="X7">
         <f>MAX(0,ABS(Statements!W22-(Statements!W8-Statements!W16-Statements!W17-Statements!W18-Statements!W19+Statements!W20))-MAX(0.01,0.001*ABS(Statements!W22)))</f>
         <v/>
       </c>
-      <c r="Y7" s="13">
+      <c r="Y7">
         <f>MAX(0,ABS(Statements!X22-(Statements!X8-Statements!X16-Statements!X17-Statements!X18-Statements!X19+Statements!X20))-MAX(0.01,0.001*ABS(Statements!X22)))</f>
         <v/>
       </c>
-      <c r="Z7" s="13">
+      <c r="Z7">
         <f>MAX(0,ABS(Statements!Y22-(Statements!Y8-Statements!Y16-Statements!Y17-Statements!Y18-Statements!Y19+Statements!Y20))-MAX(0.01,0.001*ABS(Statements!Y22)))</f>
         <v/>
       </c>
-      <c r="AA7" s="13">
+      <c r="AA7">
         <f>MAX(0,ABS(Statements!Z22-(Statements!Z8-Statements!Z16-Statements!Z17-Statements!Z18-Statements!Z19+Statements!Z20))-MAX(0.01,0.001*ABS(Statements!Z22)))</f>
         <v/>
       </c>
-      <c r="AB7" s="13">
+      <c r="AB7">
         <f>MAX(0,ABS(Statements!AA22-(Statements!AA8-Statements!AA16-Statements!AA17-Statements!AA18-Statements!AA19+Statements!AA20))-MAX(0.01,0.001*ABS(Statements!AA22)))</f>
         <v/>
       </c>
-      <c r="AC7" s="13">
+      <c r="AC7">
         <f>MAX(0,ABS(Statements!AB22-(Statements!AB8-Statements!AB16-Statements!AB17-Statements!AB18-Statements!AB19+Statements!AB20))-MAX(0.01,0.001*ABS(Statements!AB22)))</f>
         <v/>
       </c>
-      <c r="AD7" s="13">
+      <c r="AD7">
         <f>MAX(0,ABS(Statements!AC22-(Statements!AC8-Statements!AC16-Statements!AC17-Statements!AC18-Statements!AC19+Statements!AC20))-MAX(0.01,0.001*ABS(Statements!AC22)))</f>
         <v/>
       </c>
-      <c r="AE7" s="13">
+      <c r="AE7">
         <f>MAX(0,ABS(Statements!AD22-(Statements!AD8-Statements!AD16-Statements!AD17-Statements!AD18-Statements!AD19+Statements!AD20))-MAX(0.01,0.001*ABS(Statements!AD22)))</f>
         <v/>
       </c>
-      <c r="AF7" s="13">
+      <c r="AF7">
         <f>MAX(0,ABS(Statements!AE22-(Statements!AE8-Statements!AE16-Statements!AE17-Statements!AE18-Statements!AE19+Statements!AE20))-MAX(0.01,0.001*ABS(Statements!AE22)))</f>
         <v/>
       </c>
-      <c r="AG7" s="13">
+      <c r="AG7">
         <f>MAX(0,ABS(Statements!AF22-(Statements!AF8-Statements!AF16-Statements!AF17-Statements!AF18-Statements!AF19+Statements!AF20))-MAX(0.01,0.001*ABS(Statements!AF22)))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>closing = opening - repayment + drawdown</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8">
         <f>MAX(D8:AG8)</f>
         <v/>
       </c>
@@ -5019,134 +4740,134 @@
         <f>IF(B8=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8">
         <f>MAX(0,ABS(Statements!C27-(Statements!C24-Statements!C26+Statements!C25))-MAX(0.01,0.001*ABS(Statements!C27)))</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8">
         <f>MAX(0,ABS(Statements!D27-(Statements!D24-Statements!D26+Statements!D25))-MAX(0.01,0.001*ABS(Statements!D27)))</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8">
         <f>MAX(0,ABS(Statements!E27-(Statements!E24-Statements!E26+Statements!E25))-MAX(0.01,0.001*ABS(Statements!E27)))</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8">
         <f>MAX(0,ABS(Statements!F27-(Statements!F24-Statements!F26+Statements!F25))-MAX(0.01,0.001*ABS(Statements!F27)))</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8">
         <f>MAX(0,ABS(Statements!G27-(Statements!G24-Statements!G26+Statements!G25))-MAX(0.01,0.001*ABS(Statements!G27)))</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8">
         <f>MAX(0,ABS(Statements!H27-(Statements!H24-Statements!H26+Statements!H25))-MAX(0.01,0.001*ABS(Statements!H27)))</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8">
         <f>MAX(0,ABS(Statements!I27-(Statements!I24-Statements!I26+Statements!I25))-MAX(0.01,0.001*ABS(Statements!I27)))</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8">
         <f>MAX(0,ABS(Statements!J27-(Statements!J24-Statements!J26+Statements!J25))-MAX(0.01,0.001*ABS(Statements!J27)))</f>
         <v/>
       </c>
-      <c r="L8" s="13">
+      <c r="L8">
         <f>MAX(0,ABS(Statements!K27-(Statements!K24-Statements!K26+Statements!K25))-MAX(0.01,0.001*ABS(Statements!K27)))</f>
         <v/>
       </c>
-      <c r="M8" s="13">
+      <c r="M8">
         <f>MAX(0,ABS(Statements!L27-(Statements!L24-Statements!L26+Statements!L25))-MAX(0.01,0.001*ABS(Statements!L27)))</f>
         <v/>
       </c>
-      <c r="N8" s="13">
+      <c r="N8">
         <f>MAX(0,ABS(Statements!M27-(Statements!M24-Statements!M26+Statements!M25))-MAX(0.01,0.001*ABS(Statements!M27)))</f>
         <v/>
       </c>
-      <c r="O8" s="13">
+      <c r="O8">
         <f>MAX(0,ABS(Statements!N27-(Statements!N24-Statements!N26+Statements!N25))-MAX(0.01,0.001*ABS(Statements!N27)))</f>
         <v/>
       </c>
-      <c r="P8" s="13">
+      <c r="P8">
         <f>MAX(0,ABS(Statements!O27-(Statements!O24-Statements!O26+Statements!O25))-MAX(0.01,0.001*ABS(Statements!O27)))</f>
         <v/>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8">
         <f>MAX(0,ABS(Statements!P27-(Statements!P24-Statements!P26+Statements!P25))-MAX(0.01,0.001*ABS(Statements!P27)))</f>
         <v/>
       </c>
-      <c r="R8" s="13">
+      <c r="R8">
         <f>MAX(0,ABS(Statements!Q27-(Statements!Q24-Statements!Q26+Statements!Q25))-MAX(0.01,0.001*ABS(Statements!Q27)))</f>
         <v/>
       </c>
-      <c r="S8" s="13">
+      <c r="S8">
         <f>MAX(0,ABS(Statements!R27-(Statements!R24-Statements!R26+Statements!R25))-MAX(0.01,0.001*ABS(Statements!R27)))</f>
         <v/>
       </c>
-      <c r="T8" s="13">
+      <c r="T8">
         <f>MAX(0,ABS(Statements!S27-(Statements!S24-Statements!S26+Statements!S25))-MAX(0.01,0.001*ABS(Statements!S27)))</f>
         <v/>
       </c>
-      <c r="U8" s="13">
+      <c r="U8">
         <f>MAX(0,ABS(Statements!T27-(Statements!T24-Statements!T26+Statements!T25))-MAX(0.01,0.001*ABS(Statements!T27)))</f>
         <v/>
       </c>
-      <c r="V8" s="13">
+      <c r="V8">
         <f>MAX(0,ABS(Statements!U27-(Statements!U24-Statements!U26+Statements!U25))-MAX(0.01,0.001*ABS(Statements!U27)))</f>
         <v/>
       </c>
-      <c r="W8" s="13">
+      <c r="W8">
         <f>MAX(0,ABS(Statements!V27-(Statements!V24-Statements!V26+Statements!V25))-MAX(0.01,0.001*ABS(Statements!V27)))</f>
         <v/>
       </c>
-      <c r="X8" s="13">
+      <c r="X8">
         <f>MAX(0,ABS(Statements!W27-(Statements!W24-Statements!W26+Statements!W25))-MAX(0.01,0.001*ABS(Statements!W27)))</f>
         <v/>
       </c>
-      <c r="Y8" s="13">
+      <c r="Y8">
         <f>MAX(0,ABS(Statements!X27-(Statements!X24-Statements!X26+Statements!X25))-MAX(0.01,0.001*ABS(Statements!X27)))</f>
         <v/>
       </c>
-      <c r="Z8" s="13">
+      <c r="Z8">
         <f>MAX(0,ABS(Statements!Y27-(Statements!Y24-Statements!Y26+Statements!Y25))-MAX(0.01,0.001*ABS(Statements!Y27)))</f>
         <v/>
       </c>
-      <c r="AA8" s="13">
+      <c r="AA8">
         <f>MAX(0,ABS(Statements!Z27-(Statements!Z24-Statements!Z26+Statements!Z25))-MAX(0.01,0.001*ABS(Statements!Z27)))</f>
         <v/>
       </c>
-      <c r="AB8" s="13">
+      <c r="AB8">
         <f>MAX(0,ABS(Statements!AA27-(Statements!AA24-Statements!AA26+Statements!AA25))-MAX(0.01,0.001*ABS(Statements!AA27)))</f>
         <v/>
       </c>
-      <c r="AC8" s="13">
+      <c r="AC8">
         <f>MAX(0,ABS(Statements!AB27-(Statements!AB24-Statements!AB26+Statements!AB25))-MAX(0.01,0.001*ABS(Statements!AB27)))</f>
         <v/>
       </c>
-      <c r="AD8" s="13">
+      <c r="AD8">
         <f>MAX(0,ABS(Statements!AC27-(Statements!AC24-Statements!AC26+Statements!AC25))-MAX(0.01,0.001*ABS(Statements!AC27)))</f>
         <v/>
       </c>
-      <c r="AE8" s="13">
+      <c r="AE8">
         <f>MAX(0,ABS(Statements!AD27-(Statements!AD24-Statements!AD26+Statements!AD25))-MAX(0.01,0.001*ABS(Statements!AD27)))</f>
         <v/>
       </c>
-      <c r="AF8" s="13">
+      <c r="AF8">
         <f>MAX(0,ABS(Statements!AE27-(Statements!AE24-Statements!AE26+Statements!AE25))-MAX(0.01,0.001*ABS(Statements!AE27)))</f>
         <v/>
       </c>
-      <c r="AG8" s="13">
+      <c r="AG8">
         <f>MAX(0,ABS(Statements!AF27-(Statements!AF24-Statements!AF26+Statements!AF25))-MAX(0.01,0.001*ABS(Statements!AF27)))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>opening[t] = closing[t-1], and opening[0] = 0</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9">
         <f>MAX(D9:AG9)</f>
         <v/>
       </c>
@@ -5154,134 +4875,134 @@
         <f>IF(B9=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D9" s="13">
+      <c r="D9">
         <f>MAX(0,ABS(Statements!C24)-MAX(0.01,0.001*ABS(0)))</f>
         <v/>
       </c>
-      <c r="E9" s="13">
-        <f>MAX(0,ABS(Statements!D24-Statements!C27)-MAX(0.01,0.001*ABS(Statements!D24)))</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>MAX(0,ABS(Statements!E24-Statements!D27)-MAX(0.01,0.001*ABS(Statements!E24)))</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>MAX(0,ABS(Statements!F24-Statements!E27)-MAX(0.01,0.001*ABS(Statements!F24)))</f>
-        <v/>
-      </c>
-      <c r="H9" s="13">
-        <f>MAX(0,ABS(Statements!G24-Statements!F27)-MAX(0.01,0.001*ABS(Statements!G24)))</f>
-        <v/>
-      </c>
-      <c r="I9" s="13">
-        <f>MAX(0,ABS(Statements!H24-Statements!G27)-MAX(0.01,0.001*ABS(Statements!H24)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="13">
-        <f>MAX(0,ABS(Statements!I24-Statements!H27)-MAX(0.01,0.001*ABS(Statements!I24)))</f>
-        <v/>
-      </c>
-      <c r="K9" s="13">
-        <f>MAX(0,ABS(Statements!J24-Statements!I27)-MAX(0.01,0.001*ABS(Statements!J24)))</f>
-        <v/>
-      </c>
-      <c r="L9" s="13">
-        <f>MAX(0,ABS(Statements!K24-Statements!J27)-MAX(0.01,0.001*ABS(Statements!K24)))</f>
-        <v/>
-      </c>
-      <c r="M9" s="13">
-        <f>MAX(0,ABS(Statements!L24-Statements!K27)-MAX(0.01,0.001*ABS(Statements!L24)))</f>
-        <v/>
-      </c>
-      <c r="N9" s="13">
-        <f>MAX(0,ABS(Statements!M24-Statements!L27)-MAX(0.01,0.001*ABS(Statements!M24)))</f>
-        <v/>
-      </c>
-      <c r="O9" s="13">
-        <f>MAX(0,ABS(Statements!N24-Statements!M27)-MAX(0.01,0.001*ABS(Statements!N24)))</f>
-        <v/>
-      </c>
-      <c r="P9" s="13">
-        <f>MAX(0,ABS(Statements!O24-Statements!N27)-MAX(0.01,0.001*ABS(Statements!O24)))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="13">
-        <f>MAX(0,ABS(Statements!P24-Statements!O27)-MAX(0.01,0.001*ABS(Statements!P24)))</f>
-        <v/>
-      </c>
-      <c r="R9" s="13">
-        <f>MAX(0,ABS(Statements!Q24-Statements!P27)-MAX(0.01,0.001*ABS(Statements!Q24)))</f>
-        <v/>
-      </c>
-      <c r="S9" s="13">
-        <f>MAX(0,ABS(Statements!R24-Statements!Q27)-MAX(0.01,0.001*ABS(Statements!R24)))</f>
-        <v/>
-      </c>
-      <c r="T9" s="13">
-        <f>MAX(0,ABS(Statements!S24-Statements!R27)-MAX(0.01,0.001*ABS(Statements!S24)))</f>
-        <v/>
-      </c>
-      <c r="U9" s="13">
-        <f>MAX(0,ABS(Statements!T24-Statements!S27)-MAX(0.01,0.001*ABS(Statements!T24)))</f>
-        <v/>
-      </c>
-      <c r="V9" s="13">
-        <f>MAX(0,ABS(Statements!U24-Statements!T27)-MAX(0.01,0.001*ABS(Statements!U24)))</f>
-        <v/>
-      </c>
-      <c r="W9" s="13">
-        <f>MAX(0,ABS(Statements!V24-Statements!U27)-MAX(0.01,0.001*ABS(Statements!V24)))</f>
-        <v/>
-      </c>
-      <c r="X9" s="13">
-        <f>MAX(0,ABS(Statements!W24-Statements!V27)-MAX(0.01,0.001*ABS(Statements!W24)))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="13">
-        <f>MAX(0,ABS(Statements!X24-Statements!W27)-MAX(0.01,0.001*ABS(Statements!X24)))</f>
-        <v/>
-      </c>
-      <c r="Z9" s="13">
-        <f>MAX(0,ABS(Statements!Y24-Statements!X27)-MAX(0.01,0.001*ABS(Statements!Y24)))</f>
-        <v/>
-      </c>
-      <c r="AA9" s="13">
-        <f>MAX(0,ABS(Statements!Z24-Statements!Y27)-MAX(0.01,0.001*ABS(Statements!Z24)))</f>
-        <v/>
-      </c>
-      <c r="AB9" s="13">
-        <f>MAX(0,ABS(Statements!AA24-Statements!Z27)-MAX(0.01,0.001*ABS(Statements!AA24)))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="13">
-        <f>MAX(0,ABS(Statements!AB24-Statements!AA27)-MAX(0.01,0.001*ABS(Statements!AB24)))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="13">
-        <f>MAX(0,ABS(Statements!AC24-Statements!AB27)-MAX(0.01,0.001*ABS(Statements!AC24)))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="13">
-        <f>MAX(0,ABS(Statements!AD24-Statements!AC27)-MAX(0.01,0.001*ABS(Statements!AD24)))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="13">
-        <f>MAX(0,ABS(Statements!AE24-Statements!AD27)-MAX(0.01,0.001*ABS(Statements!AE24)))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="13">
-        <f>MAX(0,ABS(Statements!AF24-Statements!AE27)-MAX(0.01,0.001*ABS(Statements!AF24)))</f>
+      <c r="E9">
+        <f>MAX(0,ABS(Statements!D24-(Statements!C27))-MAX(0.01,0.001*ABS(Statements!D24)))</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>MAX(0,ABS(Statements!E24-(Statements!D27))-MAX(0.01,0.001*ABS(Statements!E24)))</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>MAX(0,ABS(Statements!F24-(Statements!E27))-MAX(0.01,0.001*ABS(Statements!F24)))</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>MAX(0,ABS(Statements!G24-(Statements!F27))-MAX(0.01,0.001*ABS(Statements!G24)))</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>MAX(0,ABS(Statements!H24-(Statements!G27))-MAX(0.01,0.001*ABS(Statements!H24)))</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>MAX(0,ABS(Statements!I24-(Statements!H27))-MAX(0.01,0.001*ABS(Statements!I24)))</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>MAX(0,ABS(Statements!J24-(Statements!I27))-MAX(0.01,0.001*ABS(Statements!J24)))</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>MAX(0,ABS(Statements!K24-(Statements!J27))-MAX(0.01,0.001*ABS(Statements!K24)))</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>MAX(0,ABS(Statements!L24-(Statements!K27))-MAX(0.01,0.001*ABS(Statements!L24)))</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>MAX(0,ABS(Statements!M24-(Statements!L27))-MAX(0.01,0.001*ABS(Statements!M24)))</f>
+        <v/>
+      </c>
+      <c r="O9">
+        <f>MAX(0,ABS(Statements!N24-(Statements!M27))-MAX(0.01,0.001*ABS(Statements!N24)))</f>
+        <v/>
+      </c>
+      <c r="P9">
+        <f>MAX(0,ABS(Statements!O24-(Statements!N27))-MAX(0.01,0.001*ABS(Statements!O24)))</f>
+        <v/>
+      </c>
+      <c r="Q9">
+        <f>MAX(0,ABS(Statements!P24-(Statements!O27))-MAX(0.01,0.001*ABS(Statements!P24)))</f>
+        <v/>
+      </c>
+      <c r="R9">
+        <f>MAX(0,ABS(Statements!Q24-(Statements!P27))-MAX(0.01,0.001*ABS(Statements!Q24)))</f>
+        <v/>
+      </c>
+      <c r="S9">
+        <f>MAX(0,ABS(Statements!R24-(Statements!Q27))-MAX(0.01,0.001*ABS(Statements!R24)))</f>
+        <v/>
+      </c>
+      <c r="T9">
+        <f>MAX(0,ABS(Statements!S24-(Statements!R27))-MAX(0.01,0.001*ABS(Statements!S24)))</f>
+        <v/>
+      </c>
+      <c r="U9">
+        <f>MAX(0,ABS(Statements!T24-(Statements!S27))-MAX(0.01,0.001*ABS(Statements!T24)))</f>
+        <v/>
+      </c>
+      <c r="V9">
+        <f>MAX(0,ABS(Statements!U24-(Statements!T27))-MAX(0.01,0.001*ABS(Statements!U24)))</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>MAX(0,ABS(Statements!V24-(Statements!U27))-MAX(0.01,0.001*ABS(Statements!V24)))</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>MAX(0,ABS(Statements!W24-(Statements!V27))-MAX(0.01,0.001*ABS(Statements!W24)))</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>MAX(0,ABS(Statements!X24-(Statements!W27))-MAX(0.01,0.001*ABS(Statements!X24)))</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>MAX(0,ABS(Statements!Y24-(Statements!X27))-MAX(0.01,0.001*ABS(Statements!Y24)))</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>MAX(0,ABS(Statements!Z24-(Statements!Y27))-MAX(0.01,0.001*ABS(Statements!Z24)))</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>MAX(0,ABS(Statements!AA24-(Statements!Z27))-MAX(0.01,0.001*ABS(Statements!AA24)))</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>MAX(0,ABS(Statements!AB24-(Statements!AA27))-MAX(0.01,0.001*ABS(Statements!AB24)))</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>MAX(0,ABS(Statements!AC24-(Statements!AB27))-MAX(0.01,0.001*ABS(Statements!AC24)))</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>MAX(0,ABS(Statements!AD24-(Statements!AC27))-MAX(0.01,0.001*ABS(Statements!AD24)))</f>
+        <v/>
+      </c>
+      <c r="AF9">
+        <f>MAX(0,ABS(Statements!AE24-(Statements!AD27))-MAX(0.01,0.001*ABS(Statements!AE24)))</f>
+        <v/>
+      </c>
+      <c r="AG9">
+        <f>MAX(0,ABS(Statements!AF24-(Statements!AE27))-MAX(0.01,0.001*ABS(Statements!AF24)))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ppe[t] = ppe[t-1] - depreciation[t] + capex[t]</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10">
         <f>MAX(D10:AG10)</f>
         <v/>
       </c>
@@ -5289,134 +5010,134 @@
         <f>IF(B10=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D10" s="13">
+      <c r="D10">
         <f>MAX(0,ABS(Statements!C29-(0-Statements!C9+Statements!C19))-MAX(0.01,0.001*ABS(Statements!C29)))</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10">
         <f>MAX(0,ABS(Statements!D29-(Statements!C29-Statements!D9+Statements!D19))-MAX(0.01,0.001*ABS(Statements!D29)))</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10">
         <f>MAX(0,ABS(Statements!E29-(Statements!D29-Statements!E9+Statements!E19))-MAX(0.01,0.001*ABS(Statements!E29)))</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10">
         <f>MAX(0,ABS(Statements!F29-(Statements!E29-Statements!F9+Statements!F19))-MAX(0.01,0.001*ABS(Statements!F29)))</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10">
         <f>MAX(0,ABS(Statements!G29-(Statements!F29-Statements!G9+Statements!G19))-MAX(0.01,0.001*ABS(Statements!G29)))</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10">
         <f>MAX(0,ABS(Statements!H29-(Statements!G29-Statements!H9+Statements!H19))-MAX(0.01,0.001*ABS(Statements!H29)))</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10">
         <f>MAX(0,ABS(Statements!I29-(Statements!H29-Statements!I9+Statements!I19))-MAX(0.01,0.001*ABS(Statements!I29)))</f>
         <v/>
       </c>
-      <c r="K10" s="13">
+      <c r="K10">
         <f>MAX(0,ABS(Statements!J29-(Statements!I29-Statements!J9+Statements!J19))-MAX(0.01,0.001*ABS(Statements!J29)))</f>
         <v/>
       </c>
-      <c r="L10" s="13">
+      <c r="L10">
         <f>MAX(0,ABS(Statements!K29-(Statements!J29-Statements!K9+Statements!K19))-MAX(0.01,0.001*ABS(Statements!K29)))</f>
         <v/>
       </c>
-      <c r="M10" s="13">
+      <c r="M10">
         <f>MAX(0,ABS(Statements!L29-(Statements!K29-Statements!L9+Statements!L19))-MAX(0.01,0.001*ABS(Statements!L29)))</f>
         <v/>
       </c>
-      <c r="N10" s="13">
+      <c r="N10">
         <f>MAX(0,ABS(Statements!M29-(Statements!L29-Statements!M9+Statements!M19))-MAX(0.01,0.001*ABS(Statements!M29)))</f>
         <v/>
       </c>
-      <c r="O10" s="13">
+      <c r="O10">
         <f>MAX(0,ABS(Statements!N29-(Statements!M29-Statements!N9+Statements!N19))-MAX(0.01,0.001*ABS(Statements!N29)))</f>
         <v/>
       </c>
-      <c r="P10" s="13">
+      <c r="P10">
         <f>MAX(0,ABS(Statements!O29-(Statements!N29-Statements!O9+Statements!O19))-MAX(0.01,0.001*ABS(Statements!O29)))</f>
         <v/>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10">
         <f>MAX(0,ABS(Statements!P29-(Statements!O29-Statements!P9+Statements!P19))-MAX(0.01,0.001*ABS(Statements!P29)))</f>
         <v/>
       </c>
-      <c r="R10" s="13">
+      <c r="R10">
         <f>MAX(0,ABS(Statements!Q29-(Statements!P29-Statements!Q9+Statements!Q19))-MAX(0.01,0.001*ABS(Statements!Q29)))</f>
         <v/>
       </c>
-      <c r="S10" s="13">
+      <c r="S10">
         <f>MAX(0,ABS(Statements!R29-(Statements!Q29-Statements!R9+Statements!R19))-MAX(0.01,0.001*ABS(Statements!R29)))</f>
         <v/>
       </c>
-      <c r="T10" s="13">
+      <c r="T10">
         <f>MAX(0,ABS(Statements!S29-(Statements!R29-Statements!S9+Statements!S19))-MAX(0.01,0.001*ABS(Statements!S29)))</f>
         <v/>
       </c>
-      <c r="U10" s="13">
+      <c r="U10">
         <f>MAX(0,ABS(Statements!T29-(Statements!S29-Statements!T9+Statements!T19))-MAX(0.01,0.001*ABS(Statements!T29)))</f>
         <v/>
       </c>
-      <c r="V10" s="13">
+      <c r="V10">
         <f>MAX(0,ABS(Statements!U29-(Statements!T29-Statements!U9+Statements!U19))-MAX(0.01,0.001*ABS(Statements!U29)))</f>
         <v/>
       </c>
-      <c r="W10" s="13">
+      <c r="W10">
         <f>MAX(0,ABS(Statements!V29-(Statements!U29-Statements!V9+Statements!V19))-MAX(0.01,0.001*ABS(Statements!V29)))</f>
         <v/>
       </c>
-      <c r="X10" s="13">
+      <c r="X10">
         <f>MAX(0,ABS(Statements!W29-(Statements!V29-Statements!W9+Statements!W19))-MAX(0.01,0.001*ABS(Statements!W29)))</f>
         <v/>
       </c>
-      <c r="Y10" s="13">
+      <c r="Y10">
         <f>MAX(0,ABS(Statements!X29-(Statements!W29-Statements!X9+Statements!X19))-MAX(0.01,0.001*ABS(Statements!X29)))</f>
         <v/>
       </c>
-      <c r="Z10" s="13">
+      <c r="Z10">
         <f>MAX(0,ABS(Statements!Y29-(Statements!X29-Statements!Y9+Statements!Y19))-MAX(0.01,0.001*ABS(Statements!Y29)))</f>
         <v/>
       </c>
-      <c r="AA10" s="13">
+      <c r="AA10">
         <f>MAX(0,ABS(Statements!Z29-(Statements!Y29-Statements!Z9+Statements!Z19))-MAX(0.01,0.001*ABS(Statements!Z29)))</f>
         <v/>
       </c>
-      <c r="AB10" s="13">
+      <c r="AB10">
         <f>MAX(0,ABS(Statements!AA29-(Statements!Z29-Statements!AA9+Statements!AA19))-MAX(0.01,0.001*ABS(Statements!AA29)))</f>
         <v/>
       </c>
-      <c r="AC10" s="13">
+      <c r="AC10">
         <f>MAX(0,ABS(Statements!AB29-(Statements!AA29-Statements!AB9+Statements!AB19))-MAX(0.01,0.001*ABS(Statements!AB29)))</f>
         <v/>
       </c>
-      <c r="AD10" s="13">
+      <c r="AD10">
         <f>MAX(0,ABS(Statements!AC29-(Statements!AB29-Statements!AC9+Statements!AC19))-MAX(0.01,0.001*ABS(Statements!AC29)))</f>
         <v/>
       </c>
-      <c r="AE10" s="13">
+      <c r="AE10">
         <f>MAX(0,ABS(Statements!AD29-(Statements!AC29-Statements!AD9+Statements!AD19))-MAX(0.01,0.001*ABS(Statements!AD29)))</f>
         <v/>
       </c>
-      <c r="AF10" s="13">
+      <c r="AF10">
         <f>MAX(0,ABS(Statements!AE29-(Statements!AD29-Statements!AE9+Statements!AE19))-MAX(0.01,0.001*ABS(Statements!AE29)))</f>
         <v/>
       </c>
-      <c r="AG10" s="13">
+      <c r="AG10">
         <f>MAX(0,ABS(Statements!AF29-(Statements!AE29-Statements!AF9+Statements!AF19))-MAX(0.01,0.001*ABS(Statements!AF29)))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>capex = debtDrawdown + equityDrawdown</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11">
         <f>MAX(D11:AG11)</f>
         <v/>
       </c>
@@ -5424,134 +5145,134 @@
         <f>IF(B11=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D11" s="13">
+      <c r="D11">
         <f>MAX(0,ABS(Statements!C19-(Statements!C20+Statements!C21))-MAX(0.01,0.001*ABS(Statements!C19)))</f>
         <v/>
       </c>
-      <c r="E11" s="13">
+      <c r="E11">
         <f>MAX(0,ABS(Statements!D19-(Statements!D20+Statements!D21))-MAX(0.01,0.001*ABS(Statements!D19)))</f>
         <v/>
       </c>
-      <c r="F11" s="13">
+      <c r="F11">
         <f>MAX(0,ABS(Statements!E19-(Statements!E20+Statements!E21))-MAX(0.01,0.001*ABS(Statements!E19)))</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11">
         <f>MAX(0,ABS(Statements!F19-(Statements!F20+Statements!F21))-MAX(0.01,0.001*ABS(Statements!F19)))</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11">
         <f>MAX(0,ABS(Statements!G19-(Statements!G20+Statements!G21))-MAX(0.01,0.001*ABS(Statements!G19)))</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11">
         <f>MAX(0,ABS(Statements!H19-(Statements!H20+Statements!H21))-MAX(0.01,0.001*ABS(Statements!H19)))</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11">
         <f>MAX(0,ABS(Statements!I19-(Statements!I20+Statements!I21))-MAX(0.01,0.001*ABS(Statements!I19)))</f>
         <v/>
       </c>
-      <c r="K11" s="13">
+      <c r="K11">
         <f>MAX(0,ABS(Statements!J19-(Statements!J20+Statements!J21))-MAX(0.01,0.001*ABS(Statements!J19)))</f>
         <v/>
       </c>
-      <c r="L11" s="13">
+      <c r="L11">
         <f>MAX(0,ABS(Statements!K19-(Statements!K20+Statements!K21))-MAX(0.01,0.001*ABS(Statements!K19)))</f>
         <v/>
       </c>
-      <c r="M11" s="13">
+      <c r="M11">
         <f>MAX(0,ABS(Statements!L19-(Statements!L20+Statements!L21))-MAX(0.01,0.001*ABS(Statements!L19)))</f>
         <v/>
       </c>
-      <c r="N11" s="13">
+      <c r="N11">
         <f>MAX(0,ABS(Statements!M19-(Statements!M20+Statements!M21))-MAX(0.01,0.001*ABS(Statements!M19)))</f>
         <v/>
       </c>
-      <c r="O11" s="13">
+      <c r="O11">
         <f>MAX(0,ABS(Statements!N19-(Statements!N20+Statements!N21))-MAX(0.01,0.001*ABS(Statements!N19)))</f>
         <v/>
       </c>
-      <c r="P11" s="13">
+      <c r="P11">
         <f>MAX(0,ABS(Statements!O19-(Statements!O20+Statements!O21))-MAX(0.01,0.001*ABS(Statements!O19)))</f>
         <v/>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11">
         <f>MAX(0,ABS(Statements!P19-(Statements!P20+Statements!P21))-MAX(0.01,0.001*ABS(Statements!P19)))</f>
         <v/>
       </c>
-      <c r="R11" s="13">
+      <c r="R11">
         <f>MAX(0,ABS(Statements!Q19-(Statements!Q20+Statements!Q21))-MAX(0.01,0.001*ABS(Statements!Q19)))</f>
         <v/>
       </c>
-      <c r="S11" s="13">
+      <c r="S11">
         <f>MAX(0,ABS(Statements!R19-(Statements!R20+Statements!R21))-MAX(0.01,0.001*ABS(Statements!R19)))</f>
         <v/>
       </c>
-      <c r="T11" s="13">
+      <c r="T11">
         <f>MAX(0,ABS(Statements!S19-(Statements!S20+Statements!S21))-MAX(0.01,0.001*ABS(Statements!S19)))</f>
         <v/>
       </c>
-      <c r="U11" s="13">
+      <c r="U11">
         <f>MAX(0,ABS(Statements!T19-(Statements!T20+Statements!T21))-MAX(0.01,0.001*ABS(Statements!T19)))</f>
         <v/>
       </c>
-      <c r="V11" s="13">
+      <c r="V11">
         <f>MAX(0,ABS(Statements!U19-(Statements!U20+Statements!U21))-MAX(0.01,0.001*ABS(Statements!U19)))</f>
         <v/>
       </c>
-      <c r="W11" s="13">
+      <c r="W11">
         <f>MAX(0,ABS(Statements!V19-(Statements!V20+Statements!V21))-MAX(0.01,0.001*ABS(Statements!V19)))</f>
         <v/>
       </c>
-      <c r="X11" s="13">
+      <c r="X11">
         <f>MAX(0,ABS(Statements!W19-(Statements!W20+Statements!W21))-MAX(0.01,0.001*ABS(Statements!W19)))</f>
         <v/>
       </c>
-      <c r="Y11" s="13">
+      <c r="Y11">
         <f>MAX(0,ABS(Statements!X19-(Statements!X20+Statements!X21))-MAX(0.01,0.001*ABS(Statements!X19)))</f>
         <v/>
       </c>
-      <c r="Z11" s="13">
+      <c r="Z11">
         <f>MAX(0,ABS(Statements!Y19-(Statements!Y20+Statements!Y21))-MAX(0.01,0.001*ABS(Statements!Y19)))</f>
         <v/>
       </c>
-      <c r="AA11" s="13">
+      <c r="AA11">
         <f>MAX(0,ABS(Statements!Z19-(Statements!Z20+Statements!Z21))-MAX(0.01,0.001*ABS(Statements!Z19)))</f>
         <v/>
       </c>
-      <c r="AB11" s="13">
+      <c r="AB11">
         <f>MAX(0,ABS(Statements!AA19-(Statements!AA20+Statements!AA21))-MAX(0.01,0.001*ABS(Statements!AA19)))</f>
         <v/>
       </c>
-      <c r="AC11" s="13">
+      <c r="AC11">
         <f>MAX(0,ABS(Statements!AB19-(Statements!AB20+Statements!AB21))-MAX(0.01,0.001*ABS(Statements!AB19)))</f>
         <v/>
       </c>
-      <c r="AD11" s="13">
+      <c r="AD11">
         <f>MAX(0,ABS(Statements!AC19-(Statements!AC20+Statements!AC21))-MAX(0.01,0.001*ABS(Statements!AC19)))</f>
         <v/>
       </c>
-      <c r="AE11" s="13">
+      <c r="AE11">
         <f>MAX(0,ABS(Statements!AD19-(Statements!AD20+Statements!AD21))-MAX(0.01,0.001*ABS(Statements!AD19)))</f>
         <v/>
       </c>
-      <c r="AF11" s="13">
+      <c r="AF11">
         <f>MAX(0,ABS(Statements!AE19-(Statements!AE20+Statements!AE21))-MAX(0.01,0.001*ABS(Statements!AE19)))</f>
         <v/>
       </c>
-      <c r="AG11" s="13">
+      <c r="AG11">
         <f>MAX(0,ABS(Statements!AF19-(Statements!AF20+Statements!AF21))-MAX(0.01,0.001*ABS(Statements!AF19)))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>dscr is present exactly inside the debt life</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12">
         <f>MAX(D12:AG12)</f>
         <v/>
       </c>
@@ -5559,134 +5280,134 @@
         <f>IF(B12=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D12" s="13">
+      <c r="D12">
         <f>IF(AND(Statements!$C$1&gt;=Identity!$B$13,Statements!$C$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!C31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="E12" s="13">
+      <c r="E12">
         <f>IF(AND(Statements!$D$1&gt;=Identity!$B$13,Statements!$D$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!D31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="F12" s="13">
+      <c r="F12">
         <f>IF(AND(Statements!$E$1&gt;=Identity!$B$13,Statements!$E$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!E31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12">
         <f>IF(AND(Statements!$F$1&gt;=Identity!$B$13,Statements!$F$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!F31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12">
         <f>IF(AND(Statements!$G$1&gt;=Identity!$B$13,Statements!$G$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!G31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12">
         <f>IF(AND(Statements!$H$1&gt;=Identity!$B$13,Statements!$H$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!H31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12">
         <f>IF(AND(Statements!$I$1&gt;=Identity!$B$13,Statements!$I$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!I31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="K12" s="13">
+      <c r="K12">
         <f>IF(AND(Statements!$J$1&gt;=Identity!$B$13,Statements!$J$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!J31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="L12" s="13">
+      <c r="L12">
         <f>IF(AND(Statements!$K$1&gt;=Identity!$B$13,Statements!$K$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!K31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="M12" s="13">
+      <c r="M12">
         <f>IF(AND(Statements!$L$1&gt;=Identity!$B$13,Statements!$L$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!L31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="N12" s="13">
+      <c r="N12">
         <f>IF(AND(Statements!$M$1&gt;=Identity!$B$13,Statements!$M$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!M31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="O12" s="13">
+      <c r="O12">
         <f>IF(AND(Statements!$N$1&gt;=Identity!$B$13,Statements!$N$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!N31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="P12" s="13">
+      <c r="P12">
         <f>IF(AND(Statements!$O$1&gt;=Identity!$B$13,Statements!$O$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!O31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="Q12" s="13">
+      <c r="Q12">
         <f>IF(AND(Statements!$P$1&gt;=Identity!$B$13,Statements!$P$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!P31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="R12" s="13">
+      <c r="R12">
         <f>IF(AND(Statements!$Q$1&gt;=Identity!$B$13,Statements!$Q$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!Q31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="S12" s="13">
+      <c r="S12">
         <f>IF(AND(Statements!$R$1&gt;=Identity!$B$13,Statements!$R$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!R31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="T12" s="13">
+      <c r="T12">
         <f>IF(AND(Statements!$S$1&gt;=Identity!$B$13,Statements!$S$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!S31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="U12" s="13">
+      <c r="U12">
         <f>IF(AND(Statements!$T$1&gt;=Identity!$B$13,Statements!$T$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!T31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="V12" s="13">
+      <c r="V12">
         <f>IF(AND(Statements!$U$1&gt;=Identity!$B$13,Statements!$U$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!U31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="W12" s="13">
+      <c r="W12">
         <f>IF(AND(Statements!$V$1&gt;=Identity!$B$13,Statements!$V$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!V31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="X12" s="13">
+      <c r="X12">
         <f>IF(AND(Statements!$W$1&gt;=Identity!$B$13,Statements!$W$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!W31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="Y12" s="13">
+      <c r="Y12">
         <f>IF(AND(Statements!$X$1&gt;=Identity!$B$13,Statements!$X$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!X31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="Z12" s="13">
+      <c r="Z12">
         <f>IF(AND(Statements!$Y$1&gt;=Identity!$B$13,Statements!$Y$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!Y31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AA12" s="13">
+      <c r="AA12">
         <f>IF(AND(Statements!$Z$1&gt;=Identity!$B$13,Statements!$Z$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!Z31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AB12" s="13">
+      <c r="AB12">
         <f>IF(AND(Statements!$AA$1&gt;=Identity!$B$13,Statements!$AA$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AA31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AC12" s="13">
+      <c r="AC12">
         <f>IF(AND(Statements!$AB$1&gt;=Identity!$B$13,Statements!$AB$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AB31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AD12" s="13">
+      <c r="AD12">
         <f>IF(AND(Statements!$AC$1&gt;=Identity!$B$13,Statements!$AC$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AC31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AE12" s="13">
+      <c r="AE12">
         <f>IF(AND(Statements!$AD$1&gt;=Identity!$B$13,Statements!$AD$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AD31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AF12" s="13">
+      <c r="AF12">
         <f>IF(AND(Statements!$AE$1&gt;=Identity!$B$13,Statements!$AE$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AE31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
-      <c r="AG12" s="13">
+      <c r="AG12">
         <f>IF(AND(Statements!$AF$1&gt;=Identity!$B$13,Statements!$AF$1&lt;Identity!$B$13+Assumptions!$B$6)=(Statements!AF31&lt;&gt;""),0,1)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>dscr = ebitda / (interestPaid + debtRepayment)</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13">
         <f>MAX(D13:AG13)</f>
         <v/>
       </c>
@@ -5694,134 +5415,134 @@
         <f>IF(B13=0,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13">
         <f>IF(OR(Statements!C31="",Statements!C16+Statements!C17=0),0,MAX(0,ABS(Statements!C31-Statements!C8/(Statements!C16+Statements!C17))-MAX(0.001,0.001*ABS(Statements!C31))))</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13">
         <f>IF(OR(Statements!D31="",Statements!D16+Statements!D17=0),0,MAX(0,ABS(Statements!D31-Statements!D8/(Statements!D16+Statements!D17))-MAX(0.001,0.001*ABS(Statements!D31))))</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13">
         <f>IF(OR(Statements!E31="",Statements!E16+Statements!E17=0),0,MAX(0,ABS(Statements!E31-Statements!E8/(Statements!E16+Statements!E17))-MAX(0.001,0.001*ABS(Statements!E31))))</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13">
         <f>IF(OR(Statements!F31="",Statements!F16+Statements!F17=0),0,MAX(0,ABS(Statements!F31-Statements!F8/(Statements!F16+Statements!F17))-MAX(0.001,0.001*ABS(Statements!F31))))</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13">
         <f>IF(OR(Statements!G31="",Statements!G16+Statements!G17=0),0,MAX(0,ABS(Statements!G31-Statements!G8/(Statements!G16+Statements!G17))-MAX(0.001,0.001*ABS(Statements!G31))))</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13">
         <f>IF(OR(Statements!H31="",Statements!H16+Statements!H17=0),0,MAX(0,ABS(Statements!H31-Statements!H8/(Statements!H16+Statements!H17))-MAX(0.001,0.001*ABS(Statements!H31))))</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13">
         <f>IF(OR(Statements!I31="",Statements!I16+Statements!I17=0),0,MAX(0,ABS(Statements!I31-Statements!I8/(Statements!I16+Statements!I17))-MAX(0.001,0.001*ABS(Statements!I31))))</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13">
         <f>IF(OR(Statements!J31="",Statements!J16+Statements!J17=0),0,MAX(0,ABS(Statements!J31-Statements!J8/(Statements!J16+Statements!J17))-MAX(0.001,0.001*ABS(Statements!J31))))</f>
         <v/>
       </c>
-      <c r="L13" s="13">
+      <c r="L13">
         <f>IF(OR(Statements!K31="",Statements!K16+Statements!K17=0),0,MAX(0,ABS(Statements!K31-Statements!K8/(Statements!K16+Statements!K17))-MAX(0.001,0.001*ABS(Statements!K31))))</f>
         <v/>
       </c>
-      <c r="M13" s="13">
+      <c r="M13">
         <f>IF(OR(Statements!L31="",Statements!L16+Statements!L17=0),0,MAX(0,ABS(Statements!L31-Statements!L8/(Statements!L16+Statements!L17))-MAX(0.001,0.001*ABS(Statements!L31))))</f>
         <v/>
       </c>
-      <c r="N13" s="13">
+      <c r="N13">
         <f>IF(OR(Statements!M31="",Statements!M16+Statements!M17=0),0,MAX(0,ABS(Statements!M31-Statements!M8/(Statements!M16+Statements!M17))-MAX(0.001,0.001*ABS(Statements!M31))))</f>
         <v/>
       </c>
-      <c r="O13" s="13">
+      <c r="O13">
         <f>IF(OR(Statements!N31="",Statements!N16+Statements!N17=0),0,MAX(0,ABS(Statements!N31-Statements!N8/(Statements!N16+Statements!N17))-MAX(0.001,0.001*ABS(Statements!N31))))</f>
         <v/>
       </c>
-      <c r="P13" s="13">
+      <c r="P13">
         <f>IF(OR(Statements!O31="",Statements!O16+Statements!O17=0),0,MAX(0,ABS(Statements!O31-Statements!O8/(Statements!O16+Statements!O17))-MAX(0.001,0.001*ABS(Statements!O31))))</f>
         <v/>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13">
         <f>IF(OR(Statements!P31="",Statements!P16+Statements!P17=0),0,MAX(0,ABS(Statements!P31-Statements!P8/(Statements!P16+Statements!P17))-MAX(0.001,0.001*ABS(Statements!P31))))</f>
         <v/>
       </c>
-      <c r="R13" s="13">
+      <c r="R13">
         <f>IF(OR(Statements!Q31="",Statements!Q16+Statements!Q17=0),0,MAX(0,ABS(Statements!Q31-Statements!Q8/(Statements!Q16+Statements!Q17))-MAX(0.001,0.001*ABS(Statements!Q31))))</f>
         <v/>
       </c>
-      <c r="S13" s="13">
+      <c r="S13">
         <f>IF(OR(Statements!R31="",Statements!R16+Statements!R17=0),0,MAX(0,ABS(Statements!R31-Statements!R8/(Statements!R16+Statements!R17))-MAX(0.001,0.001*ABS(Statements!R31))))</f>
         <v/>
       </c>
-      <c r="T13" s="13">
+      <c r="T13">
         <f>IF(OR(Statements!S31="",Statements!S16+Statements!S17=0),0,MAX(0,ABS(Statements!S31-Statements!S8/(Statements!S16+Statements!S17))-MAX(0.001,0.001*ABS(Statements!S31))))</f>
         <v/>
       </c>
-      <c r="U13" s="13">
+      <c r="U13">
         <f>IF(OR(Statements!T31="",Statements!T16+Statements!T17=0),0,MAX(0,ABS(Statements!T31-Statements!T8/(Statements!T16+Statements!T17))-MAX(0.001,0.001*ABS(Statements!T31))))</f>
         <v/>
       </c>
-      <c r="V13" s="13">
+      <c r="V13">
         <f>IF(OR(Statements!U31="",Statements!U16+Statements!U17=0),0,MAX(0,ABS(Statements!U31-Statements!U8/(Statements!U16+Statements!U17))-MAX(0.001,0.001*ABS(Statements!U31))))</f>
         <v/>
       </c>
-      <c r="W13" s="13">
+      <c r="W13">
         <f>IF(OR(Statements!V31="",Statements!V16+Statements!V17=0),0,MAX(0,ABS(Statements!V31-Statements!V8/(Statements!V16+Statements!V17))-MAX(0.001,0.001*ABS(Statements!V31))))</f>
         <v/>
       </c>
-      <c r="X13" s="13">
+      <c r="X13">
         <f>IF(OR(Statements!W31="",Statements!W16+Statements!W17=0),0,MAX(0,ABS(Statements!W31-Statements!W8/(Statements!W16+Statements!W17))-MAX(0.001,0.001*ABS(Statements!W31))))</f>
         <v/>
       </c>
-      <c r="Y13" s="13">
+      <c r="Y13">
         <f>IF(OR(Statements!X31="",Statements!X16+Statements!X17=0),0,MAX(0,ABS(Statements!X31-Statements!X8/(Statements!X16+Statements!X17))-MAX(0.001,0.001*ABS(Statements!X31))))</f>
         <v/>
       </c>
-      <c r="Z13" s="13">
+      <c r="Z13">
         <f>IF(OR(Statements!Y31="",Statements!Y16+Statements!Y17=0),0,MAX(0,ABS(Statements!Y31-Statements!Y8/(Statements!Y16+Statements!Y17))-MAX(0.001,0.001*ABS(Statements!Y31))))</f>
         <v/>
       </c>
-      <c r="AA13" s="13">
+      <c r="AA13">
         <f>IF(OR(Statements!Z31="",Statements!Z16+Statements!Z17=0),0,MAX(0,ABS(Statements!Z31-Statements!Z8/(Statements!Z16+Statements!Z17))-MAX(0.001,0.001*ABS(Statements!Z31))))</f>
         <v/>
       </c>
-      <c r="AB13" s="13">
+      <c r="AB13">
         <f>IF(OR(Statements!AA31="",Statements!AA16+Statements!AA17=0),0,MAX(0,ABS(Statements!AA31-Statements!AA8/(Statements!AA16+Statements!AA17))-MAX(0.001,0.001*ABS(Statements!AA31))))</f>
         <v/>
       </c>
-      <c r="AC13" s="13">
+      <c r="AC13">
         <f>IF(OR(Statements!AB31="",Statements!AB16+Statements!AB17=0),0,MAX(0,ABS(Statements!AB31-Statements!AB8/(Statements!AB16+Statements!AB17))-MAX(0.001,0.001*ABS(Statements!AB31))))</f>
         <v/>
       </c>
-      <c r="AD13" s="13">
+      <c r="AD13">
         <f>IF(OR(Statements!AC31="",Statements!AC16+Statements!AC17=0),0,MAX(0,ABS(Statements!AC31-Statements!AC8/(Statements!AC16+Statements!AC17))-MAX(0.001,0.001*ABS(Statements!AC31))))</f>
         <v/>
       </c>
-      <c r="AE13" s="13">
+      <c r="AE13">
         <f>IF(OR(Statements!AD31="",Statements!AD16+Statements!AD17=0),0,MAX(0,ABS(Statements!AD31-Statements!AD8/(Statements!AD16+Statements!AD17))-MAX(0.001,0.001*ABS(Statements!AD31))))</f>
         <v/>
       </c>
-      <c r="AF13" s="13">
+      <c r="AF13">
         <f>IF(OR(Statements!AE31="",Statements!AE16+Statements!AE17=0),0,MAX(0,ABS(Statements!AE31-Statements!AE8/(Statements!AE16+Statements!AE17))-MAX(0.001,0.001*ABS(Statements!AE31))))</f>
         <v/>
       </c>
-      <c r="AG13" s="13">
+      <c r="AG13">
         <f>IF(OR(Statements!AF31="",Statements!AF16+Statements!AF17=0),0,MAX(0,ABS(Statements!AF31-Statements!AF8/(Statements!AF16+Statements!AF17))-MAX(0.001,0.001*ABS(Statements!AF31))))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>closing[last] = 0</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14">
         <f>MAX(0,ABS(Statements!AF27)-MAX(0.01,0.001*ABS(0)))</f>
         <v/>
       </c>
@@ -5831,12 +5552,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>sum debtDrawdown = seniorDebt</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15">
         <f>MAX(0,ABS(SUM(Statements!$C$20:$AF$20)-Identity!$B$26)-MAX(0.01,0.001*ABS(Identity!$B$26)))</f>
         <v/>
       </c>
@@ -5846,12 +5567,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>sum equityDrawdown = totalCapex - seniorDebt</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16">
         <f>MAX(0,ABS(SUM(Statements!$C$21:$AF$21)-(Identity!$B$25-Identity!$B$26))-MAX(0.01,0.001*ABS(Identity!$B$25-Identity!$B$26)))</f>
         <v/>
       </c>
@@ -5861,12 +5582,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>sum capex = totalCapex</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17">
         <f>MAX(0,ABS(SUM(Statements!$C$19:$AF$19)-Identity!$B$25)-MAX(0.01,0.001*ABS(Identity!$B$25)))</f>
         <v/>
       </c>
@@ -5876,12 +5597,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>sum depreciation = totalCapex - ppe[last]</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18">
         <f>MAX(0,ABS(SUM(Statements!$C$9:$AF$9)-(Identity!$B$25-Statements!AF29))-MAX(0.01,0.001*ABS(Identity!$B$25)))</f>
         <v/>
       </c>
@@ -5891,12 +5612,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>taxExpense = taxRate * max(0, pbt)   [warn]</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19">
         <f>MAX(0,ABS(SUM(Statements!$C$13:$AF$13)-Assumptions!$B$3*SUMPRODUCT((Statements!$C$12:$AF$12&gt;0)*Statements!$C$12:$AF$12))-MAX(0.01,0.001*ABS(SUM(Statements!$C$13:$AF$13))))</f>
         <v/>
       </c>
@@ -5906,7 +5627,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Live formulas against Statements, Identity and Assumptions. Each cell holds the BREACH over tolerance -- max(0, |residual| - max(absolute, 0.1% of the line)) -- so zero means the year is inside tolerance and any non-zero cell names the year that is not. The absolute limb is EUR 0.01m for a money line and 0.001 for the DSCR ratio, from the assumption set. Every check must read PASS before the file is loaded; the last one is a plausibility warning, not a blocker.</t>
         </is>
